--- a/state_keywords_analysis.xlsx
+++ b/state_keywords_analysis.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F427"/>
+  <dimension ref="A1:F432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2338,73 +2338,73 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Apalachee High School, GA, Shooting (2024)</t>
+          <t>Self-Defense</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0066</v>
       </c>
       <c r="F85" t="n">
-        <v>501.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Registration of Voters</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>40</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F86" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Georgia Criminal Case Against Trump (2020 Election)</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>152</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="F86" t="n">
-        <v>336.2</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta Spa Shootings (2021)</t>
+          <t>Apalachee High School, GA, Shooting (2024)</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="F87" t="n">
-        <v>265.9</v>
+        <v>501.8</v>
       </c>
     </row>
     <row r="88">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Voting Rights Act (1965)</t>
+          <t>Georgia Criminal Case Against Trump (2020 Election)</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0455</v>
       </c>
       <c r="F88" t="n">
-        <v>27.2</v>
+        <v>336.2</v>
       </c>
     </row>
     <row r="89">
@@ -2438,61 +2438,61 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Presidential Election of 2020</t>
+          <t>Atlanta Spa Shootings (2021)</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>440</v>
+        <v>32</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.1319</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>23</v>
+        <v>265.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Voter Fraud (Election Fraud)</t>
+          <t>Voting Rights Act (1965)</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>204</v>
+        <v>22</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.0611</v>
+        <v>0.0066</v>
       </c>
       <c r="F90" t="n">
-        <v>90.09999999999999</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Racketeering and Racketeers</t>
+          <t>Presidential Election of 2020</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>51</v>
+        <v>440</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.1319</v>
       </c>
       <c r="F91" t="n">
-        <v>38.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92">
@@ -2504,17 +2504,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Voter Fraud (Election Fraud)</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>33</v>
+        <v>204</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0611</v>
       </c>
       <c r="F92" t="n">
-        <v>26.4</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -2526,17 +2526,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Voter Registration and Requirements</t>
+          <t>Racketeering and Racketeers</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0153</v>
       </c>
       <c r="F93" t="n">
-        <v>25.4</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="94">
@@ -2548,25 +2548,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Conspiracy Theories</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>20.3</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -2574,17 +2570,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hula Bowl</t>
+          <t>Voter Registration and Requirements</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>0.0043</v>
+        <v>0.0231</v>
       </c>
       <c r="F95" t="n">
-        <v>3085.4</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="96">
@@ -2596,21 +2592,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ehime Maru (Ship)</t>
+          <t>Conspiracy Theories</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>1487.6</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -2618,17 +2618,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Greeneville (Submarine)</t>
+          <t>Hula Bowl</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="F97" t="n">
-        <v>1410.5</v>
+        <v>3085.4</v>
       </c>
     </row>
     <row r="98">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Native Hawaiians</t>
+          <t>Ehime Maru (Ship)</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0385</v>
       </c>
       <c r="F98" t="n">
-        <v>981.7</v>
+        <v>1487.6</v>
       </c>
     </row>
     <row r="99">
@@ -2662,17 +2662,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Japan-International Relations-US</t>
+          <t>Greeneville (Submarine)</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>602</v>
+        <v>1410.5</v>
       </c>
     </row>
     <row r="100">
@@ -2684,17 +2684,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>False Alarms</t>
+          <t>Native Hawaiians</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="F100" t="n">
-        <v>457.1</v>
+        <v>981.7</v>
       </c>
     </row>
     <row r="101">
@@ -2706,25 +2706,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Submarines</t>
+          <t>Japan-International Relations-US</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.0471</v>
+        <v>0.0114</v>
       </c>
       <c r="F101" t="n">
-        <v>393.1</v>
+        <v>602</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Idaho</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -2732,17 +2728,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nez Perce Indians</t>
+          <t>False Alarms</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>2510.1</v>
+        <v>457.1</v>
       </c>
     </row>
     <row r="103">
@@ -2754,21 +2750,25 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Submarines</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0471</v>
       </c>
       <c r="F103" t="n">
-        <v>198.5</v>
+        <v>393.1</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Eighth Amendment (US Constitution)</t>
+          <t>Nez Perce Indians</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.0058</v>
       </c>
       <c r="F104" t="n">
-        <v>148.1</v>
+        <v>2510.1</v>
       </c>
     </row>
     <row r="105">
@@ -2798,17 +2798,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0251</v>
       </c>
       <c r="F105" t="n">
-        <v>106.4</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="106">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nuclear Wastes</t>
+          <t>Eighth Amendment (US Constitution)</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0077</v>
       </c>
       <c r="F106" t="n">
-        <v>95.7</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="107">
@@ -2842,17 +2842,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Logging Industry</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0058</v>
       </c>
       <c r="F107" t="n">
-        <v>83.90000000000001</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="108">
@@ -2864,43 +2864,39 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Genealogy</t>
+          <t>Nuclear Wastes</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.0193</v>
       </c>
       <c r="F108" t="n">
-        <v>79.59999999999999</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Illinois</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Highland Park Parade Shooting (July 4, 2022)</t>
+          <t>Logging Industry</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0155</v>
       </c>
       <c r="F109" t="n">
-        <v>373.5</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -2912,39 +2908,43 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Federal Actions in US Cities</t>
+          <t>Genealogy</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0135</v>
       </c>
       <c r="F110" t="n">
-        <v>111.4</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Democratic National Convention</t>
+          <t>Highland Park Parade Shooting (July 4, 2022)</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.005</v>
       </c>
       <c r="F111" t="n">
-        <v>27.5</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="112">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Federal Actions in US Cities</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0148</v>
       </c>
       <c r="F112" t="n">
-        <v>25.5</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="113">
@@ -2978,17 +2978,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gangs</t>
+          <t>Democratic National Convention</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.0124</v>
+        <v>0.0131</v>
       </c>
       <c r="F113" t="n">
-        <v>21.6</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="114">
@@ -3000,17 +3000,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Racketeering and Racketeers</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0095</v>
       </c>
       <c r="F114" t="n">
-        <v>13.8</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="115">
@@ -3022,17 +3022,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>False Arrests, Convictions and Imprisonments</t>
+          <t>Gangs</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0124</v>
       </c>
       <c r="F115" t="n">
-        <v>12.5</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="116">
@@ -3044,43 +3044,39 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Police Brutality, Misconduct and Shootings</t>
+          <t>Racketeering and Racketeers</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.0491</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>11.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Indianapolis, Ind, Shooting (April, 2021)</t>
+          <t>False Arrests, Convictions and Imprisonments</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0067</v>
       </c>
       <c r="F117" t="n">
-        <v>1389.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="118">
@@ -3092,39 +3088,43 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Prairie Dogs</t>
+          <t>Police Brutality, Misconduct and Shootings</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6</v>
+        <v>206</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0491</v>
       </c>
       <c r="F118" t="n">
-        <v>496.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Blue Collar Workers</t>
+          <t>Indianapolis, Ind, Shooting (April, 2021)</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.0043</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>96.5</v>
+        <v>1389.4</v>
       </c>
     </row>
     <row r="120">
@@ -3136,17 +3136,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Prairie Dogs</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0064</v>
       </c>
       <c r="F120" t="n">
-        <v>92.09999999999999</v>
+        <v>496.2</v>
       </c>
     </row>
     <row r="121">
@@ -3158,17 +3158,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hypodermic Needles and Syringes</t>
+          <t>Blue Collar Workers</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0043</v>
       </c>
       <c r="F121" t="n">
-        <v>88.2</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="122">
@@ -3180,17 +3180,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>State and County Fairs</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.0043</v>
+        <v>0.0075</v>
       </c>
       <c r="F122" t="n">
-        <v>77.8</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -3202,17 +3202,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Hypodermic Needles and Syringes</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0086</v>
       </c>
       <c r="F123" t="n">
-        <v>57.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="124">
@@ -3224,87 +3224,87 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Freedom of Religion</t>
+          <t>State and County Fairs</t>
         </is>
       </c>
       <c r="D124" t="n">
+        <v>4</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="F124" t="n">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tornadoes</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
         <v>20</v>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E125" s="2" t="n">
         <v>0.0214</v>
       </c>
-      <c r="F124" t="n">
-        <v>40.2</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Presidential Election of 2012</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>469</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>0.1665</v>
-      </c>
       <c r="F125" t="n">
-        <v>46.8</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Freedom of Religion</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>20</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="F126" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Presidential Election of 2016</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>539</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>0.1914</v>
-      </c>
-      <c r="F126" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Presidential Election of 2004</t>
+          <t>Presidential Election of 2012</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>232</v>
+        <v>469</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.0824</v>
+        <v>0.1665</v>
       </c>
       <c r="F127" t="n">
-        <v>27.8</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="128">
@@ -3316,61 +3316,61 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Presidential Election of 2008</t>
+          <t>Presidential Election of 2016</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>212</v>
+        <v>539</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1914</v>
       </c>
       <c r="F128" t="n">
-        <v>24.1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>State and County Fairs</t>
+          <t>Presidential Election of 2004</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0824</v>
       </c>
       <c r="F129" t="n">
-        <v>135.5</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Primaries and Caucuses</t>
+          <t>Presidential Election of 2008</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>840</v>
+        <v>212</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.2983</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>56.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="131">
@@ -3382,17 +3382,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Political Advertising</t>
+          <t>State and County Fairs</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>0.0558</v>
+        <v>0.0075</v>
       </c>
       <c r="F131" t="n">
-        <v>32.4</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="132">
@@ -3404,17 +3404,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ethanol</t>
+          <t>Primaries and Caucuses</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>14</v>
+        <v>840</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.005</v>
+        <v>0.2983</v>
       </c>
       <c r="F132" t="n">
-        <v>30.5</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="133">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Evangelical Movement</t>
+          <t>Political Advertising</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.0107</v>
+        <v>0.0558</v>
       </c>
       <c r="F133" t="n">
-        <v>24.4</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="134">
@@ -3448,25 +3448,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Endorsements</t>
+          <t>Ethanol</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.005</v>
       </c>
       <c r="F134" t="n">
-        <v>21.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -3474,17 +3470,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Swatting (Crime)</t>
+          <t>Evangelical Movement</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0107</v>
       </c>
       <c r="F135" t="n">
-        <v>338.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="136">
@@ -3496,21 +3492,25 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>American Airlines Flight 5342</t>
+          <t>Endorsements</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0231</v>
       </c>
       <c r="F136" t="n">
-        <v>221.5</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -3518,17 +3518,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dust and Sand Storms</t>
+          <t>Swatting (Crime)</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0.004</v>
+        <v>0.0053</v>
       </c>
       <c r="F137" t="n">
-        <v>200.9</v>
+        <v>338.8</v>
       </c>
     </row>
     <row r="138">
@@ -3540,17 +3540,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Creationism</t>
+          <t>American Airlines Flight 5342</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.004</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>169.4</v>
+        <v>221.5</v>
       </c>
     </row>
     <row r="139">
@@ -3562,17 +3562,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Somali-Americans</t>
+          <t>Dust and Sand Storms</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.004</v>
       </c>
       <c r="F139" t="n">
-        <v>145.8</v>
+        <v>200.9</v>
       </c>
     </row>
     <row r="140">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Birth Certificates</t>
+          <t>Creationism</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -3594,7 +3594,7 @@
         <v>0.004</v>
       </c>
       <c r="F140" t="n">
-        <v>130.9</v>
+        <v>169.4</v>
       </c>
     </row>
     <row r="141">
@@ -3606,109 +3606,109 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Somali-Americans</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0053</v>
       </c>
       <c r="F141" t="n">
-        <v>103.1</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Louisville, KY, Bank Shooting (April 2023)</t>
+          <t>Birth Certificates</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="F142" t="n">
-        <v>1626.7</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Tornadoes</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>29</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="F143" t="n">
+        <v>103.1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>George Floyd Protests (2020)</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>26</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="F143" t="n">
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr"/>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bourbon (Whiskey)</t>
+          <t>Louisville, KY, Bank Shooting (April 2023)</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F144" t="n">
-        <v>286.3</v>
+        <v>1626.7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ten Commandments</t>
+          <t>George Floyd Protests (2020)</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0235</v>
       </c>
       <c r="F145" t="n">
-        <v>157.1</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="146">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Bourbon (Whiskey)</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.0478</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F146" t="n">
-        <v>127.7</v>
+        <v>286.3</v>
       </c>
     </row>
     <row r="147">
@@ -3742,17 +3742,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Sheriffs</t>
+          <t>Ten Commandments</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0063</v>
       </c>
       <c r="F147" t="n">
-        <v>56.1</v>
+        <v>157.1</v>
       </c>
     </row>
     <row r="148">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Black Lives Matter Movement</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.0361</v>
+        <v>0.0478</v>
       </c>
       <c r="F148" t="n">
-        <v>54.6</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="149">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Police Reform</t>
+          <t>Sheriffs</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F149" t="n">
-        <v>39.6</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="150">
@@ -3808,87 +3808,87 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Black Lives Matter Movement</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0361</v>
       </c>
       <c r="F150" t="n">
-        <v>32.6</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Louisiana</t>
-        </is>
-      </c>
+      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hurricane Laura (2020)</t>
+          <t>Police Reform</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0072</v>
       </c>
       <c r="F151" t="n">
-        <v>566</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>32</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="F152" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, New Year's Day Attack (2025)</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>29</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="F152" t="n">
-        <v>524.8</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr"/>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hurricane Isaac (2012)</t>
+          <t>Hurricane Laura (2020)</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0123</v>
       </c>
       <c r="F153" t="n">
-        <v>423.2</v>
+        <v>566</v>
       </c>
     </row>
     <row r="154">
@@ -3900,17 +3900,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hurricane Gustav</t>
+          <t>New Orleans, LA, New Year's Day Attack (2025)</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0119</v>
       </c>
       <c r="F154" t="n">
-        <v>295.6</v>
+        <v>524.8</v>
       </c>
     </row>
     <row r="155">
@@ -3922,17 +3922,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hurricane Katrina</t>
+          <t>Hurricane Isaac (2012)</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>714</v>
+        <v>21</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.2927</v>
+        <v>0.0086</v>
       </c>
       <c r="F155" t="n">
-        <v>275.8</v>
+        <v>423.2</v>
       </c>
     </row>
     <row r="156">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Rita (Storm)</t>
+          <t>Hurricane Gustav</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -3954,7 +3954,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F156" t="n">
-        <v>264.5</v>
+        <v>295.6</v>
       </c>
     </row>
     <row r="157">
@@ -3966,61 +3966,61 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hurricane Ida (2021)</t>
+          <t>Hurricane Katrina</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>39</v>
+        <v>714</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.016</v>
+        <v>0.2927</v>
       </c>
       <c r="F157" t="n">
-        <v>230.6</v>
+        <v>275.8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Superdome (New Orleans)</t>
+          <t>Rita (Storm)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F158" t="n">
-        <v>886.8</v>
+        <v>264.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Levees</t>
+          <t>Hurricane Ida (2021)</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.016</v>
       </c>
       <c r="F159" t="n">
-        <v>636.7</v>
+        <v>230.6</v>
       </c>
     </row>
     <row r="160">
@@ -4032,43 +4032,39 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mardi Gras</t>
+          <t>Superdome (New Orleans)</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0049</v>
       </c>
       <c r="F160" t="n">
-        <v>311.2</v>
+        <v>886.8</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Maine</t>
-        </is>
-      </c>
+      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Lewiston, Maine, Shootings (2023)</t>
+          <t>Levees</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0.0503</v>
+        <v>0.0115</v>
       </c>
       <c r="F161" t="n">
-        <v>2133.8</v>
+        <v>636.7</v>
       </c>
     </row>
     <row r="162">
@@ -4080,17 +4076,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Lobsters</t>
+          <t>Mardi Gras</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0164</v>
       </c>
       <c r="F162" t="n">
-        <v>191.3</v>
+        <v>311.2</v>
       </c>
     </row>
     <row r="163">
@@ -4102,17 +4098,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Paper and Pulp</t>
+          <t>Dams and Dikes</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0139</v>
       </c>
       <c r="F163" t="n">
-        <v>78.59999999999999</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="164">
@@ -4124,39 +4120,43 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Migrant Labor</t>
+          <t>Hurricanes and Tropical Storms</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>462</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.005</v>
+        <v>0.1894</v>
       </c>
       <c r="F164" t="n">
-        <v>77.2</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Fourteenth Amendment (US Constitution)</t>
+          <t>Lewiston, Maine, Shootings (2023)</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.0101</v>
+        <v>0.0503</v>
       </c>
       <c r="F165" t="n">
-        <v>67</v>
+        <v>2133.8</v>
       </c>
     </row>
     <row r="166">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Fishing, Commercial</t>
+          <t>Lobsters</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0226</v>
       </c>
       <c r="F166" t="n">
-        <v>53.1</v>
+        <v>191.3</v>
       </c>
     </row>
     <row r="167">
@@ -4190,17 +4190,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Fish Farming</t>
+          <t>Paper and Pulp</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="F167" t="n">
-        <v>50.9</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="168">
@@ -4212,25 +4212,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Reserves (Military)</t>
+          <t>Migrant Labor</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.005</v>
       </c>
       <c r="F168" t="n">
-        <v>50.2</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
+      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -4238,17 +4234,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serial Murders</t>
+          <t>Fourteenth Amendment (US Constitution)</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.1275</v>
+        <v>0.0101</v>
       </c>
       <c r="F169" t="n">
-        <v>290.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="170">
@@ -4260,17 +4256,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ports</t>
+          <t>Fishing, Commercial</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.0352</v>
       </c>
       <c r="F170" t="n">
-        <v>41.9</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="171">
@@ -4282,17 +4278,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Maritime Accidents and Safety</t>
+          <t>Fish Farming</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.005</v>
       </c>
       <c r="F171" t="n">
-        <v>40.6</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="172">
@@ -4304,21 +4300,25 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Arson</t>
+          <t>Reserves (Military)</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0063</v>
       </c>
       <c r="F172" t="n">
-        <v>36.7</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -4326,17 +4326,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Freight (Cargo)</t>
+          <t>Serial Murders</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>14</v>
+        <v>247</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.1275</v>
       </c>
       <c r="F173" t="n">
-        <v>33</v>
+        <v>290.9</v>
       </c>
     </row>
     <row r="174">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bridges and Tunnels</t>
+          <t>Ports</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0108</v>
       </c>
       <c r="F174" t="n">
-        <v>29.7</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="175">
@@ -4370,43 +4370,39 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Confessions</t>
+          <t>Maritime Accidents and Safety</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0207</v>
       </c>
       <c r="F175" t="n">
-        <v>27.2</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Boston Marathon Bombings (2013)</t>
+          <t>Arson</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0181</v>
       </c>
       <c r="F176" t="n">
-        <v>228.5</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="177">
@@ -4418,17 +4414,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Logan International Airport (Boston)</t>
+          <t>Freight (Cargo)</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0072</v>
       </c>
       <c r="F177" t="n">
-        <v>264.4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="178">
@@ -4440,17 +4436,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Bridges and Tunnels</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.0717</v>
+        <v>0.0253</v>
       </c>
       <c r="F178" t="n">
-        <v>59</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="179">
@@ -4462,39 +4458,43 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Informers</t>
+          <t>Confessions</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0052</v>
       </c>
       <c r="F179" t="n">
-        <v>42.3</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cardinals (Roman Catholic Prelates)</t>
+          <t>Boston Marathon Bombings (2013)</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0445</v>
       </c>
       <c r="F180" t="n">
-        <v>34.8</v>
+        <v>228.5</v>
       </c>
     </row>
     <row r="181">
@@ -4506,17 +4506,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Conventions, National (US)</t>
+          <t>Logan International Airport (Boston)</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.005</v>
       </c>
       <c r="F181" t="n">
-        <v>32.2</v>
+        <v>264.4</v>
       </c>
     </row>
     <row r="182">
@@ -4528,17 +4528,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Organized Crime</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>69</v>
+        <v>229</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0717</v>
       </c>
       <c r="F182" t="n">
-        <v>24.4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="183">
@@ -4550,43 +4550,39 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Child Abuse and Neglect</t>
+          <t>Informers</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>229</v>
+        <v>25</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.0717</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F183" t="n">
-        <v>24.3</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
+      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Oxford Charter Township, Mich, Shooting (2021)</t>
+          <t>Cardinals (Roman Catholic Prelates)</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.006</v>
       </c>
       <c r="F184" t="n">
-        <v>506.2</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="185">
@@ -4598,17 +4594,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Arab-Americans</t>
+          <t>Conventions, National (US)</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0219</v>
       </c>
       <c r="F185" t="n">
-        <v>146.9</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="186">
@@ -4620,17 +4616,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Organized Crime</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.0216</v>
       </c>
       <c r="F186" t="n">
-        <v>144.4</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="187">
@@ -4642,39 +4638,43 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Muslim Americans</t>
+          <t>Child Abuse and Neglect</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0717</v>
       </c>
       <c r="F187" t="n">
-        <v>35.6</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Voter Fraud (Election Fraud)</t>
+          <t>Oxford Charter Township, Mich, Shooting (2021)</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.0119</v>
       </c>
       <c r="F188" t="n">
-        <v>33</v>
+        <v>506.2</v>
       </c>
     </row>
     <row r="189">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Water Pollution</t>
+          <t>Arab-Americans</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0235</v>
       </c>
       <c r="F189" t="n">
-        <v>32.4</v>
+        <v>146.9</v>
       </c>
     </row>
     <row r="190">
@@ -4708,17 +4708,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Electoral College</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0362</v>
       </c>
       <c r="F190" t="n">
-        <v>24.9</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="191">
@@ -4730,87 +4730,83 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Muslim Americans</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0123</v>
       </c>
       <c r="F191" t="n">
-        <v>20.8</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
+      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Shootings of Minnesota Legislators (2025)</t>
+          <t>Voter Fraud (Election Fraud)</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>0.0224</v>
       </c>
       <c r="F192" t="n">
-        <v>969.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Minneapolis Catholic School Shooting (Aug 27, 2025)</t>
+          <t>Water Pollution</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0366</v>
       </c>
       <c r="F193" t="n">
-        <v>680.5</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>George Floyd Protests (2020)</t>
+          <t>Electoral College</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0063</v>
       </c>
       <c r="F194" t="n">
-        <v>122.3</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="195">
@@ -4822,83 +4818,87 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Somali-Americans</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0347</v>
       </c>
       <c r="F195" t="n">
-        <v>565.3</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Federal Actions in US Cities</t>
+          <t>Shootings of Minnesota Legislators (2025)</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0224</v>
       </c>
       <c r="F196" t="n">
-        <v>249</v>
+        <v>969.8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Looting (Crime)</t>
+          <t>Minneapolis Catholic School Shooting (Aug 27, 2025)</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F197" t="n">
-        <v>116</v>
+        <v>680.5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Police Reform</t>
+          <t>George Floyd Protests (2020)</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F198" t="n">
-        <v>100.4</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="199">
@@ -4910,17 +4910,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Black Lives Matter Movement</t>
+          <t>Somali-Americans</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.0525</v>
+        <v>0.0206</v>
       </c>
       <c r="F199" t="n">
-        <v>79.40000000000001</v>
+        <v>565.3</v>
       </c>
     </row>
     <row r="200">
@@ -4932,17 +4932,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Stun Guns</t>
+          <t>Federal Actions in US Cities</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.033</v>
       </c>
       <c r="F200" t="n">
-        <v>72.5</v>
+        <v>249</v>
       </c>
     </row>
     <row r="201">
@@ -4954,87 +4954,83 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Police Brutality, Misconduct and Shootings</t>
+          <t>Looting (Crime)</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>331</v>
+        <v>10</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.1953</v>
+        <v>0.0059</v>
       </c>
       <c r="F201" t="n">
-        <v>47</v>
+        <v>116</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Mississippi</t>
-        </is>
-      </c>
+      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Presidential Election of 1948</t>
+          <t>Police Reform</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0183</v>
       </c>
       <c r="F202" t="n">
-        <v>423.4</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hurricane Isaac (2012)</t>
+          <t>Black Lives Matter Movement</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0525</v>
       </c>
       <c r="F203" t="n">
-        <v>307.9</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hurricane Katrina</t>
+          <t>Stun Guns</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.0799</v>
+        <v>0.0059</v>
       </c>
       <c r="F204" t="n">
-        <v>75.2</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="205">
@@ -5046,83 +5042,87 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Sheriffs</t>
+          <t>Police Brutality, Misconduct and Shootings</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>18</v>
+        <v>331</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.1953</v>
       </c>
       <c r="F205" t="n">
-        <v>175.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Presidential Election of 1948</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F206" t="n">
-        <v>119.2</v>
+        <v>423.4</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Lynching</t>
+          <t>Hurricane Isaac (2012)</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0063</v>
       </c>
       <c r="F207" t="n">
-        <v>89.09999999999999</v>
+        <v>307.9</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Flags, Emblems and Insignia</t>
+          <t>Hurricane Katrina</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0799</v>
       </c>
       <c r="F208" t="n">
-        <v>56.7</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="209">
@@ -5134,17 +5134,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Appeals Courts</t>
+          <t>Sheriffs</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0141</v>
       </c>
       <c r="F209" t="n">
-        <v>56.5</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="210">
@@ -5156,17 +5156,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Civil Rights Movement (1954-68)</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0446</v>
       </c>
       <c r="F210" t="n">
-        <v>53.2</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="211">
@@ -5178,43 +5178,39 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Autopsies</t>
+          <t>Lynching</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F211" t="n">
-        <v>51.8</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Missouri</t>
-        </is>
-      </c>
+      <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Kansas City, MO, Shooting (Feb 14, 2024)</t>
+          <t>Flags, Emblems and Insignia</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0227</v>
       </c>
       <c r="F212" t="n">
-        <v>910.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="213">
@@ -5226,17 +5222,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Appeals Courts</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F213" t="n">
-        <v>108.8</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="214">
@@ -5248,17 +5244,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Traffic and Parking Violations</t>
+          <t>Civil Rights Movement (1954-68)</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0227</v>
       </c>
       <c r="F214" t="n">
-        <v>51.8</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="215">
@@ -5270,39 +5266,43 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Police Brutality, Misconduct and Shootings</t>
+          <t>Autopsies</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>371</v>
+        <v>7</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>0.2043</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F215" t="n">
-        <v>49.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Racial Profiling</t>
+          <t>Kansas City, MO, Shooting (Feb 14, 2024)</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0072</v>
       </c>
       <c r="F216" t="n">
-        <v>49.1</v>
+        <v>910.8</v>
       </c>
     </row>
     <row r="217">
@@ -5314,17 +5314,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Child Pornography</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0407</v>
       </c>
       <c r="F217" t="n">
-        <v>39.3</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="218">
@@ -5336,17 +5336,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Levees and Dams</t>
+          <t>Traffic and Parking Violations</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0061</v>
       </c>
       <c r="F218" t="n">
-        <v>33</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="219">
@@ -5358,25 +5358,21 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Rivers</t>
+          <t>Police Brutality, Misconduct and Shootings</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.2043</v>
       </c>
       <c r="F219" t="n">
-        <v>22.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Montana</t>
-        </is>
-      </c>
+      <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -5384,17 +5380,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Vermiculite</t>
+          <t>Racial Profiling</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="F220" t="n">
-        <v>1398.1</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="221">
@@ -5406,17 +5402,17 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Brucellosis</t>
+          <t>Child Pornography</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="F221" t="n">
-        <v>815.6</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="222">
@@ -5428,17 +5424,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bison</t>
+          <t>Levees and Dams</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F222" t="n">
-        <v>348.4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="223">
@@ -5450,21 +5446,25 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Balloons (Aeronautics)</t>
+          <t>Rivers</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="F223" t="n">
-        <v>225</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -5472,17 +5472,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Vermiculite</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F224" t="n">
-        <v>154.8</v>
+        <v>1398.1</v>
       </c>
     </row>
     <row r="225">
@@ -5494,17 +5494,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bears</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>0.0241</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F225" t="n">
-        <v>127.9</v>
+        <v>815.6</v>
       </c>
     </row>
     <row r="226">
@@ -5516,25 +5516,21 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Bison</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0166</v>
       </c>
       <c r="F226" t="n">
-        <v>96.2</v>
+        <v>348.4</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
+      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -5542,17 +5538,17 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Keystone Pipeline System</t>
+          <t>Balloons (Aeronautics)</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F227" t="n">
-        <v>212.3</v>
+        <v>225</v>
       </c>
     </row>
     <row r="228">
@@ -5564,17 +5560,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Abandonment (Property)</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0196</v>
       </c>
       <c r="F228" t="n">
-        <v>165.6</v>
+        <v>154.8</v>
       </c>
     </row>
     <row r="229">
@@ -5586,17 +5582,17 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Oil Spills</t>
+          <t>Bears</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0241</v>
       </c>
       <c r="F229" t="n">
-        <v>83.7</v>
+        <v>127.9</v>
       </c>
     </row>
     <row r="230">
@@ -5608,21 +5604,25 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Oil Sands</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0151</v>
       </c>
       <c r="F230" t="n">
-        <v>71.09999999999999</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -5630,17 +5630,17 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Electoral College</t>
+          <t>Keystone Pipeline System</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0279</v>
       </c>
       <c r="F231" t="n">
-        <v>68.5</v>
+        <v>212.3</v>
       </c>
     </row>
     <row r="232">
@@ -5652,17 +5652,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Beef</t>
+          <t>Abandonment (Property)</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0139</v>
       </c>
       <c r="F232" t="n">
-        <v>54.2</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="233">
@@ -5674,43 +5674,39 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Abortion Drugs</t>
+          <t>Oil Spills</t>
         </is>
       </c>
       <c r="D233" t="n">
+        <v>4</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F233" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Oil Sands</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
         <v>3</v>
       </c>
-      <c r="E233" s="2" t="n">
+      <c r="E234" s="2" t="n">
         <v>0.0052</v>
       </c>
-      <c r="F233" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Nevada</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Las Vegas, Nev, Shooting (October, 2017)</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>54</v>
-      </c>
-      <c r="E234" s="2" t="n">
-        <v>0.0327</v>
-      </c>
       <c r="F234" t="n">
-        <v>343.2</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="235">
@@ -5722,17 +5718,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Burning Man Festival</t>
+          <t>Electoral College</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0174</v>
       </c>
       <c r="F235" t="n">
-        <v>197.1</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="236">
@@ -5744,17 +5740,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Nuclear Wastes</t>
+          <t>Beef</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F236" t="n">
-        <v>164.8</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="237">
@@ -5766,39 +5762,43 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avalanches</t>
+          <t>Abortion Drugs</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0052</v>
       </c>
       <c r="F237" t="n">
-        <v>70.90000000000001</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Casinos</t>
+          <t>Las Vegas, Nev, Shooting (October, 2017)</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="E238" s="2" t="n">
-        <v>0.046</v>
+        <v>0.0327</v>
       </c>
       <c r="F238" t="n">
-        <v>63.3</v>
+        <v>343.2</v>
       </c>
     </row>
     <row r="239">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Federal Lands</t>
+          <t>Burning Man Festival</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F239" t="n">
-        <v>43.1</v>
+        <v>197.1</v>
       </c>
     </row>
     <row r="240">
@@ -5832,17 +5832,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ethics (Institutional)</t>
+          <t>Nuclear Wastes</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0333</v>
       </c>
       <c r="F240" t="n">
-        <v>33.8</v>
+        <v>164.8</v>
       </c>
     </row>
     <row r="241">
@@ -5854,219 +5854,219 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Gambling</t>
+          <t>Avalanches</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0.0309</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F241" t="n">
-        <v>27.1</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>New Hampshire</t>
-        </is>
-      </c>
+      <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Presidential Election of 2012</t>
+          <t>Casinos</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>297</v>
+        <v>76</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0.1459</v>
+        <v>0.046</v>
       </c>
       <c r="F242" t="n">
-        <v>41</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Presidential Election of 2004</t>
+          <t>Federal Lands</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>186</v>
+        <v>11</v>
       </c>
       <c r="E243" s="2" t="n">
-        <v>0.09140000000000001</v>
+        <v>0.0067</v>
       </c>
       <c r="F243" t="n">
-        <v>30.8</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Presidential Election of 2016</t>
+          <t>Ethics (Institutional)</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>397</v>
+        <v>9</v>
       </c>
       <c r="E244" s="2" t="n">
-        <v>0.1951</v>
+        <v>0.0054</v>
       </c>
       <c r="F244" t="n">
-        <v>29.6</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Gambling</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>51</v>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="F245" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Presidential Election of 2000</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>115</v>
-      </c>
-      <c r="E245" s="2" t="n">
-        <v>0.0565</v>
-      </c>
-      <c r="F245" t="n">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr"/>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Presidential Election of 2008</t>
+          <t>Presidential Election of 2012</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>137</v>
+        <v>297</v>
       </c>
       <c r="E246" s="2" t="n">
-        <v>0.0673</v>
+        <v>0.1459</v>
       </c>
       <c r="F246" t="n">
-        <v>21.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Primaries and Caucuses</t>
+          <t>Presidential Election of 2004</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>646</v>
+        <v>186</v>
       </c>
       <c r="E247" s="2" t="n">
-        <v>0.3174</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="F247" t="n">
-        <v>59.8</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Political Advertising</t>
+          <t>Presidential Election of 2016</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>116</v>
+        <v>397</v>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.057</v>
+        <v>0.1951</v>
       </c>
       <c r="F248" t="n">
-        <v>33.1</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Endorsements</t>
+          <t>Presidential Election of 2000</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0565</v>
       </c>
       <c r="F249" t="n">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Debates (Political)</t>
+          <t>Presidential Election of 2008</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0673</v>
       </c>
       <c r="F250" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="251">
@@ -6078,43 +6078,39 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Political Action Committees</t>
+          <t>Primaries and Caucuses</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>24</v>
+        <v>646</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.3174</v>
       </c>
       <c r="F251" t="n">
-        <v>21.4</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
+      <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Hurricane Sandy (2012)</t>
+          <t>Political Advertising</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="E252" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.057</v>
       </c>
       <c r="F252" t="n">
-        <v>12.8</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="253">
@@ -6126,17 +6122,17 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Lotteries</t>
+          <t>Endorsements</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>2125</v>
+        <v>56</v>
       </c>
       <c r="E253" s="2" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.0275</v>
       </c>
       <c r="F253" t="n">
-        <v>59.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="254">
@@ -6148,17 +6144,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Tolls</t>
+          <t>Debates (Political)</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="E254" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.0383</v>
       </c>
       <c r="F254" t="n">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="255">
@@ -6170,39 +6166,43 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Casinos</t>
+          <t>Political Action Committees</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>234</v>
+        <v>24</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>0.0107</v>
+        <v>0.0118</v>
       </c>
       <c r="F255" t="n">
-        <v>14.7</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr"/>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Property Taxes</t>
+          <t>Hurricane Sandy (2012)</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="F256" t="n">
-        <v>14.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="257">
@@ -6214,17 +6214,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bridges and Tunnels</t>
+          <t>Lotteries</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>220</v>
+        <v>2125</v>
       </c>
       <c r="E257" s="2" t="n">
-        <v>0.01</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="F257" t="n">
-        <v>11.8</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="258">
@@ -6236,17 +6236,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Commuting</t>
+          <t>Tolls</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="E258" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0077</v>
       </c>
       <c r="F258" t="n">
-        <v>11.3</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="259">
@@ -6258,25 +6258,21 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Roads and Traffic</t>
+          <t>Casinos</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>755</v>
+        <v>234</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.0107</v>
       </c>
       <c r="F259" t="n">
-        <v>10.6</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
+      <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -6284,17 +6280,17 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Cockfighting</t>
+          <t>Property Taxes</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>4</v>
+        <v>172</v>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F260" t="n">
-        <v>320.8</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="261">
@@ -6306,17 +6302,17 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Navajo Indians</t>
+          <t>Bridges and Tunnels</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.01</v>
       </c>
       <c r="F261" t="n">
-        <v>319.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="262">
@@ -6328,17 +6324,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Treasure Troves</t>
+          <t>Commuting</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4</v>
+        <v>191</v>
       </c>
       <c r="E262" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>202.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="263">
@@ -6350,21 +6346,25 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Manhattan Project</t>
+          <t>Roads and Traffic</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>5</v>
+        <v>755</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0345</v>
       </c>
       <c r="F263" t="n">
-        <v>144.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Plague</t>
+          <t>Cockfighting</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6382,7 +6382,7 @@
         <v>0.0046</v>
       </c>
       <c r="F264" t="n">
-        <v>106.9</v>
+        <v>320.8</v>
       </c>
     </row>
     <row r="265">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Forest and Brush Fires</t>
+          <t>Navajo Indians</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E265" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0253</v>
       </c>
       <c r="F265" t="n">
-        <v>91.90000000000001</v>
+        <v>319.8</v>
       </c>
     </row>
     <row r="266">
@@ -6416,43 +6416,39 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Unidentified Flying Objects (UFO)</t>
+          <t>Treasure Troves</t>
         </is>
       </c>
       <c r="D266" t="n">
+        <v>4</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F266" t="n">
+        <v>202.9</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Manhattan Project</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
         <v>5</v>
       </c>
-      <c r="E266" s="2" t="n">
+      <c r="E267" s="2" t="n">
         <v>0.005699999999999999</v>
       </c>
-      <c r="F266" t="n">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Subways</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>2913</v>
-      </c>
-      <c r="E267" s="2" t="n">
-        <v>0.0242</v>
-      </c>
       <c r="F267" t="n">
-        <v>11.9</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="268">
@@ -6464,17 +6460,17 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Lotteries</t>
+          <t>Plague</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>2201</v>
+        <v>4</v>
       </c>
       <c r="E268" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.0046</v>
       </c>
       <c r="F268" t="n">
-        <v>11.2</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="269">
@@ -6486,17 +6482,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Taxicabs and Taxicab Drivers</t>
+          <t>Forest and Brush Fires</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>750</v>
+        <v>25</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0287</v>
       </c>
       <c r="F269" t="n">
-        <v>9.5</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -6508,21 +6504,25 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Transit Systems</t>
+          <t>Unidentified Flying Objects (UFO)</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>3005</v>
+        <v>5</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.025</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F270" t="n">
-        <v>9.300000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr"/>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -6530,17 +6530,17 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Fires and Firemen</t>
+          <t>Subways</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>778</v>
+        <v>2913</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0242</v>
       </c>
       <c r="F271" t="n">
-        <v>8.699999999999999</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="272">
@@ -6552,17 +6552,17 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Buses</t>
+          <t>Lotteries</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>981</v>
+        <v>2201</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0183</v>
       </c>
       <c r="F272" t="n">
-        <v>8.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="273">
@@ -6574,131 +6574,131 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>World Trade Center (NYC)</t>
+          <t>Taxicabs and Taxicab Drivers</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>6688</v>
+        <v>750</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>0.0556</v>
+        <v>0.0062</v>
       </c>
       <c r="F273" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
-        </is>
-      </c>
+      <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Hurricane Florence (2018)</t>
+          <t>Transit Systems</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>42</v>
+        <v>3005</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.025</v>
       </c>
       <c r="F274" t="n">
-        <v>457.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Isabel (Storm)</t>
+          <t>Fires and Firemen</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>12</v>
+        <v>778</v>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F275" t="n">
-        <v>307.2</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Hurricane Helene (2024)</t>
+          <t>Buses</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>57</v>
+        <v>981</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.027</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F276" t="n">
-        <v>299.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>World Trade Center (NYC)</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>6688</v>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="F277" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Hurricane Dorian (2019)</t>
-        </is>
-      </c>
-      <c r="D277" t="n">
-        <v>10</v>
-      </c>
-      <c r="E277" s="2" t="n">
-        <v>0.004699999999999999</v>
-      </c>
-      <c r="F277" t="n">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr"/>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Hurricane Irene (2011)</t>
+          <t>Hurricane Florence (2018)</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E278" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0199</v>
       </c>
       <c r="F278" t="n">
-        <v>53</v>
+        <v>457.6</v>
       </c>
     </row>
     <row r="279">
@@ -6710,113 +6710,109 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Voting Rights Act (1965)</t>
+          <t>Isabel (Storm)</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E279" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F279" t="n">
-        <v>35.1</v>
+        <v>307.2</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Bathrooms and Toilets</t>
+          <t>Hurricane Helene (2024)</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.027</v>
       </c>
       <c r="F280" t="n">
-        <v>39.6</v>
+        <v>299.3</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Democratic National Convention</t>
+          <t>Hurricane Dorian (2019)</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E281" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F281" t="n">
-        <v>33.7</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Lacrosse</t>
+          <t>Hurricane Irene (2011)</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E282" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F282" t="n">
-        <v>32.3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Voter Registration and Requirements</t>
+          <t>Voting Rights Act (1965)</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E283" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F283" t="n">
-        <v>30.7</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>North Dakota</t>
-        </is>
-      </c>
+      <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -6824,17 +6820,17 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Spirit Lake Tribe (Sioux)</t>
+          <t>Bathrooms and Toilets</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="E284" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="F284" t="n">
-        <v>4159.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="285">
@@ -6846,17 +6842,17 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Pipelines</t>
+          <t>Democratic National Convention</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0161</v>
       </c>
       <c r="F285" t="n">
-        <v>134.9</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="286">
@@ -6868,17 +6864,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Oil Spills</t>
+          <t>Lacrosse</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E286" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0062</v>
       </c>
       <c r="F286" t="n">
-        <v>115.5</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="287">
@@ -6890,17 +6886,17 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Native Americans</t>
+          <t>Voter Registration and Requirements</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0.1298</v>
+        <v>0.0279</v>
       </c>
       <c r="F287" t="n">
-        <v>96.7</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="288">
@@ -6912,21 +6908,25 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Levees and Dams</t>
+          <t>Hurricanes and Tropical Storms</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="E288" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0492</v>
       </c>
       <c r="F288" t="n">
-        <v>93.3</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr"/>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -6934,17 +6934,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Navajo Indians</t>
+          <t>Spirit Lake Tribe (Sioux)</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E289" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F289" t="n">
-        <v>91.2</v>
+        <v>4159.4</v>
       </c>
     </row>
     <row r="290">
@@ -6956,65 +6956,61 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Keystone Pipeline System</t>
+          <t>Pipelines</t>
         </is>
       </c>
       <c r="D290" t="n">
+        <v>32</v>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>0.07690000000000001</v>
+      </c>
+      <c r="F290" t="n">
+        <v>134.9</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Oil Spills</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
         <v>4</v>
       </c>
-      <c r="E290" s="2" t="n">
+      <c r="E291" s="2" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="F290" t="n">
-        <v>73.2</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>East Palestine, Ohio, Train Derailment (Feb 3, 2023)</t>
-        </is>
-      </c>
-      <c r="D291" t="n">
-        <v>30</v>
-      </c>
-      <c r="E291" s="2" t="n">
-        <v>0.012</v>
-      </c>
       <c r="F291" t="n">
-        <v>439.2</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Dayton, Ohio, Shooting (2019)</t>
+          <t>Native Americans</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.1298</v>
       </c>
       <c r="F292" t="n">
-        <v>252.5</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="293">
@@ -7026,17 +7022,17 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Amish</t>
+          <t>Levees and Dams</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0264</v>
       </c>
       <c r="F293" t="n">
-        <v>132.9</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="294">
@@ -7048,17 +7044,17 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Haitian-Americans</t>
+          <t>Navajo Indians</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v>0.0128</v>
+        <v>0.0072</v>
       </c>
       <c r="F294" t="n">
-        <v>117.1</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="295">
@@ -7070,61 +7066,65 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Registration of Voters</t>
+          <t>Keystone Pipeline System</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E295" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F295" t="n">
-        <v>66.09999999999999</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr"/>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Republican National Convention</t>
+          <t>East Palestine, Ohio, Train Derailment (Feb 3, 2023)</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="E296" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.012</v>
       </c>
       <c r="F296" t="n">
-        <v>42.3</v>
+        <v>439.2</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Railroad Accidents and Safety</t>
+          <t>Dayton, Ohio, Shooting (2019)</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E297" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.0076</v>
       </c>
       <c r="F297" t="n">
-        <v>32.6</v>
+        <v>252.5</v>
       </c>
     </row>
     <row r="298">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Vouchers</t>
+          <t>Amish</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -7146,7 +7146,7 @@
         <v>0.0072</v>
       </c>
       <c r="F298" t="n">
-        <v>31.2</v>
+        <v>132.9</v>
       </c>
     </row>
     <row r="299">
@@ -7158,43 +7158,39 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Blackouts and Brownouts (Electrical)</t>
+          <t>Haitian-Americans</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E299" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="F299" t="n">
-        <v>23</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
+      <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Tulsa Race Riot (1921)</t>
+          <t>Registration of Voters</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0064</v>
       </c>
       <c r="F300" t="n">
-        <v>909.3</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -7206,17 +7202,17 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Murrah, Alfred P, Federal Building (Oklahoma City, Okla)</t>
+          <t>Republican National Convention</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0216</v>
       </c>
       <c r="F301" t="n">
-        <v>1409.3</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="302">
@@ -7228,17 +7224,17 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Cherokee Indians</t>
+          <t>Railroad Accidents and Safety</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="F302" t="n">
-        <v>328.1</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="303">
@@ -7250,17 +7246,17 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Vouchers</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0.0765</v>
+        <v>0.0072</v>
       </c>
       <c r="F303" t="n">
-        <v>204.2</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="304">
@@ -7272,39 +7268,43 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Juneteenth</t>
+          <t>Blackouts and Brownouts (Electrical)</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F304" t="n">
-        <v>196.1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr"/>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Sedatives</t>
+          <t>Tulsa Race Riot (1921)</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0261</v>
       </c>
       <c r="F305" t="n">
-        <v>129</v>
+        <v>909.3</v>
       </c>
     </row>
     <row r="306">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Capital Punishment</t>
+          <t>Murrah, Alfred P, Federal Building (Oklahoma City, Okla)</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>0.1182</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F306" t="n">
-        <v>66.8</v>
+        <v>1409.3</v>
       </c>
     </row>
     <row r="307">
@@ -7338,43 +7338,39 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Hydraulic Fracturing</t>
+          <t>Cherokee Indians</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F307" t="n">
-        <v>37.8</v>
+        <v>328.1</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
+      <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>George Floyd Protests (2020)</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>0.0489</v>
+        <v>0.0765</v>
       </c>
       <c r="F308" t="n">
-        <v>62.1</v>
+        <v>204.2</v>
       </c>
     </row>
     <row r="309">
@@ -7386,17 +7382,17 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Suckerfish</t>
+          <t>Juneteenth</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.0104</v>
       </c>
       <c r="F309" t="n">
-        <v>873.2</v>
+        <v>196.1</v>
       </c>
     </row>
     <row r="310">
@@ -7408,17 +7404,17 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Antifa Movement (US)</t>
+          <t>Sedatives</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0061</v>
       </c>
       <c r="F310" t="n">
-        <v>278.4</v>
+        <v>129</v>
       </c>
     </row>
     <row r="311">
@@ -7430,17 +7426,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Federal Lands</t>
+          <t>Capital Punishment</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.1182</v>
       </c>
       <c r="F311" t="n">
-        <v>167.8</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="312">
@@ -7452,39 +7448,43 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Federal Actions in US Cities</t>
+          <t>Hydraulic Fracturing</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0104</v>
       </c>
       <c r="F312" t="n">
-        <v>156.2</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr"/>
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Wildlife Sanctuaries and Nature Reserves</t>
+          <t>George Floyd Protests (2020)</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0489</v>
       </c>
       <c r="F313" t="n">
-        <v>128.5</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="314">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Suckerfish</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0044</v>
       </c>
       <c r="F314" t="n">
-        <v>113.3</v>
+        <v>873.2</v>
       </c>
     </row>
     <row r="315">
@@ -7518,65 +7518,61 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Irrigation</t>
+          <t>Antifa Movement (US)</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E315" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0089</v>
       </c>
       <c r="F315" t="n">
-        <v>78.09999999999999</v>
+        <v>278.4</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
+      <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Trump Assassination Attempt (July 2024)</t>
+          <t>Federal Lands</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0259</v>
       </c>
       <c r="F316" t="n">
-        <v>240.7</v>
+        <v>167.8</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, Shooting (2018)</t>
+          <t>Federal Actions in US Cities</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0207</v>
       </c>
       <c r="F317" t="n">
-        <v>185.3</v>
+        <v>156.2</v>
       </c>
     </row>
     <row r="318">
@@ -7588,17 +7584,17 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Hazing</t>
+          <t>Wildlife Sanctuaries and Nature Reserves</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F318" t="n">
-        <v>74</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="319">
@@ -7610,17 +7606,17 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Railroad Accidents and Safety</t>
+          <t>Salmon</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E319" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0237</v>
       </c>
       <c r="F319" t="n">
-        <v>45.8</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="320">
@@ -7632,61 +7628,65 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Fraternities and Sororities</t>
+          <t>Irrigation</t>
         </is>
       </c>
       <c r="D320" t="n">
+        <v>14</v>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="F320" t="n">
+        <v>78.09999999999999</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Headline event</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Trump Assassination Attempt (July 2024)</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
         <v>21</v>
       </c>
-      <c r="E320" s="2" t="n">
+      <c r="E321" s="2" t="n">
         <v>0.0058</v>
       </c>
-      <c r="F320" t="n">
-        <v>37.7</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr"/>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Democratic National Convention</t>
-        </is>
-      </c>
-      <c r="D321" t="n">
-        <v>59</v>
-      </c>
-      <c r="E321" s="2" t="n">
-        <v>0.0163</v>
-      </c>
       <c r="F321" t="n">
-        <v>34.1</v>
+        <v>240.7</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Fugitives</t>
+          <t>Pittsburgh, PA, Shooting (2018)</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E322" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0102</v>
       </c>
       <c r="F322" t="n">
-        <v>33</v>
+        <v>185.3</v>
       </c>
     </row>
     <row r="323">
@@ -7698,17 +7698,17 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Prison Escapes</t>
+          <t>Hazing</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E323" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0105</v>
       </c>
       <c r="F323" t="n">
-        <v>27.3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="324">
@@ -7720,65 +7720,61 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Electoral College</t>
+          <t>Railroad Accidents and Safety</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0152</v>
       </c>
       <c r="F324" t="n">
-        <v>19.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
+      <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brown University Shooting (Dec 13, 2025)</t>
+          <t>Fraternities and Sororities</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.0058</v>
       </c>
       <c r="F325" t="n">
-        <v>2359.8</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Hurricane Henri (2021)</t>
+          <t>Democratic National Convention</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0163</v>
       </c>
       <c r="F326" t="n">
-        <v>717.4</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="327">
@@ -7790,17 +7786,17 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Narragansett Indians</t>
+          <t>Fugitives</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0.0083</v>
       </c>
       <c r="F327" t="n">
-        <v>3586.9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="328">
@@ -7812,17 +7808,17 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Fireworks</t>
+          <t>Prison Escapes</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="F328" t="n">
-        <v>294.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="329">
@@ -7834,61 +7830,65 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Paints and Painting</t>
+          <t>Electoral College</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E329" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.005</v>
       </c>
       <c r="F329" t="n">
-        <v>103.7</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr"/>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Burns</t>
+          <t>Brown University Shooting (Dec 13, 2025)</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E330" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0415</v>
       </c>
       <c r="F330" t="n">
-        <v>92.8</v>
+        <v>2359.8</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Habeas Corpus</t>
+          <t>Hurricane Henri (2021)</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E331" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0066</v>
       </c>
       <c r="F331" t="n">
-        <v>66.40000000000001</v>
+        <v>717.4</v>
       </c>
     </row>
     <row r="332">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Fugitives</t>
+          <t>Narragansett Indians</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0083</v>
       </c>
       <c r="F332" t="n">
-        <v>66.2</v>
+        <v>3586.9</v>
       </c>
     </row>
     <row r="333">
@@ -7922,87 +7922,83 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Bars and Nightclubs</t>
+          <t>Fireworks</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>0.0929</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F333" t="n">
-        <v>56.4</v>
+        <v>294.4</v>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
-        </is>
-      </c>
+      <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Charleston, SC, Shooting (2015)</t>
+          <t>Paints and Painting</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="E334" s="2" t="n">
-        <v>0.0541</v>
+        <v>0.0083</v>
       </c>
       <c r="F334" t="n">
-        <v>521.9</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Hurricane Florence (2018)</t>
+          <t>Burns</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E335" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.005</v>
       </c>
       <c r="F335" t="n">
-        <v>350.5</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Presidential Election of 2012</t>
+          <t>Habeas Corpus</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>187</v>
+        <v>3</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0.0919</v>
+        <v>0.005</v>
       </c>
       <c r="F336" t="n">
-        <v>25.8</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="337">
@@ -8014,17 +8010,17 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Flags, Emblems and Insignia</t>
+          <t>Fugitives</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>0.0472</v>
+        <v>0.0166</v>
       </c>
       <c r="F337" t="n">
-        <v>117.8</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="338">
@@ -8036,83 +8032,87 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Plutonium</t>
+          <t>Bars and Nightclubs</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E338" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.0929</v>
       </c>
       <c r="F338" t="n">
-        <v>80.7</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr"/>
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Nuclear Wastes</t>
+          <t>Charleston, SC, Shooting (2015)</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E339" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0541</v>
       </c>
       <c r="F339" t="n">
-        <v>58.4</v>
+        <v>521.9</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Primaries and Caucuses</t>
+          <t>Hurricane Florence (2018)</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>453</v>
+        <v>31</v>
       </c>
       <c r="E340" s="2" t="n">
-        <v>0.2226</v>
+        <v>0.0152</v>
       </c>
       <c r="F340" t="n">
-        <v>41.9</v>
+        <v>350.5</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Political Advertising</t>
+          <t>Presidential Election of 2012</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="E341" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0919</v>
       </c>
       <c r="F341" t="n">
-        <v>22.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="342">
@@ -8124,17 +8124,17 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Adultery</t>
+          <t>Flags, Emblems and Insignia</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E342" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0472</v>
       </c>
       <c r="F342" t="n">
-        <v>22.5</v>
+        <v>117.8</v>
       </c>
     </row>
     <row r="343">
@@ -8146,25 +8146,21 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Hate Crimes</t>
+          <t>Plutonium</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E343" s="2" t="n">
-        <v>0.0177</v>
+        <v>0.0059</v>
       </c>
       <c r="F343" t="n">
-        <v>19</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
+      <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -8172,17 +8168,17 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Sioux Indians</t>
+          <t>Nuclear Wastes</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E344" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0118</v>
       </c>
       <c r="F344" t="n">
-        <v>2746.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="345">
@@ -8194,17 +8190,17 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Lakota Indians</t>
+          <t>Primaries and Caucuses</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>3</v>
+        <v>453</v>
       </c>
       <c r="E345" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.2226</v>
       </c>
       <c r="F345" t="n">
-        <v>2403.2</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="346">
@@ -8216,17 +8212,17 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>budgets_and_budgeting</t>
+          <t>Political Advertising</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="E346" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0393</v>
       </c>
       <c r="F346" t="n">
-        <v>1802.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="347">
@@ -8238,17 +8234,17 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Oglala Sioux Indians</t>
+          <t>Adultery</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E347" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F347" t="n">
-        <v>1762.3</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="348">
@@ -8260,21 +8256,25 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>health_insurance</t>
+          <t>Hate Crimes</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E348" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0177</v>
       </c>
       <c r="F348" t="n">
-        <v>1310.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr"/>
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -8282,17 +8282,17 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Neutrinos</t>
+          <t>Sioux Indians</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E349" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0089</v>
       </c>
       <c r="F349" t="n">
-        <v>313.5</v>
+        <v>2746.5</v>
       </c>
     </row>
     <row r="350">
@@ -8304,109 +8304,105 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Bison</t>
+          <t>Lakota Indians</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E350" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0067</v>
       </c>
       <c r="F350" t="n">
-        <v>186.7</v>
+        <v>2403.2</v>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
+      <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Tennessee Ammunition Plant Explosion (Oct 2025)</t>
+          <t>budgets_and_budgeting</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E351" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0067</v>
       </c>
       <c r="F351" t="n">
-        <v>1628.7</v>
+        <v>1802.4</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Nashville, Tenn, Explosion (2020)</t>
+          <t>Oglala Sioux Indians</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E352" s="2" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0244</v>
       </c>
       <c r="F352" t="n">
-        <v>1396</v>
+        <v>1762.3</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Covenant School, Nashville, Tenn, Shooting (2023)</t>
+          <t>health_insurance</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E353" s="2" t="n">
-        <v>0.0188</v>
+        <v>0.0067</v>
       </c>
       <c r="F353" t="n">
-        <v>866.3</v>
+        <v>1310.8</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Hurricane Helene (2024)</t>
+          <t>Neutrinos</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E354" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0067</v>
       </c>
       <c r="F354" t="n">
-        <v>83.5</v>
+        <v>313.5</v>
       </c>
     </row>
     <row r="355">
@@ -8418,105 +8414,109 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Drag (Performance)</t>
+          <t>Bison</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E355" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0089</v>
       </c>
       <c r="F355" t="n">
-        <v>165.2</v>
+        <v>186.7</v>
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr"/>
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Tennessee Ammunition Plant Explosion (Oct 2025)</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="E356" s="2" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="F356" t="n">
-        <v>86.5</v>
+        <v>1628.7</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Cold and Cold Spells</t>
+          <t>Nashville, Tenn, Explosion (2020)</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E357" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F357" t="n">
-        <v>51.1</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Federal Actions in US Cities</t>
+          <t>Covenant School, Nashville, Tenn, Shooting (2023)</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E358" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0188</v>
       </c>
       <c r="F358" t="n">
-        <v>45.4</v>
+        <v>866.3</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>School Shootings and Armed Attacks</t>
+          <t>Hurricane Helene (2024)</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E359" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0075</v>
       </c>
       <c r="F359" t="n">
-        <v>28.4</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="360">
@@ -8528,109 +8528,105 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Fugitives</t>
+          <t>Drag (Performance)</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E360" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0053</v>
       </c>
       <c r="F360" t="n">
-        <v>27</v>
+        <v>165.2</v>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
+      <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Central Texas Floods (July 2025)</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E361" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="F361" t="n">
-        <v>162.4</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Uvalde, Tex, Shooting (May 24, 2022)</t>
+          <t>Cold and Cold Spells</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="E362" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0053</v>
       </c>
       <c r="F362" t="n">
-        <v>114.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Hurricane Harvey (2017)</t>
+          <t>Federal Actions in US Cities</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="E363" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.006</v>
       </c>
       <c r="F363" t="n">
-        <v>111.4</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>El Paso, Tex, Shooting (2019)</t>
+          <t>School Shootings and Armed Attacks</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E364" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0166</v>
       </c>
       <c r="F364" t="n">
-        <v>81.09999999999999</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="365">
@@ -8642,105 +8638,109 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Hurricane Ike</t>
+          <t>Fugitives</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E365" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0068</v>
       </c>
       <c r="F365" t="n">
-        <v>146.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr"/>
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Border Barriers</t>
+          <t>Central Texas Floods (July 2025)</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="E366" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0073</v>
       </c>
       <c r="F366" t="n">
-        <v>27.1</v>
+        <v>162.4</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Immigration Detention</t>
+          <t>Uvalde, Tex, Shooting (May 24, 2022)</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="E367" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0132</v>
       </c>
       <c r="F367" t="n">
-        <v>23.7</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Hurricane Harvey (2017)</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E368" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0165</v>
       </c>
       <c r="F368" t="n">
-        <v>23.1</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Mass Shootings</t>
+          <t>El Paso, Tex, Shooting (2019)</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="E369" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F369" t="n">
-        <v>22.7</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="370">
@@ -8752,43 +8752,39 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Power Failures and Blackouts</t>
+          <t>Hurricane Ike</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E370" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0052</v>
       </c>
       <c r="F370" t="n">
-        <v>20.9</v>
+        <v>146.1</v>
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
+      <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Olympic Games (2002)</t>
+          <t>Border Barriers</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="E371" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0104</v>
       </c>
       <c r="F371" t="n">
-        <v>135.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="372">
@@ -8800,17 +8796,17 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Polygamy</t>
+          <t>Immigration Detention</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="E372" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0187</v>
       </c>
       <c r="F372" t="n">
-        <v>434.1</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="373">
@@ -8822,17 +8818,17 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Fundamentalist Church of Jesus Christ of Latter-day Saints</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E373" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F373" t="n">
-        <v>388.5</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="374">
@@ -8844,17 +8840,17 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mormons (Church of Jesus Christ of Latter-Day Saints)</t>
+          <t>Mass Shootings</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E374" s="2" t="n">
-        <v>0.0915</v>
+        <v>0.0109</v>
       </c>
       <c r="F374" t="n">
-        <v>365.9</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="375">
@@ -8866,39 +8862,43 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Residence Requirements</t>
+          <t>Power Failures and Blackouts</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="E375" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0086</v>
       </c>
       <c r="F375" t="n">
-        <v>162.4</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr"/>
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Federal Lands</t>
+          <t>Olympic Games (2002)</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E376" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0318</v>
       </c>
       <c r="F376" t="n">
-        <v>99.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="377">
@@ -8910,17 +8910,17 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Navajo Indians</t>
+          <t>Polygamy</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E377" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.0289</v>
       </c>
       <c r="F377" t="n">
-        <v>97.5</v>
+        <v>434.1</v>
       </c>
     </row>
     <row r="378">
@@ -8932,43 +8932,39 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Public Property</t>
+          <t>Fundamentalist Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E378" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0106</v>
       </c>
       <c r="F378" t="n">
-        <v>87.3</v>
+        <v>388.5</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Vermont</t>
-        </is>
-      </c>
+      <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Hurricane Irene (2011)</t>
+          <t>Mormons (Church of Jesus Christ of Latter-Day Saints)</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="E379" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.0915</v>
       </c>
       <c r="F379" t="n">
-        <v>299.3</v>
+        <v>365.9</v>
       </c>
     </row>
     <row r="380">
@@ -8980,17 +8976,17 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Green Cards (US)</t>
+          <t>Residence Requirements</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E380" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0058</v>
       </c>
       <c r="F380" t="n">
-        <v>257.2</v>
+        <v>162.4</v>
       </c>
     </row>
     <row r="381">
@@ -9002,17 +8998,17 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Maple Syrup and Sugar</t>
+          <t>Federal Lands</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E381" s="2" t="n">
-        <v>0.0048</v>
+        <v>0.0154</v>
       </c>
       <c r="F381" t="n">
-        <v>140.7</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="382">
@@ -9024,17 +9020,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Heroin</t>
+          <t>Navajo Indians</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E382" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0077</v>
       </c>
       <c r="F382" t="n">
-        <v>61</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="383">
@@ -9046,39 +9042,43 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Euthanasia and Assisted Suicide</t>
+          <t>Public Property</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E383" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0067</v>
       </c>
       <c r="F383" t="n">
-        <v>53.2</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr"/>
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Foreign Students (in US)</t>
+          <t>Hurricane Irene (2011)</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E384" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0321</v>
       </c>
       <c r="F384" t="n">
-        <v>49.1</v>
+        <v>299.3</v>
       </c>
     </row>
     <row r="385">
@@ -9090,17 +9090,17 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Executive Privilege, Doctrine of</t>
+          <t>Green Cards (US)</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E385" s="2" t="n">
-        <v>0.0048</v>
+        <v>0.0064</v>
       </c>
       <c r="F385" t="n">
-        <v>43.6</v>
+        <v>257.2</v>
       </c>
     </row>
     <row r="386">
@@ -9112,65 +9112,61 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Pro-Palestinian Campus Protests (2023- )</t>
+          <t>Maple Syrup and Sugar</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0048</v>
       </c>
       <c r="F386" t="n">
-        <v>29.7</v>
+        <v>140.7</v>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
+      <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, Shooting (2019)</t>
+          <t>Heroin</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E387" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.0144</v>
       </c>
       <c r="F387" t="n">
-        <v>660.5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, Violence (August, 2017)</t>
+          <t>Euthanasia and Assisted Suicide</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="E388" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0064</v>
       </c>
       <c r="F388" t="n">
-        <v>226.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="389">
@@ -9182,17 +9178,17 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Serial Murders</t>
+          <t>Foreign Students (in US)</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>248</v>
+        <v>6</v>
       </c>
       <c r="E389" s="2" t="n">
-        <v>0.101</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F389" t="n">
-        <v>230.4</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="390">
@@ -9204,17 +9200,17 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Gifts to Public Officials</t>
+          <t>Executive Privilege, Doctrine of</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E390" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0048</v>
       </c>
       <c r="F390" t="n">
-        <v>93.09999999999999</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="391">
@@ -9226,61 +9222,65 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Neo Nazi Groups</t>
+          <t>Pro-Palestinian Campus Protests (2023- )</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E391" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0064</v>
       </c>
       <c r="F391" t="n">
-        <v>38.7</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr"/>
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Whites</t>
+          <t>Virginia Beach, VA, Shooting (2019)</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E392" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0049</v>
       </c>
       <c r="F392" t="n">
-        <v>36.3</v>
+        <v>660.5</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Confessions</t>
+          <t>Charlottesville, VA, Violence (August, 2017)</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="E393" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.0375</v>
       </c>
       <c r="F393" t="n">
-        <v>25.8</v>
+        <v>226.3</v>
       </c>
     </row>
     <row r="394">
@@ -9292,17 +9292,17 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Fringe Groups and Movements</t>
+          <t>Serial Murders</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>56</v>
+        <v>248</v>
       </c>
       <c r="E394" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.101</v>
       </c>
       <c r="F394" t="n">
-        <v>25.5</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="395">
@@ -9314,25 +9314,21 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Civil War (US) (1861-65)</t>
+          <t>Gifts to Public Officials</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E395" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.0106</v>
       </c>
       <c r="F395" t="n">
-        <v>20</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
+      <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -9340,17 +9336,17 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Hanford Nuclear Reservation (Wash)</t>
+          <t>Neo Nazi Groups</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E396" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0069</v>
       </c>
       <c r="F396" t="n">
-        <v>507.1</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="397">
@@ -9362,17 +9358,17 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Hornets (Insects)</t>
+          <t>Whites</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E397" s="2" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0163</v>
       </c>
       <c r="F397" t="n">
-        <v>446</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="398">
@@ -9384,17 +9380,17 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Landslides and Mudslides</t>
+          <t>Confessions</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E398" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0049</v>
       </c>
       <c r="F398" t="n">
-        <v>87.7</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="399">
@@ -9406,17 +9402,17 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Mad Cow Disease (Bovine Spongiform Encephalopathy)</t>
+          <t>Fringe Groups and Movements</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E399" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0228</v>
       </c>
       <c r="F399" t="n">
-        <v>87</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="400">
@@ -9428,21 +9424,25 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Livestock Diseases</t>
+          <t>Civil War (US) (1861-65)</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E400" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0171</v>
       </c>
       <c r="F400" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr"/>
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -9450,17 +9450,17 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Hanford Nuclear Reservation (Wash)</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E401" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F401" t="n">
-        <v>56</v>
+        <v>507.1</v>
       </c>
     </row>
     <row r="402">
@@ -9472,65 +9472,61 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Serial Murders</t>
+          <t>Hornets (Insects)</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E402" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F402" t="n">
-        <v>47</v>
+        <v>446</v>
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>West Virginia</t>
-        </is>
-      </c>
+      <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Washington DC National Guard Shooting (Nov 2025)</t>
+          <t>Landslides and Mudslides</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="E403" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0251</v>
       </c>
       <c r="F403" t="n">
-        <v>308.8</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>American Families Plan (2021)</t>
+          <t>Mad Cow Disease (Bovine Spongiform Encephalopathy)</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E404" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0145</v>
       </c>
       <c r="F404" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="405">
@@ -9542,17 +9538,17 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Strip Mining</t>
+          <t>Livestock Diseases</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E405" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0089</v>
       </c>
       <c r="F405" t="n">
-        <v>694.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="406">
@@ -9564,17 +9560,17 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mountaintop Removal Mining</t>
+          <t>Salmon</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0117</v>
       </c>
       <c r="F406" t="n">
-        <v>294.8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="407">
@@ -9586,61 +9582,65 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Mines and Mining</t>
+          <t>Serial Murders</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="E407" s="2" t="n">
-        <v>0.1619</v>
+        <v>0.0206</v>
       </c>
       <c r="F407" t="n">
-        <v>145.7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr"/>
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Washington DC National Guard Shooting (Nov 2025)</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="E408" s="2" t="n">
-        <v>0.1274</v>
+        <v>0.006</v>
       </c>
       <c r="F408" t="n">
-        <v>143.8</v>
+        <v>308.8</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Missing in Action</t>
+          <t>American Families Plan (2021)</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E409" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0075</v>
       </c>
       <c r="F409" t="n">
-        <v>109</v>
+        <v>73</v>
       </c>
     </row>
     <row r="410">
@@ -9652,17 +9652,17 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Explosions (Accidental)</t>
+          <t>Strip Mining</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E410" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F410" t="n">
-        <v>88.7</v>
+        <v>694.9</v>
       </c>
     </row>
     <row r="411">
@@ -9674,65 +9674,61 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Explosions</t>
+          <t>Mountaintop Removal Mining</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E411" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.006</v>
       </c>
       <c r="F411" t="n">
-        <v>68.90000000000001</v>
+        <v>294.8</v>
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
+      <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Waukesha, Wis, Holiday Parade Attack (2021)</t>
+          <t>Mines and Mining</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="E412" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.1619</v>
       </c>
       <c r="F412" t="n">
-        <v>788.3</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Oak Creek, Wis, Shooting (2012)</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="E413" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.1274</v>
       </c>
       <c r="F413" t="n">
-        <v>436.7</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="414">
@@ -9744,17 +9740,17 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Collective Bargaining</t>
+          <t>Missing in Action</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E414" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.006</v>
       </c>
       <c r="F414" t="n">
-        <v>97.3</v>
+        <v>109</v>
       </c>
     </row>
     <row r="415">
@@ -9766,17 +9762,17 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Self-Defense</t>
+          <t>Explosions (Accidental)</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E415" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0165</v>
       </c>
       <c r="F415" t="n">
-        <v>74.59999999999999</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="416">
@@ -9788,61 +9784,65 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Sikhs and Sikhism</t>
+          <t>Explosions</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E416" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0255</v>
       </c>
       <c r="F416" t="n">
-        <v>73.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr"/>
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Project Democracy</t>
+          <t>Waukesha, Wis, Holiday Parade Attack (2021)</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E417" s="2" t="n">
-        <v>0.005</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F417" t="n">
-        <v>66.40000000000001</v>
+        <v>788.3</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Republican National Convention</t>
+          <t>Oak Creek, Wis, Shooting (2012)</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E418" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F418" t="n">
-        <v>36.1</v>
+        <v>436.7</v>
       </c>
     </row>
     <row r="419">
@@ -9854,17 +9854,17 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Deer</t>
+          <t>Collective Bargaining</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E419" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0224</v>
       </c>
       <c r="F419" t="n">
-        <v>32.6</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="420">
@@ -9876,25 +9876,21 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Voter Fraud (Election Fraud)</t>
+          <t>Self-Defense</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E420" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F420" t="n">
-        <v>27.8</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
+      <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -9902,17 +9898,17 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Treasure Troves</t>
+          <t>Sikhs and Sikhism</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E421" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F421" t="n">
-        <v>345.7</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="422">
@@ -9924,17 +9920,17 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Elk</t>
+          <t>Project Democracy</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E422" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.005</v>
       </c>
       <c r="F422" t="n">
-        <v>327.4</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="423">
@@ -9946,17 +9942,17 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Republican National Convention</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E423" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0184</v>
       </c>
       <c r="F423" t="n">
-        <v>247.3</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="424">
@@ -9968,17 +9964,17 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Snowmobiles</t>
+          <t>Deer</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E424" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.005</v>
       </c>
       <c r="F424" t="n">
-        <v>207.6</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="425">
@@ -9990,39 +9986,43 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Bison</t>
+          <t>Voter Fraud (Election Fraud)</t>
         </is>
       </c>
       <c r="D425" t="n">
+        <v>38</v>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F425" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Treasure Troves</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
         <v>3</v>
       </c>
-      <c r="E425" s="2" t="n">
+      <c r="E426" s="2" t="n">
         <v>0.007800000000000001</v>
       </c>
-      <c r="F425" t="n">
-        <v>164.5</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr"/>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>Ranches</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>7</v>
-      </c>
-      <c r="E426" s="2" t="n">
-        <v>0.0183</v>
-      </c>
       <c r="F426" t="n">
-        <v>153.2</v>
+        <v>345.7</v>
       </c>
     </row>
     <row r="427">
@@ -10034,21 +10034,131 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
+          <t>Elk</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>4</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="F427" t="n">
+        <v>327.4</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr"/>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Wolves</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>12</v>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F428" t="n">
+        <v>247.3</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Snowmobiles</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>5</v>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F429" t="n">
+        <v>207.6</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr"/>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Bison</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>3</v>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F430" t="n">
+        <v>164.5</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr"/>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Ranches</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>7</v>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F431" t="n">
+        <v>153.2</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr"/>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
           <t>National Parks, Monuments and Seashores</t>
         </is>
       </c>
-      <c r="D427" t="n">
+      <c r="D432" t="n">
         <v>25</v>
       </c>
-      <c r="E427" s="2" t="n">
+      <c r="E432" s="2" t="n">
         <v>0.0653</v>
       </c>
-      <c r="F427" t="n">
+      <c r="F432" t="n">
         <v>84.5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E427">
+  <conditionalFormatting sqref="E2:E432">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10058,7 +10168,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F427">
+  <conditionalFormatting sqref="F2:F432">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10475,13 +10585,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>122.2</v>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>58.2</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.0297</v>
@@ -10784,16 +10894,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>886.8</v>
       </c>
       <c r="D20" t="n">
-        <v>311.2</v>
+        <v>106.1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.1894</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0.0049</v>
@@ -11299,16 +11409,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
         <v>39.6</v>
       </c>
       <c r="D35" t="n">
-        <v>30.7</v>
+        <v>27.6</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0492</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>0.0062</v>

--- a/state_keywords_analysis.xlsx
+++ b/state_keywords_analysis.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F432"/>
+  <dimension ref="A1:F434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0098</v>
       </c>
       <c r="F2" t="n">
-        <v>531.8</v>
+        <v>473.2</v>
       </c>
     </row>
     <row r="3">
@@ -513,10 +513,10 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>305.3</v>
+        <v>310.4</v>
       </c>
     </row>
     <row r="4">
@@ -535,10 +535,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1709.4</v>
+        <v>1738.3</v>
       </c>
     </row>
     <row r="5">
@@ -557,10 +557,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.0138</v>
+        <v>0.0141</v>
       </c>
       <c r="F5" t="n">
-        <v>575.3</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6">
@@ -579,10 +579,10 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0155</v>
       </c>
       <c r="F6" t="n">
-        <v>522.3</v>
+        <v>531.1</v>
       </c>
     </row>
     <row r="7">
@@ -601,10 +601,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="F7" t="n">
-        <v>345.2</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8">
@@ -623,10 +623,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
       <c r="F8" t="n">
-        <v>240.7</v>
+        <v>244.8</v>
       </c>
     </row>
     <row r="9">
@@ -645,10 +645,10 @@
         <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="F9" t="n">
-        <v>224.4</v>
+        <v>228.2</v>
       </c>
     </row>
     <row r="10">
@@ -667,10 +667,10 @@
         <v>20</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0281</v>
       </c>
       <c r="F10" t="n">
-        <v>160</v>
+        <v>162.7</v>
       </c>
     </row>
     <row r="11">
@@ -693,10 +693,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0173</v>
       </c>
       <c r="F11" t="n">
-        <v>1065.5</v>
+        <v>1070.1</v>
       </c>
     </row>
     <row r="12">
@@ -708,17 +708,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Caribou</t>
+          <t>Alaska Natives</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0303</v>
       </c>
       <c r="F12" t="n">
-        <v>1331.8</v>
+        <v>601.3</v>
       </c>
     </row>
     <row r="13">
@@ -730,17 +730,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reindeer</t>
+          <t>Moose</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.013</v>
       </c>
       <c r="F13" t="n">
-        <v>608</v>
+        <v>460.5</v>
       </c>
     </row>
     <row r="14">
@@ -752,17 +752,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alaska Natives</t>
+          <t>Avalanches</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.0302</v>
+        <v>0.0433</v>
       </c>
       <c r="F14" t="n">
-        <v>598.7</v>
+        <v>390.1</v>
       </c>
     </row>
     <row r="15">
@@ -774,17 +774,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Moose</t>
+          <t>Tankers</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.013</v>
       </c>
       <c r="F15" t="n">
-        <v>458.5</v>
+        <v>292.6</v>
       </c>
     </row>
     <row r="16">
@@ -796,17 +796,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avalanches</t>
+          <t>Logging Industry</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.0433</v>
       </c>
       <c r="F16" t="n">
-        <v>388.4</v>
+        <v>234.7</v>
       </c>
     </row>
     <row r="17">
@@ -818,17 +818,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tankers</t>
+          <t>Glaciers</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0346</v>
       </c>
       <c r="F17" t="n">
-        <v>291.3</v>
+        <v>215.2</v>
       </c>
     </row>
     <row r="18">
@@ -840,17 +840,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Logging Industry</t>
+          <t>Bears</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.039</v>
       </c>
       <c r="F18" t="n">
-        <v>233.7</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="19">
@@ -873,10 +873,10 @@
         <v>66</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.0489</v>
+        <v>0.0491</v>
       </c>
       <c r="F19" t="n">
-        <v>403.9</v>
+        <v>405.7</v>
       </c>
     </row>
     <row r="20">
@@ -895,10 +895,10 @@
         <v>6</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>310.3</v>
+        <v>311.7</v>
       </c>
     </row>
     <row r="21">
@@ -920,7 +920,7 @@
         <v>0.008199999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>113.1</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="22">
@@ -942,7 +942,7 @@
         <v>0.0089</v>
       </c>
       <c r="F22" t="n">
-        <v>112.5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
@@ -964,7 +964,7 @@
         <v>0.0067</v>
       </c>
       <c r="F23" t="n">
-        <v>102.3</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="24">
@@ -983,10 +983,10 @@
         <v>8</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="F24" t="n">
-        <v>79.2</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="25">
@@ -1005,10 +1005,10 @@
         <v>63</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.0467</v>
+        <v>0.0469</v>
       </c>
       <c r="F25" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hit-and-Run Drivers</t>
+          <t>Border Barriers</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.0179</v>
       </c>
       <c r="F26" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="27">
@@ -1211,10 +1211,10 @@
         <v>217</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="F34" t="n">
-        <v>82.7</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0135</v>
       </c>
       <c r="F35" t="n">
-        <v>83.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1255,10 +1255,10 @@
         <v>683</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.0496</v>
+        <v>0.0503</v>
       </c>
       <c r="F36" t="n">
-        <v>41.2</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="37">
@@ -1277,10 +1277,10 @@
         <v>151</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.011</v>
+        <v>0.0111</v>
       </c>
       <c r="F37" t="n">
-        <v>35.1</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="38">
@@ -1299,10 +1299,10 @@
         <v>226</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0166</v>
       </c>
       <c r="F38" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="39">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>0.0052</v>
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.0436</v>
+        <v>0.0441</v>
       </c>
       <c r="F40" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="41">
@@ -1365,10 +1365,10 @@
         <v>160</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0118</v>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="42">
@@ -1391,10 +1391,10 @@
         <v>21</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0091</v>
       </c>
       <c r="F42" t="n">
-        <v>610.8</v>
+        <v>617.9</v>
       </c>
     </row>
     <row r="43">
@@ -1413,10 +1413,10 @@
         <v>22</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>511.9</v>
+        <v>517.9</v>
       </c>
     </row>
     <row r="44">
@@ -1435,10 +1435,10 @@
         <v>65</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0283</v>
       </c>
       <c r="F44" t="n">
-        <v>371.1</v>
+        <v>375.5</v>
       </c>
     </row>
     <row r="45">
@@ -1457,10 +1457,10 @@
         <v>31</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0135</v>
       </c>
       <c r="F45" t="n">
-        <v>88.8</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="46">
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0218</v>
       </c>
       <c r="F46" t="n">
-        <v>73</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1504,7 +1504,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>46.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="48">
@@ -1523,10 +1523,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="F48" t="n">
-        <v>42.7</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="49">
@@ -1545,10 +1545,10 @@
         <v>34</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0148</v>
       </c>
       <c r="F49" t="n">
-        <v>30.5</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="50">
@@ -1567,10 +1567,10 @@
         <v>66</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0287</v>
       </c>
       <c r="F50" t="n">
-        <v>30.2</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="51">
@@ -1589,10 +1589,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>28.1</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="52">
@@ -1615,10 +1615,10 @@
         <v>139</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.0127</v>
+        <v>0.015</v>
       </c>
       <c r="F52" t="n">
-        <v>38.1</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="53">
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2097</v>
+        <v>552</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.1916</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>117.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="54">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0147</v>
       </c>
       <c r="F54" t="n">
-        <v>15.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="55">
@@ -1681,10 +1681,10 @@
         <v>304</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.0278</v>
+        <v>0.0329</v>
       </c>
       <c r="F55" t="n">
-        <v>14.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="56">
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.0122</v>
+        <v>0.0142</v>
       </c>
       <c r="F56" t="n">
-        <v>10.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="57">
@@ -1725,10 +1725,10 @@
         <v>100</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0108</v>
       </c>
       <c r="F57" t="n">
-        <v>9.6</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="58">
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0074</v>
       </c>
       <c r="F58" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="59">
@@ -1769,10 +1769,10 @@
         <v>67</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0073</v>
       </c>
       <c r="F59" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="60">
@@ -1795,10 +1795,10 @@
         <v>73</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0108</v>
       </c>
       <c r="F60" t="n">
-        <v>186.1</v>
+        <v>193.3</v>
       </c>
     </row>
     <row r="61">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1888</v>
+        <v>1802</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.2693</v>
+        <v>0.267</v>
       </c>
       <c r="F61" t="n">
-        <v>123.3</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="62">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.0205</v>
+        <v>0.0204</v>
       </c>
       <c r="F62" t="n">
-        <v>97.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4064</v>
+        <v>3842</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.5797</v>
+        <v>0.5692</v>
       </c>
       <c r="F63" t="n">
-        <v>93</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="64">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Missing Persons</t>
+          <t>National Mall (Washington, DC)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1167</v>
+        <v>34</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.1665</v>
+        <v>0.005</v>
       </c>
       <c r="F64" t="n">
-        <v>83.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>World Trade Center (NYC)</t>
+          <t>Missing Persons</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4036</v>
+        <v>1106</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.5757</v>
+        <v>0.1639</v>
       </c>
       <c r="F65" t="n">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1920,17 +1920,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serial Murders</t>
+          <t>World Trade Center (NYC)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>245</v>
+        <v>3814</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.035</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>79.7</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1953,10 +1953,10 @@
         <v>35</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.0959</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="68">
@@ -1975,10 +1975,10 @@
         <v>3</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="F68" t="n">
-        <v>38.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="69">
@@ -1997,10 +1997,10 @@
         <v>5</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0138</v>
       </c>
       <c r="F69" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
@@ -2019,10 +2019,10 @@
         <v>44</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.1205</v>
+        <v>0.1215</v>
       </c>
       <c r="F70" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="71">
@@ -2041,10 +2041,10 @@
         <v>5</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0138</v>
       </c>
       <c r="F71" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
@@ -2063,10 +2063,10 @@
         <v>8</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.0221</v>
       </c>
       <c r="F72" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="73">
@@ -2085,10 +2085,10 @@
         <v>5</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0138</v>
       </c>
       <c r="F73" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="74">
@@ -2110,7 +2110,7 @@
         <v>0.011</v>
       </c>
       <c r="F74" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="75">
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0064</v>
       </c>
       <c r="F75" t="n">
-        <v>229.3</v>
+        <v>228.4</v>
       </c>
     </row>
     <row r="76">
@@ -2155,10 +2155,10 @@
         <v>79</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0113</v>
       </c>
       <c r="F76" t="n">
-        <v>214.5</v>
+        <v>218.3</v>
       </c>
     </row>
     <row r="77">
@@ -2177,10 +2177,10 @@
         <v>71</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.01</v>
+        <v>0.0102</v>
       </c>
       <c r="F77" t="n">
-        <v>177</v>
+        <v>180.2</v>
       </c>
     </row>
     <row r="78">
@@ -2199,10 +2199,10 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0054</v>
       </c>
       <c r="F78" t="n">
-        <v>156.2</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79">
@@ -2221,10 +2221,10 @@
         <v>65</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>103.5</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="80">
@@ -2243,10 +2243,10 @@
         <v>133</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.019</v>
       </c>
       <c r="F80" t="n">
-        <v>90.3</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -2265,10 +2265,10 @@
         <v>73</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.0104</v>
       </c>
       <c r="F81" t="n">
-        <v>79.90000000000001</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="82">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.0291</v>
       </c>
       <c r="F82" t="n">
-        <v>122.2</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="83">
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0109</v>
       </c>
       <c r="F83" t="n">
-        <v>81.59999999999999</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="84">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cuba-International Relations-US</t>
+          <t>Self-Defense</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.0067</v>
       </c>
       <c r="F84" t="n">
-        <v>76</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="85">
@@ -2346,17 +2346,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Self-Defense</t>
+          <t>Registration of Voters</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0052</v>
       </c>
       <c r="F85" t="n">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="86">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Registration of Voters</t>
+          <t>Child Custody and Support</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0198</v>
       </c>
       <c r="F86" t="n">
-        <v>58.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87">
@@ -2401,10 +2401,10 @@
         <v>24</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0073</v>
       </c>
       <c r="F87" t="n">
-        <v>501.8</v>
+        <v>507.7</v>
       </c>
     </row>
     <row r="88">
@@ -2423,10 +2423,10 @@
         <v>152</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.0455</v>
+        <v>0.0461</v>
       </c>
       <c r="F88" t="n">
-        <v>336.2</v>
+        <v>340.2</v>
       </c>
     </row>
     <row r="89">
@@ -2445,10 +2445,10 @@
         <v>32</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0097</v>
       </c>
       <c r="F89" t="n">
-        <v>265.9</v>
+        <v>269.1</v>
       </c>
     </row>
     <row r="90">
@@ -2467,10 +2467,10 @@
         <v>22</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0067</v>
       </c>
       <c r="F90" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="91">
@@ -2489,10 +2489,10 @@
         <v>440</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.1319</v>
+        <v>0.1334</v>
       </c>
       <c r="F91" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="92">
@@ -2511,10 +2511,10 @@
         <v>204</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.0611</v>
+        <v>0.0619</v>
       </c>
       <c r="F92" t="n">
-        <v>90.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -2533,10 +2533,10 @@
         <v>51</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0155</v>
       </c>
       <c r="F93" t="n">
-        <v>38.5</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="94">
@@ -2555,10 +2555,10 @@
         <v>33</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F94" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="95">
@@ -2577,10 +2577,10 @@
         <v>77</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0233</v>
       </c>
       <c r="F95" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="96">
@@ -2599,10 +2599,10 @@
         <v>28</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="97">
@@ -2628,7 +2628,7 @@
         <v>0.0043</v>
       </c>
       <c r="F97" t="n">
-        <v>3085.4</v>
+        <v>3125.5</v>
       </c>
     </row>
     <row r="98">
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>1487.6</v>
+        <v>1451.1</v>
       </c>
     </row>
     <row r="99">
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0434</v>
       </c>
       <c r="F99" t="n">
-        <v>1410.5</v>
+        <v>1339.5</v>
       </c>
     </row>
     <row r="100">
@@ -2691,10 +2691,10 @@
         <v>14</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0202</v>
       </c>
       <c r="F100" t="n">
-        <v>981.7</v>
+        <v>994.5</v>
       </c>
     </row>
     <row r="101">
@@ -2713,10 +2713,10 @@
         <v>8</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0116</v>
       </c>
       <c r="F101" t="n">
-        <v>602</v>
+        <v>609.9</v>
       </c>
     </row>
     <row r="102">
@@ -2735,10 +2735,10 @@
         <v>4</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="F102" t="n">
-        <v>457.1</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.0471</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F103" t="n">
-        <v>393.1</v>
+        <v>374.1</v>
       </c>
     </row>
     <row r="104">
@@ -2783,10 +2783,10 @@
         <v>3</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
       <c r="F104" t="n">
-        <v>2510.1</v>
+        <v>2534.6</v>
       </c>
     </row>
     <row r="105">
@@ -2805,10 +2805,10 @@
         <v>13</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0254</v>
       </c>
       <c r="F105" t="n">
-        <v>198.5</v>
+        <v>200.4</v>
       </c>
     </row>
     <row r="106">
@@ -2827,10 +2827,10 @@
         <v>4</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F106" t="n">
-        <v>148.1</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="107">
@@ -2849,10 +2849,10 @@
         <v>3</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
       <c r="F107" t="n">
-        <v>106.4</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="108">
@@ -2871,10 +2871,10 @@
         <v>10</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0195</v>
       </c>
       <c r="F108" t="n">
-        <v>95.7</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="109">
@@ -2893,10 +2893,10 @@
         <v>8</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0156</v>
       </c>
       <c r="F109" t="n">
-        <v>83.90000000000001</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="110">
@@ -2915,10 +2915,10 @@
         <v>7</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.0137</v>
       </c>
       <c r="F110" t="n">
-        <v>79.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -2941,10 +2941,10 @@
         <v>21</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="F111" t="n">
-        <v>373.5</v>
+        <v>377.5</v>
       </c>
     </row>
     <row r="112">
@@ -2963,10 +2963,10 @@
         <v>62</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0149</v>
       </c>
       <c r="F112" t="n">
-        <v>111.4</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="113">
@@ -2985,10 +2985,10 @@
         <v>55</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0133</v>
       </c>
       <c r="F113" t="n">
-        <v>27.5</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="114">
@@ -3007,10 +3007,10 @@
         <v>40</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="115">
@@ -3029,10 +3029,10 @@
         <v>52</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.0124</v>
+        <v>0.0125</v>
       </c>
       <c r="F115" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="116">
@@ -3054,7 +3054,7 @@
         <v>0.005500000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
@@ -3076,7 +3076,7 @@
         <v>0.0067</v>
       </c>
       <c r="F117" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="118">
@@ -3095,10 +3095,10 @@
         <v>206</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.0491</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="F118" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="119">
@@ -3121,10 +3121,10 @@
         <v>9</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0098</v>
       </c>
       <c r="F119" t="n">
-        <v>1389.4</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="120">
@@ -3143,10 +3143,10 @@
         <v>6</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>496.2</v>
+        <v>502.1</v>
       </c>
     </row>
     <row r="121">
@@ -3168,7 +3168,7 @@
         <v>0.0043</v>
       </c>
       <c r="F121" t="n">
-        <v>96.5</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -3187,10 +3187,10 @@
         <v>7</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0076</v>
       </c>
       <c r="F122" t="n">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="123">
@@ -3209,10 +3209,10 @@
         <v>8</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>88.2</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="124">
@@ -3234,7 +3234,7 @@
         <v>0.0043</v>
       </c>
       <c r="F124" t="n">
-        <v>77.8</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="125">
@@ -3253,10 +3253,10 @@
         <v>20</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0217</v>
       </c>
       <c r="F125" t="n">
-        <v>57.2</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="126">
@@ -3275,10 +3275,10 @@
         <v>20</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0217</v>
       </c>
       <c r="F126" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="127">
@@ -3301,10 +3301,10 @@
         <v>469</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.1665</v>
+        <v>0.1672</v>
       </c>
       <c r="F127" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="128">
@@ -3323,10 +3323,10 @@
         <v>539</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.1914</v>
+        <v>0.1922</v>
       </c>
       <c r="F128" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="129">
@@ -3342,13 +3342,13 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.0824</v>
+        <v>0.08130000000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="130">
@@ -3367,10 +3367,10 @@
         <v>212</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="F130" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="131">
@@ -3392,7 +3392,7 @@
         <v>0.0075</v>
       </c>
       <c r="F131" t="n">
-        <v>135.5</v>
+        <v>136.1</v>
       </c>
     </row>
     <row r="132">
@@ -3411,10 +3411,10 @@
         <v>840</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.2983</v>
+        <v>0.2995</v>
       </c>
       <c r="F132" t="n">
-        <v>56.2</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="133">
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.0558</v>
+        <v>0.0556</v>
       </c>
       <c r="F133" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="134">
@@ -3458,7 +3458,7 @@
         <v>0.005</v>
       </c>
       <c r="F134" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="135">
@@ -3480,7 +3480,7 @@
         <v>0.0107</v>
       </c>
       <c r="F135" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="136">
@@ -3499,10 +3499,10 @@
         <v>65</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0232</v>
       </c>
       <c r="F136" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="137">
@@ -3525,10 +3525,10 @@
         <v>4</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0054</v>
       </c>
       <c r="F137" t="n">
-        <v>338.8</v>
+        <v>341.1</v>
       </c>
     </row>
     <row r="138">
@@ -3547,10 +3547,10 @@
         <v>7</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>221.5</v>
+        <v>223</v>
       </c>
     </row>
     <row r="139">
@@ -3572,7 +3572,7 @@
         <v>0.004</v>
       </c>
       <c r="F139" t="n">
-        <v>200.9</v>
+        <v>202.3</v>
       </c>
     </row>
     <row r="140">
@@ -3594,7 +3594,7 @@
         <v>0.004</v>
       </c>
       <c r="F140" t="n">
-        <v>169.4</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="141">
@@ -3613,10 +3613,10 @@
         <v>4</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0054</v>
       </c>
       <c r="F141" t="n">
-        <v>145.8</v>
+        <v>146.8</v>
       </c>
     </row>
     <row r="142">
@@ -3638,7 +3638,7 @@
         <v>0.004</v>
       </c>
       <c r="F142" t="n">
-        <v>130.9</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="143">
@@ -3657,10 +3657,10 @@
         <v>29</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0389</v>
       </c>
       <c r="F143" t="n">
-        <v>103.1</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="144">
@@ -3686,7 +3686,7 @@
         <v>0.004500000000000001</v>
       </c>
       <c r="F144" t="n">
-        <v>1626.7</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="145">
@@ -3705,10 +3705,10 @@
         <v>26</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0237</v>
       </c>
       <c r="F145" t="n">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="146">
@@ -3727,10 +3727,10 @@
         <v>11</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F146" t="n">
-        <v>286.3</v>
+        <v>288.6</v>
       </c>
     </row>
     <row r="147">
@@ -3749,10 +3749,10 @@
         <v>7</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="F147" t="n">
-        <v>157.1</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="148">
@@ -3771,10 +3771,10 @@
         <v>53</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.0478</v>
+        <v>0.0482</v>
       </c>
       <c r="F148" t="n">
-        <v>127.7</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="149">
@@ -3796,7 +3796,7 @@
         <v>0.004500000000000001</v>
       </c>
       <c r="F149" t="n">
-        <v>56.1</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="150">
@@ -3815,10 +3815,10 @@
         <v>40</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.0361</v>
+        <v>0.0364</v>
       </c>
       <c r="F150" t="n">
-        <v>54.6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151">
@@ -3837,10 +3837,10 @@
         <v>8</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0073</v>
       </c>
       <c r="F151" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152">
@@ -3856,13 +3856,13 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0282</v>
       </c>
       <c r="F152" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="153">
@@ -3885,10 +3885,10 @@
         <v>30</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="F153" t="n">
-        <v>566</v>
+        <v>571.4</v>
       </c>
     </row>
     <row r="154">
@@ -3907,10 +3907,10 @@
         <v>29</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.012</v>
       </c>
       <c r="F154" t="n">
-        <v>524.8</v>
+        <v>529.8</v>
       </c>
     </row>
     <row r="155">
@@ -3929,10 +3929,10 @@
         <v>21</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F155" t="n">
-        <v>423.2</v>
+        <v>427.3</v>
       </c>
     </row>
     <row r="156">
@@ -3954,7 +3954,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F156" t="n">
-        <v>295.6</v>
+        <v>298.4</v>
       </c>
     </row>
     <row r="157">
@@ -3970,13 +3970,13 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.2927</v>
+        <v>0.2889</v>
       </c>
       <c r="F157" t="n">
-        <v>275.8</v>
+        <v>272.2</v>
       </c>
     </row>
     <row r="158">
@@ -3998,7 +3998,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F158" t="n">
-        <v>264.5</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159">
@@ -4017,10 +4017,10 @@
         <v>39</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.016</v>
+        <v>0.0161</v>
       </c>
       <c r="F159" t="n">
-        <v>230.6</v>
+        <v>232.8</v>
       </c>
     </row>
     <row r="160">
@@ -4039,10 +4039,10 @@
         <v>12</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="F160" t="n">
-        <v>886.8</v>
+        <v>895.2</v>
       </c>
     </row>
     <row r="161">
@@ -4061,10 +4061,10 @@
         <v>28</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0116</v>
       </c>
       <c r="F161" t="n">
-        <v>636.7</v>
+        <v>642.7</v>
       </c>
     </row>
     <row r="162">
@@ -4083,10 +4083,10 @@
         <v>40</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0166</v>
       </c>
       <c r="F162" t="n">
-        <v>311.2</v>
+        <v>314.1</v>
       </c>
     </row>
     <row r="163">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0137</v>
       </c>
       <c r="F163" t="n">
-        <v>109.2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164">
@@ -4124,13 +4124,13 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.1894</v>
+        <v>0.1842</v>
       </c>
       <c r="F164" t="n">
-        <v>106.1</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="165">
@@ -4153,10 +4153,10 @@
         <v>40</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.0503</v>
+        <v>0.0509</v>
       </c>
       <c r="F165" t="n">
-        <v>2133.8</v>
+        <v>2158.2</v>
       </c>
     </row>
     <row r="166">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0216</v>
       </c>
       <c r="F166" t="n">
-        <v>191.3</v>
+        <v>182.7</v>
       </c>
     </row>
     <row r="167">
@@ -4197,10 +4197,10 @@
         <v>5</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="F167" t="n">
-        <v>78.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="168">
@@ -4219,10 +4219,10 @@
         <v>4</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="F168" t="n">
-        <v>77.2</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -4241,10 +4241,10 @@
         <v>8</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.0101</v>
+        <v>0.0102</v>
       </c>
       <c r="F169" t="n">
-        <v>67</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="170">
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0344</v>
       </c>
       <c r="F170" t="n">
-        <v>53.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="171">
@@ -4285,10 +4285,10 @@
         <v>4</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="F171" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="172">
@@ -4307,10 +4307,10 @@
         <v>5</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="F172" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="173">
@@ -4330,13 +4330,13 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.1275</v>
+        <v>0.1224</v>
       </c>
       <c r="F173" t="n">
-        <v>290.9</v>
+        <v>279.3</v>
       </c>
     </row>
     <row r="174">
@@ -4355,10 +4355,10 @@
         <v>21</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.011</v>
       </c>
       <c r="F174" t="n">
-        <v>41.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="175">
@@ -4377,10 +4377,10 @@
         <v>40</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.021</v>
       </c>
       <c r="F175" t="n">
-        <v>40.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="176">
@@ -4396,13 +4396,13 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0179</v>
       </c>
       <c r="F176" t="n">
-        <v>36.7</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="177">
@@ -4421,10 +4421,10 @@
         <v>14</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="F177" t="n">
-        <v>33</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="178">
@@ -4443,10 +4443,10 @@
         <v>49</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0257</v>
       </c>
       <c r="F178" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="179">
@@ -4465,10 +4465,10 @@
         <v>10</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="F179" t="n">
-        <v>27.2</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="180">
@@ -4491,10 +4491,10 @@
         <v>142</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0452</v>
       </c>
       <c r="F180" t="n">
-        <v>228.5</v>
+        <v>232.3</v>
       </c>
     </row>
     <row r="181">
@@ -4510,13 +4510,13 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0048</v>
       </c>
       <c r="F181" t="n">
-        <v>264.4</v>
+        <v>251.9</v>
       </c>
     </row>
     <row r="182">
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.0717</v>
+        <v>0.0707</v>
       </c>
       <c r="F182" t="n">
-        <v>59</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="183">
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="F183" t="n">
-        <v>42.3</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="184">
@@ -4582,7 +4582,7 @@
         <v>0.006</v>
       </c>
       <c r="F184" t="n">
-        <v>34.8</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="185">
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.022</v>
       </c>
       <c r="F185" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="186">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>0.0216</v>
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.0717</v>
+        <v>0.0707</v>
       </c>
       <c r="F187" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="188">
@@ -4671,10 +4671,10 @@
         <v>32</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0121</v>
       </c>
       <c r="F188" t="n">
-        <v>506.2</v>
+        <v>511.9</v>
       </c>
     </row>
     <row r="189">
@@ -4690,13 +4690,13 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0234</v>
       </c>
       <c r="F189" t="n">
-        <v>146.9</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="190">
@@ -4715,10 +4715,10 @@
         <v>97</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
       <c r="F190" t="n">
-        <v>144.4</v>
+        <v>146</v>
       </c>
     </row>
     <row r="191">
@@ -4737,10 +4737,10 @@
         <v>33</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="F191" t="n">
-        <v>35.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="192">
@@ -4759,10 +4759,10 @@
         <v>60</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.0226</v>
       </c>
       <c r="F192" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="193">
@@ -4781,10 +4781,10 @@
         <v>98</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F193" t="n">
-        <v>32.4</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="194">
@@ -4803,10 +4803,10 @@
         <v>17</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="F194" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="195">
@@ -4825,10 +4825,10 @@
         <v>93</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0351</v>
       </c>
       <c r="F195" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196">
@@ -4851,10 +4851,10 @@
         <v>38</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.0226</v>
       </c>
       <c r="F196" t="n">
-        <v>969.8</v>
+        <v>979.6</v>
       </c>
     </row>
     <row r="197">
@@ -4873,10 +4873,10 @@
         <v>8</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="F197" t="n">
-        <v>680.5</v>
+        <v>687.4</v>
       </c>
     </row>
     <row r="198">
@@ -4895,10 +4895,10 @@
         <v>163</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="F198" t="n">
-        <v>122.3</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="199">
@@ -4917,10 +4917,10 @@
         <v>35</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0209</v>
       </c>
       <c r="F199" t="n">
-        <v>565.3</v>
+        <v>571.1</v>
       </c>
     </row>
     <row r="200">
@@ -4939,10 +4939,10 @@
         <v>56</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0334</v>
       </c>
       <c r="F200" t="n">
-        <v>249</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="201">
@@ -4961,10 +4961,10 @@
         <v>10</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="F201" t="n">
-        <v>116</v>
+        <v>117.2</v>
       </c>
     </row>
     <row r="202">
@@ -4983,10 +4983,10 @@
         <v>31</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.0185</v>
       </c>
       <c r="F202" t="n">
-        <v>100.4</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="203">
@@ -5005,10 +5005,10 @@
         <v>89</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.0525</v>
+        <v>0.053</v>
       </c>
       <c r="F203" t="n">
-        <v>79.40000000000001</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="204">
@@ -5027,10 +5027,10 @@
         <v>10</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="F204" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="205">
@@ -5049,10 +5049,10 @@
         <v>331</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>0.1953</v>
+        <v>0.1973</v>
       </c>
       <c r="F205" t="n">
-        <v>47</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="206">
@@ -5072,13 +5072,13 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F206" t="n">
-        <v>423.4</v>
+        <v>392.4</v>
       </c>
     </row>
     <row r="207">
@@ -5100,7 +5100,7 @@
         <v>0.0063</v>
       </c>
       <c r="F207" t="n">
-        <v>307.9</v>
+        <v>311.4</v>
       </c>
     </row>
     <row r="208">
@@ -5116,13 +5116,13 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.0799</v>
+        <v>0.0776</v>
       </c>
       <c r="F208" t="n">
-        <v>75.2</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="209">
@@ -5141,10 +5141,10 @@
         <v>18</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.0143</v>
       </c>
       <c r="F209" t="n">
-        <v>175.2</v>
+        <v>177.2</v>
       </c>
     </row>
     <row r="210">
@@ -5163,10 +5163,10 @@
         <v>57</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0451</v>
       </c>
       <c r="F210" t="n">
-        <v>119.2</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="211">
@@ -5185,10 +5185,10 @@
         <v>9</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0071</v>
       </c>
       <c r="F211" t="n">
-        <v>89.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -5200,17 +5200,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Flags, Emblems and Insignia</t>
+          <t>Appeals Courts</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0048</v>
       </c>
       <c r="F212" t="n">
-        <v>56.7</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="213">
@@ -5222,17 +5222,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Appeals Courts</t>
+          <t>Flags, Emblems and Insignia</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0222</v>
       </c>
       <c r="F213" t="n">
-        <v>56.5</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="214">
@@ -5251,10 +5251,10 @@
         <v>29</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.023</v>
       </c>
       <c r="F214" t="n">
-        <v>53.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="215">
@@ -5276,7 +5276,7 @@
         <v>0.005500000000000001</v>
       </c>
       <c r="F215" t="n">
-        <v>51.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="216">
@@ -5302,7 +5302,7 @@
         <v>0.0072</v>
       </c>
       <c r="F216" t="n">
-        <v>910.8</v>
+        <v>916.8</v>
       </c>
     </row>
     <row r="217">
@@ -5321,10 +5321,10 @@
         <v>74</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="F217" t="n">
-        <v>108.8</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="218">
@@ -5346,7 +5346,7 @@
         <v>0.0061</v>
       </c>
       <c r="F218" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="219">
@@ -5365,10 +5365,10 @@
         <v>371</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>0.2043</v>
+        <v>0.2057</v>
       </c>
       <c r="F219" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="220">
@@ -5390,7 +5390,7 @@
         <v>0.0105</v>
       </c>
       <c r="F220" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="221">
@@ -5412,7 +5412,7 @@
         <v>0.005</v>
       </c>
       <c r="F221" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="222">
@@ -5434,7 +5434,7 @@
         <v>0.009399999999999999</v>
       </c>
       <c r="F222" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="223">
@@ -5456,7 +5456,7 @@
         <v>0.0083</v>
       </c>
       <c r="F223" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="224">
@@ -5479,10 +5479,10 @@
         <v>3</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0046</v>
       </c>
       <c r="F224" t="n">
-        <v>1398.1</v>
+        <v>1408.7</v>
       </c>
     </row>
     <row r="225">
@@ -5501,10 +5501,10 @@
         <v>3</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0046</v>
       </c>
       <c r="F225" t="n">
-        <v>815.6</v>
+        <v>821.8</v>
       </c>
     </row>
     <row r="226">
@@ -5523,10 +5523,10 @@
         <v>11</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0167</v>
       </c>
       <c r="F226" t="n">
-        <v>348.4</v>
+        <v>351</v>
       </c>
     </row>
     <row r="227">
@@ -5545,10 +5545,10 @@
         <v>6</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0091</v>
       </c>
       <c r="F227" t="n">
-        <v>225</v>
+        <v>226.7</v>
       </c>
     </row>
     <row r="228">
@@ -5567,10 +5567,10 @@
         <v>13</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0198</v>
       </c>
       <c r="F228" t="n">
-        <v>154.8</v>
+        <v>156</v>
       </c>
     </row>
     <row r="229">
@@ -5589,10 +5589,10 @@
         <v>16</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>0.0241</v>
+        <v>0.0243</v>
       </c>
       <c r="F229" t="n">
-        <v>127.9</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="230">
@@ -5611,10 +5611,10 @@
         <v>10</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0152</v>
       </c>
       <c r="F230" t="n">
-        <v>96.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="231">
@@ -5637,10 +5637,10 @@
         <v>16</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0281</v>
       </c>
       <c r="F231" t="n">
-        <v>212.3</v>
+        <v>214.2</v>
       </c>
     </row>
     <row r="232">
@@ -5659,10 +5659,10 @@
         <v>8</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0141</v>
       </c>
       <c r="F232" t="n">
-        <v>165.6</v>
+        <v>167.1</v>
       </c>
     </row>
     <row r="233">
@@ -5684,7 +5684,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F233" t="n">
-        <v>83.7</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="234">
@@ -5703,10 +5703,10 @@
         <v>3</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="F234" t="n">
-        <v>71.09999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="235">
@@ -5725,10 +5725,10 @@
         <v>10</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0176</v>
       </c>
       <c r="F235" t="n">
-        <v>68.5</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -5750,7 +5750,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F236" t="n">
-        <v>54.2</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="237">
@@ -5769,10 +5769,10 @@
         <v>3</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="F237" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="238">
@@ -5795,10 +5795,10 @@
         <v>54</v>
       </c>
       <c r="E238" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.033</v>
       </c>
       <c r="F238" t="n">
-        <v>343.2</v>
+        <v>346.8</v>
       </c>
     </row>
     <row r="239">
@@ -5817,10 +5817,10 @@
         <v>14</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="F239" t="n">
-        <v>197.1</v>
+        <v>199.1</v>
       </c>
     </row>
     <row r="240">
@@ -5836,13 +5836,13 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.033</v>
       </c>
       <c r="F240" t="n">
-        <v>164.8</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="241">
@@ -5861,10 +5861,10 @@
         <v>13</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="F241" t="n">
-        <v>70.90000000000001</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="242">
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0.046</v>
+        <v>0.0453</v>
       </c>
       <c r="F242" t="n">
-        <v>63.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="243">
@@ -5908,7 +5908,7 @@
         <v>0.0067</v>
       </c>
       <c r="F243" t="n">
-        <v>43.1</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="244">
@@ -5927,10 +5927,10 @@
         <v>9</v>
       </c>
       <c r="E244" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F244" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="245">
@@ -5946,13 +5946,13 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E245" s="2" t="n">
-        <v>0.0309</v>
+        <v>0.03</v>
       </c>
       <c r="F245" t="n">
-        <v>27.1</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="246">
@@ -5975,10 +5975,10 @@
         <v>297</v>
       </c>
       <c r="E246" s="2" t="n">
-        <v>0.1459</v>
+        <v>0.1467</v>
       </c>
       <c r="F246" t="n">
-        <v>41</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="247">
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E247" s="2" t="n">
-        <v>0.09140000000000001</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F247" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="248">
@@ -6019,10 +6019,10 @@
         <v>397</v>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.1951</v>
+        <v>0.1961</v>
       </c>
       <c r="F248" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="249">
@@ -6038,13 +6038,13 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0.0565</v>
+        <v>0.0558</v>
       </c>
       <c r="F249" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="250">
@@ -6063,10 +6063,10 @@
         <v>137</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0.0673</v>
+        <v>0.0677</v>
       </c>
       <c r="F250" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="251">
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0.3174</v>
+        <v>0.3182</v>
       </c>
       <c r="F251" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="252">
@@ -6107,10 +6107,10 @@
         <v>116</v>
       </c>
       <c r="E252" s="2" t="n">
-        <v>0.057</v>
+        <v>0.0573</v>
       </c>
       <c r="F252" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="253">
@@ -6129,10 +6129,10 @@
         <v>56</v>
       </c>
       <c r="E253" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0277</v>
       </c>
       <c r="F253" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="254">
@@ -6151,10 +6151,10 @@
         <v>78</v>
       </c>
       <c r="E254" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0385</v>
       </c>
       <c r="F254" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="255">
@@ -6173,10 +6173,10 @@
         <v>24</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0119</v>
       </c>
       <c r="F255" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="256">
@@ -6199,10 +6199,10 @@
         <v>213</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0106</v>
       </c>
       <c r="F256" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257">
@@ -6214,17 +6214,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Lotteries</t>
+          <t>Tolls</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>2125</v>
+        <v>165</v>
       </c>
       <c r="E257" s="2" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F257" t="n">
-        <v>59.5</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="258">
@@ -6236,17 +6236,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Tolls</t>
+          <t>Lotteries</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>169</v>
+        <v>580</v>
       </c>
       <c r="E258" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.029</v>
       </c>
       <c r="F258" t="n">
-        <v>25.9</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="259">
@@ -6265,10 +6265,10 @@
         <v>234</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.0107</v>
+        <v>0.0117</v>
       </c>
       <c r="F259" t="n">
-        <v>14.7</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="260">
@@ -6284,13 +6284,13 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="F260" t="n">
-        <v>14.5</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="261">
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.01</v>
+        <v>0.0108</v>
       </c>
       <c r="F261" t="n">
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="262">
@@ -6328,13 +6328,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E262" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="F262" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="263">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.0372</v>
       </c>
       <c r="F263" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="264">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Cockfighting</t>
+          <t>Navajo Indians</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.0257</v>
       </c>
       <c r="F264" t="n">
-        <v>320.8</v>
+        <v>325.5</v>
       </c>
     </row>
     <row r="265">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Navajo Indians</t>
+          <t>Treasure Troves</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E265" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F265" t="n">
-        <v>319.8</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="266">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Treasure Troves</t>
+          <t>Manhattan Project</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E266" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.0058</v>
       </c>
       <c r="F266" t="n">
-        <v>202.9</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="267">
@@ -6438,17 +6438,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Manhattan Project</t>
+          <t>Plague</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F267" t="n">
-        <v>144.5</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="268">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Plague</t>
+          <t>Forest and Brush Fires</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E268" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.0281</v>
       </c>
       <c r="F268" t="n">
-        <v>106.9</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="269">
@@ -6482,17 +6482,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Forest and Brush Fires</t>
+          <t>Unidentified Flying Objects (UFO)</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0058</v>
       </c>
       <c r="F269" t="n">
-        <v>91.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Unidentified Flying Objects (UFO)</t>
+          <t>Nuclear Wastes</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0175</v>
       </c>
       <c r="F270" t="n">
-        <v>87.5</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="271">
@@ -6525,22 +6525,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Subways</t>
+          <t>Hurricane Sandy (2012)</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>2913</v>
+        <v>677</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.0058</v>
       </c>
       <c r="F271" t="n">
-        <v>11.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="272">
@@ -6552,17 +6552,17 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Lotteries</t>
+          <t>Subways</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2201</v>
+        <v>2864</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.0246</v>
       </c>
       <c r="F272" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="273">
@@ -6578,13 +6578,13 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0064</v>
       </c>
       <c r="F273" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>3005</v>
+        <v>2928</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0251</v>
       </c>
       <c r="F274" t="n">
         <v>9.300000000000001</v>
@@ -6622,13 +6622,13 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="E275" s="2" t="n">
         <v>0.006500000000000001</v>
       </c>
       <c r="F275" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -6644,13 +6644,13 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="F276" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -6666,61 +6666,61 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>6688</v>
+        <v>6336</v>
       </c>
       <c r="E277" s="2" t="n">
-        <v>0.0556</v>
+        <v>0.0544</v>
       </c>
       <c r="F277" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Hijacking</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>5564</v>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="F278" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>North Carolina</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>Hurricane Florence (2018)</t>
         </is>
       </c>
-      <c r="D278" t="n">
+      <c r="D279" t="n">
         <v>42</v>
       </c>
-      <c r="E278" s="2" t="n">
-        <v>0.0199</v>
-      </c>
-      <c r="F278" t="n">
-        <v>457.6</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr"/>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Isabel (Storm)</t>
-        </is>
-      </c>
-      <c r="D279" t="n">
-        <v>12</v>
-      </c>
       <c r="E279" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="F279" t="n">
-        <v>307.2</v>
+        <v>460.6</v>
       </c>
     </row>
     <row r="280">
@@ -6739,10 +6739,10 @@
         <v>57</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>0.027</v>
+        <v>0.0272</v>
       </c>
       <c r="F280" t="n">
-        <v>299.3</v>
+        <v>301.3</v>
       </c>
     </row>
     <row r="281">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Hurricane Dorian (2019)</t>
+          <t>Isabel (Storm)</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E281" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0052</v>
       </c>
       <c r="F281" t="n">
-        <v>95.7</v>
+        <v>283.5</v>
       </c>
     </row>
     <row r="282">
@@ -6776,17 +6776,17 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Hurricane Irene (2011)</t>
+          <t>Hurricane Dorian (2019)</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E282" s="2" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="F282" t="n">
-        <v>53</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="283">
@@ -6798,39 +6798,39 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Voting Rights Act (1965)</t>
+          <t>Hurricane Irene (2011)</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E283" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>35.1</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bathrooms and Toilets</t>
+          <t>Voting Rights Act (1965)</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E284" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0086</v>
       </c>
       <c r="F284" t="n">
-        <v>39.6</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="285">
@@ -6842,17 +6842,17 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Democratic National Convention</t>
+          <t>Bathrooms and Toilets</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0157</v>
       </c>
       <c r="F285" t="n">
-        <v>33.7</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="286">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Lacrosse</t>
+          <t>Democratic National Convention</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E286" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0162</v>
       </c>
       <c r="F286" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="287">
@@ -6893,10 +6893,10 @@
         <v>59</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0281</v>
       </c>
       <c r="F287" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="288">
@@ -6908,65 +6908,65 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
+          <t>Lacrosse</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>12</v>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="F288" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
           <t>Hurricanes and Tropical Storms</t>
         </is>
       </c>
-      <c r="D288" t="n">
-        <v>104</v>
-      </c>
-      <c r="E288" s="2" t="n">
-        <v>0.0492</v>
-      </c>
-      <c r="F288" t="n">
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
+      <c r="D289" t="n">
+        <v>103</v>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="F289" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>North Dakota</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
         <is>
           <t>Spirit Lake Tribe (Sioux)</t>
         </is>
       </c>
-      <c r="D289" t="n">
+      <c r="D290" t="n">
         <v>4</v>
       </c>
-      <c r="E289" s="2" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="F289" t="n">
-        <v>4159.4</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr"/>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Pipelines</t>
-        </is>
-      </c>
-      <c r="D290" t="n">
-        <v>32</v>
-      </c>
       <c r="E290" s="2" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="F290" t="n">
-        <v>134.9</v>
+        <v>4179.5</v>
       </c>
     </row>
     <row r="291">
@@ -6978,17 +6978,17 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Oil Spills</t>
+          <t>Pipelines</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E291" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="F291" t="n">
-        <v>115.5</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="292">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Native Americans</t>
+          <t>Oil Spills</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>0.1298</v>
+        <v>0.0097</v>
       </c>
       <c r="F292" t="n">
-        <v>96.7</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="293">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Levees and Dams</t>
+          <t>Native Americans</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.1304</v>
       </c>
       <c r="F293" t="n">
-        <v>93.3</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="294">
@@ -7044,17 +7044,17 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Navajo Indians</t>
+          <t>Levees and Dams</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0266</v>
       </c>
       <c r="F294" t="n">
-        <v>91.2</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="295">
@@ -7066,87 +7066,87 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
+          <t>Navajo Indians</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>3</v>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F295" t="n">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
           <t>Keystone Pipeline System</t>
         </is>
       </c>
-      <c r="D295" t="n">
+      <c r="D296" t="n">
         <v>4</v>
       </c>
-      <c r="E295" s="2" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="F295" t="n">
-        <v>73.2</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
+      <c r="E296" s="2" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="F296" t="n">
+        <v>73.59999999999999</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C297" t="inlineStr">
         <is>
           <t>East Palestine, Ohio, Train Derailment (Feb 3, 2023)</t>
         </is>
       </c>
-      <c r="D296" t="n">
+      <c r="D297" t="n">
         <v>30</v>
       </c>
-      <c r="E296" s="2" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="F296" t="n">
-        <v>439.2</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr"/>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio, Shooting (2019)</t>
-        </is>
-      </c>
-      <c r="D297" t="n">
-        <v>19</v>
-      </c>
       <c r="E297" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.0121</v>
       </c>
       <c r="F297" t="n">
-        <v>252.5</v>
+        <v>443.1</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Amish</t>
+          <t>Dayton, Ohio, Shooting (2019)</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E298" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0077</v>
       </c>
       <c r="F298" t="n">
-        <v>132.9</v>
+        <v>254.7</v>
       </c>
     </row>
     <row r="299">
@@ -7158,17 +7158,17 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Haitian-Americans</t>
+          <t>Amish</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E299" s="2" t="n">
-        <v>0.0128</v>
+        <v>0.0073</v>
       </c>
       <c r="F299" t="n">
-        <v>117.1</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="300">
@@ -7180,17 +7180,17 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Registration of Voters</t>
+          <t>Haitian-Americans</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0129</v>
       </c>
       <c r="F300" t="n">
-        <v>66.09999999999999</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="301">
@@ -7202,17 +7202,17 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Republican National Convention</t>
+          <t>Registration of Voters</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0064</v>
       </c>
       <c r="F301" t="n">
-        <v>42.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="302">
@@ -7224,17 +7224,17 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Railroad Accidents and Safety</t>
+          <t>Republican National Convention</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.0218</v>
       </c>
       <c r="F302" t="n">
-        <v>32.6</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="303">
@@ -7246,17 +7246,17 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Vouchers</t>
+          <t>Railroad Accidents and Safety</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0109</v>
       </c>
       <c r="F303" t="n">
-        <v>31.2</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="304">
@@ -7268,65 +7268,65 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
+          <t>Vouchers</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>18</v>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F304" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
           <t>Blackouts and Brownouts (Electrical)</t>
         </is>
       </c>
-      <c r="D304" t="n">
-        <v>21</v>
-      </c>
-      <c r="E304" s="2" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="F304" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
+      <c r="D305" t="n">
+        <v>20</v>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F305" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>Oklahoma</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
+      <c r="C306" t="inlineStr">
         <is>
           <t>Tulsa Race Riot (1921)</t>
         </is>
       </c>
-      <c r="D305" t="n">
+      <c r="D306" t="n">
         <v>30</v>
       </c>
-      <c r="E305" s="2" t="n">
-        <v>0.0261</v>
-      </c>
-      <c r="F305" t="n">
-        <v>909.3</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr"/>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Murrah, Alfred P, Federal Building (Oklahoma City, Okla)</t>
-        </is>
-      </c>
-      <c r="D306" t="n">
-        <v>9</v>
-      </c>
       <c r="E306" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="F306" t="n">
-        <v>1409.3</v>
+        <v>917.2</v>
       </c>
     </row>
     <row r="307">
@@ -7338,17 +7338,17 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Cherokee Indians</t>
+          <t>Murrah, Alfred P, Federal Building (Oklahoma City, Okla)</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F307" t="n">
-        <v>328.1</v>
+        <v>1421.7</v>
       </c>
     </row>
     <row r="308">
@@ -7360,17 +7360,17 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Cherokee Indians</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>0.0765</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F308" t="n">
-        <v>204.2</v>
+        <v>331</v>
       </c>
     </row>
     <row r="309">
@@ -7382,17 +7382,17 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Juneteenth</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0771</v>
       </c>
       <c r="F309" t="n">
-        <v>196.1</v>
+        <v>205.9</v>
       </c>
     </row>
     <row r="310">
@@ -7404,17 +7404,17 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Sedatives</t>
+          <t>Juneteenth</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0105</v>
       </c>
       <c r="F310" t="n">
-        <v>129</v>
+        <v>197.8</v>
       </c>
     </row>
     <row r="311">
@@ -7426,17 +7426,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Capital Punishment</t>
+          <t>Sedatives</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0.1182</v>
+        <v>0.0061</v>
       </c>
       <c r="F311" t="n">
-        <v>66.8</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="312">
@@ -7448,65 +7448,65 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
+          <t>Capital Punishment</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>134</v>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>0.1174</v>
+      </c>
+      <c r="F312" t="n">
+        <v>66.40000000000001</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
           <t>Hydraulic Fracturing</t>
         </is>
       </c>
-      <c r="D312" t="n">
+      <c r="D313" t="n">
         <v>12</v>
       </c>
-      <c r="E312" s="2" t="n">
-        <v>0.0104</v>
-      </c>
-      <c r="F312" t="n">
-        <v>37.8</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
+      <c r="E313" s="2" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F313" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>Oregon</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
+      <c r="C314" t="inlineStr">
         <is>
           <t>George Floyd Protests (2020)</t>
         </is>
       </c>
-      <c r="D313" t="n">
+      <c r="D314" t="n">
         <v>66</v>
       </c>
-      <c r="E313" s="2" t="n">
-        <v>0.0489</v>
-      </c>
-      <c r="F313" t="n">
-        <v>62.1</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr"/>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Suckerfish</t>
-        </is>
-      </c>
-      <c r="D314" t="n">
-        <v>6</v>
-      </c>
       <c r="E314" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="F314" t="n">
-        <v>873.2</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="315">
@@ -7518,17 +7518,17 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Antifa Movement (US)</t>
+          <t>Suckerfish</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E315" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F315" t="n">
-        <v>278.4</v>
+        <v>883.7</v>
       </c>
     </row>
     <row r="316">
@@ -7540,17 +7540,17 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Federal Lands</t>
+          <t>Antifa Movement (US)</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>167.8</v>
+        <v>281.8</v>
       </c>
     </row>
     <row r="317">
@@ -7562,17 +7562,17 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Federal Actions in US Cities</t>
+          <t>Federal Lands</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0262</v>
       </c>
       <c r="F317" t="n">
-        <v>156.2</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="318">
@@ -7584,17 +7584,17 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Wildlife Sanctuaries and Nature Reserves</t>
+          <t>Federal Actions in US Cities</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="F318" t="n">
-        <v>128.5</v>
+        <v>158.1</v>
       </c>
     </row>
     <row r="319">
@@ -7606,17 +7606,17 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Wildlife Sanctuaries and Nature Reserves</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E319" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0097</v>
       </c>
       <c r="F319" t="n">
-        <v>113.3</v>
+        <v>130</v>
       </c>
     </row>
     <row r="320">
@@ -7628,87 +7628,87 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
+          <t>Salmon</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>32</v>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F320" t="n">
+        <v>114.7</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
           <t>Irrigation</t>
         </is>
       </c>
-      <c r="D320" t="n">
+      <c r="D321" t="n">
         <v>14</v>
       </c>
-      <c r="E320" s="2" t="n">
-        <v>0.0104</v>
-      </c>
-      <c r="F320" t="n">
-        <v>78.09999999999999</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+      <c r="E321" s="2" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F321" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>Pennsylvania</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C322" t="inlineStr">
         <is>
           <t>Trump Assassination Attempt (July 2024)</t>
         </is>
       </c>
-      <c r="D321" t="n">
+      <c r="D322" t="n">
         <v>21</v>
       </c>
-      <c r="E321" s="2" t="n">
+      <c r="E322" s="2" t="n">
         <v>0.0058</v>
       </c>
-      <c r="F321" t="n">
-        <v>240.7</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr"/>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, Shooting (2018)</t>
-        </is>
-      </c>
-      <c r="D322" t="n">
-        <v>37</v>
-      </c>
-      <c r="E322" s="2" t="n">
-        <v>0.0102</v>
-      </c>
       <c r="F322" t="n">
-        <v>185.3</v>
+        <v>243.1</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Hazing</t>
+          <t>Pittsburgh, PA, Shooting (2018)</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E323" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0103</v>
       </c>
       <c r="F323" t="n">
-        <v>74</v>
+        <v>187.2</v>
       </c>
     </row>
     <row r="324">
@@ -7720,17 +7720,17 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Railroad Accidents and Safety</t>
+          <t>Hazing</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0106</v>
       </c>
       <c r="F324" t="n">
-        <v>45.8</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="325">
@@ -7742,17 +7742,17 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Fraternities and Sororities</t>
+          <t>Railroad Accidents and Safety</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0153</v>
       </c>
       <c r="F325" t="n">
-        <v>37.7</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="326">
@@ -7764,17 +7764,17 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Democratic National Convention</t>
+          <t>Fraternities and Sororities</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0058</v>
       </c>
       <c r="F326" t="n">
-        <v>34.1</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="327">
@@ -7786,17 +7786,17 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Fugitives</t>
+          <t>Democratic National Convention</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0164</v>
       </c>
       <c r="F327" t="n">
-        <v>33</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="328">
@@ -7808,17 +7808,17 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Prison Escapes</t>
+          <t>Fugitives</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0083</v>
       </c>
       <c r="F328" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="329">
@@ -7830,87 +7830,87 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
+          <t>Prison Escapes</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>24</v>
+      </c>
+      <c r="E329" s="2" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="F329" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
           <t>Electoral College</t>
         </is>
       </c>
-      <c r="D329" t="n">
+      <c r="D330" t="n">
         <v>18</v>
       </c>
-      <c r="E329" s="2" t="n">
+      <c r="E330" s="2" t="n">
         <v>0.005</v>
       </c>
-      <c r="F329" t="n">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
+      <c r="F330" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C331" t="inlineStr">
         <is>
           <t>Brown University Shooting (Dec 13, 2025)</t>
         </is>
       </c>
-      <c r="D330" t="n">
+      <c r="D331" t="n">
         <v>25</v>
       </c>
-      <c r="E330" s="2" t="n">
-        <v>0.0415</v>
-      </c>
-      <c r="F330" t="n">
-        <v>2359.8</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr"/>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Hurricane Henri (2021)</t>
-        </is>
-      </c>
-      <c r="D331" t="n">
-        <v>4</v>
-      </c>
       <c r="E331" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F331" t="n">
-        <v>717.4</v>
+        <v>2383.5</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Narragansett Indians</t>
+          <t>Hurricane Henri (2021)</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0067</v>
       </c>
       <c r="F332" t="n">
-        <v>3586.9</v>
+        <v>724.6</v>
       </c>
     </row>
     <row r="333">
@@ -7922,17 +7922,17 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Fireworks</t>
+          <t>Narragansett Indians</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F333" t="n">
-        <v>294.4</v>
+        <v>3622.9</v>
       </c>
     </row>
     <row r="334">
@@ -7944,17 +7944,17 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Paints and Painting</t>
+          <t>Fireworks</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E334" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0436</v>
       </c>
       <c r="F334" t="n">
-        <v>103.7</v>
+        <v>286.3</v>
       </c>
     </row>
     <row r="335">
@@ -7976,7 +7976,7 @@
         <v>0.005</v>
       </c>
       <c r="F335" t="n">
-        <v>92.8</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="336">
@@ -7988,17 +7988,17 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Habeas Corpus</t>
+          <t>Paints and Painting</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0067</v>
       </c>
       <c r="F336" t="n">
-        <v>66.40000000000001</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="337">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Fugitives</t>
+          <t>Habeas Corpus</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.005</v>
       </c>
       <c r="F337" t="n">
-        <v>66.2</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="338">
@@ -8032,65 +8032,65 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
+          <t>Fugitives</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>10</v>
+      </c>
+      <c r="E338" s="2" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="F338" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
           <t>Bars and Nightclubs</t>
         </is>
       </c>
-      <c r="D338" t="n">
-        <v>56</v>
-      </c>
-      <c r="E338" s="2" t="n">
-        <v>0.0929</v>
-      </c>
-      <c r="F338" t="n">
-        <v>56.4</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+      <c r="D339" t="n">
+        <v>55</v>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>0.09210000000000002</v>
+      </c>
+      <c r="F339" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
         <is>
           <t>South Carolina</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C340" t="inlineStr">
         <is>
           <t>Charleston, SC, Shooting (2015)</t>
         </is>
       </c>
-      <c r="D339" t="n">
+      <c r="D340" t="n">
         <v>110</v>
       </c>
-      <c r="E339" s="2" t="n">
-        <v>0.0541</v>
-      </c>
-      <c r="F339" t="n">
-        <v>521.9</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr"/>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Hurricane Florence (2018)</t>
-        </is>
-      </c>
-      <c r="D340" t="n">
-        <v>31</v>
-      </c>
       <c r="E340" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F340" t="n">
-        <v>350.5</v>
+        <v>524</v>
       </c>
     </row>
     <row r="341">
@@ -8102,39 +8102,39 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Presidential Election of 2012</t>
+          <t>Hurricane Florence (2018)</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>187</v>
+        <v>31</v>
       </c>
       <c r="E341" s="2" t="n">
-        <v>0.0919</v>
+        <v>0.0153</v>
       </c>
       <c r="F341" t="n">
-        <v>25.8</v>
+        <v>351.9</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Flags, Emblems and Insignia</t>
+          <t>Presidential Election of 2012</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="E342" s="2" t="n">
-        <v>0.0472</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="F342" t="n">
-        <v>117.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="343">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Plutonium</t>
+          <t>Flags, Emblems and Insignia</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="E343" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.0469</v>
       </c>
       <c r="F343" t="n">
-        <v>80.7</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="344">
@@ -8168,17 +8168,17 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Nuclear Wastes</t>
+          <t>Plutonium</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E344" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0059</v>
       </c>
       <c r="F344" t="n">
-        <v>58.4</v>
+        <v>81</v>
       </c>
     </row>
     <row r="345">
@@ -8190,17 +8190,17 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Primaries and Caucuses</t>
+          <t>Nuclear Wastes</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>453</v>
+        <v>24</v>
       </c>
       <c r="E345" s="2" t="n">
-        <v>0.2226</v>
+        <v>0.0118</v>
       </c>
       <c r="F345" t="n">
-        <v>41.9</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="346">
@@ -8212,17 +8212,17 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Political Advertising</t>
+          <t>Primaries and Caucuses</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="E346" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.222</v>
       </c>
       <c r="F346" t="n">
-        <v>22.8</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="347">
@@ -8234,17 +8234,17 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Adultery</t>
+          <t>Political Advertising</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="E347" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0395</v>
       </c>
       <c r="F347" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="348">
@@ -8256,65 +8256,65 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
+          <t>Adultery</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>17</v>
+      </c>
+      <c r="E348" s="2" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="F348" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
           <t>Hate Crimes</t>
         </is>
       </c>
-      <c r="D348" t="n">
+      <c r="D349" t="n">
         <v>36</v>
       </c>
-      <c r="E348" s="2" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="F348" t="n">
+      <c r="E349" s="2" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="F349" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr">
         <is>
           <t>South Dakota</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
         <is>
           <t>Sioux Indians</t>
         </is>
       </c>
-      <c r="D349" t="n">
+      <c r="D350" t="n">
         <v>4</v>
       </c>
-      <c r="E349" s="2" t="n">
-        <v>0.0089</v>
-      </c>
-      <c r="F349" t="n">
-        <v>2746.5</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr"/>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Lakota Indians</t>
-        </is>
-      </c>
-      <c r="D350" t="n">
-        <v>3</v>
-      </c>
       <c r="E350" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F350" t="n">
-        <v>2403.2</v>
+        <v>2783.6</v>
       </c>
     </row>
     <row r="351">
@@ -8326,17 +8326,17 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>budgets_and_budgeting</t>
+          <t>Lakota Indians</t>
         </is>
       </c>
       <c r="D351" t="n">
         <v>3</v>
       </c>
       <c r="E351" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0068</v>
       </c>
       <c r="F351" t="n">
-        <v>1802.4</v>
+        <v>2435.7</v>
       </c>
     </row>
     <row r="352">
@@ -8348,17 +8348,17 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Oglala Sioux Indians</t>
+          <t>budgets_and_budgeting</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E352" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.0068</v>
       </c>
       <c r="F352" t="n">
-        <v>1762.3</v>
+        <v>1826.7</v>
       </c>
     </row>
     <row r="353">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>health_insurance</t>
+          <t>Oglala Sioux Indians</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E353" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0248</v>
       </c>
       <c r="F353" t="n">
-        <v>1310.8</v>
+        <v>1786.2</v>
       </c>
     </row>
     <row r="354">
@@ -8392,17 +8392,17 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Neutrinos</t>
+          <t>health_insurance</t>
         </is>
       </c>
       <c r="D354" t="n">
         <v>3</v>
       </c>
       <c r="E354" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0068</v>
       </c>
       <c r="F354" t="n">
-        <v>313.5</v>
+        <v>1328.5</v>
       </c>
     </row>
     <row r="355">
@@ -8414,65 +8414,65 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
+          <t>Neutrinos</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>3</v>
+      </c>
+      <c r="E355" s="2" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F355" t="n">
+        <v>317.7</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
           <t>Bison</t>
         </is>
       </c>
-      <c r="D355" t="n">
-        <v>4</v>
-      </c>
-      <c r="E355" s="2" t="n">
-        <v>0.0089</v>
-      </c>
-      <c r="F355" t="n">
-        <v>186.7</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
+      <c r="D356" t="n">
+        <v>3</v>
+      </c>
+      <c r="E356" s="2" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F356" t="n">
+        <v>141.9</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>Tennessee</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B357" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C357" t="inlineStr">
         <is>
           <t>Tennessee Ammunition Plant Explosion (Oct 2025)</t>
         </is>
       </c>
-      <c r="D356" t="n">
+      <c r="D357" t="n">
         <v>8</v>
       </c>
-      <c r="E356" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="F356" t="n">
-        <v>1628.7</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr"/>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Nashville, Tenn, Explosion (2020)</t>
-        </is>
-      </c>
-      <c r="D357" t="n">
-        <v>12</v>
-      </c>
       <c r="E357" s="2" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="F357" t="n">
-        <v>1396</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="358">
@@ -8484,17 +8484,17 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Covenant School, Nashville, Tenn, Shooting (2023)</t>
+          <t>Nashville, Tenn, Explosion (2020)</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E358" s="2" t="n">
-        <v>0.0188</v>
+        <v>0.0091</v>
       </c>
       <c r="F358" t="n">
-        <v>866.3</v>
+        <v>1406.6</v>
       </c>
     </row>
     <row r="359">
@@ -8506,39 +8506,39 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Hurricane Helene (2024)</t>
+          <t>Covenant School, Nashville, Tenn, Shooting (2023)</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E359" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.019</v>
       </c>
       <c r="F359" t="n">
-        <v>83.5</v>
+        <v>872.9</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Drag (Performance)</t>
+          <t>Hurricane Helene (2024)</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E360" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0076</v>
       </c>
       <c r="F360" t="n">
-        <v>165.2</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="361">
@@ -8550,17 +8550,17 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Drag (Performance)</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E361" s="2" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="F361" t="n">
-        <v>86.5</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="362">
@@ -8572,17 +8572,17 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Cold and Cold Spells</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="E362" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0326</v>
       </c>
       <c r="F362" t="n">
-        <v>51.1</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="363">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Federal Actions in US Cities</t>
+          <t>Cold and Cold Spells</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E363" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0053</v>
       </c>
       <c r="F363" t="n">
-        <v>45.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="364">
@@ -8616,17 +8616,17 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>School Shootings and Armed Attacks</t>
+          <t>Federal Actions in US Cities</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E364" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0061</v>
       </c>
       <c r="F364" t="n">
-        <v>28.4</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="365">
@@ -8638,65 +8638,65 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
+          <t>School Shootings and Armed Attacks</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>22</v>
+      </c>
+      <c r="E365" s="2" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F365" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
           <t>Fugitives</t>
         </is>
       </c>
-      <c r="D365" t="n">
+      <c r="D366" t="n">
         <v>9</v>
       </c>
-      <c r="E365" s="2" t="n">
+      <c r="E366" s="2" t="n">
         <v>0.0068</v>
       </c>
-      <c r="F365" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+      <c r="F366" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
         <is>
           <t>Texas</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C367" t="inlineStr">
         <is>
           <t>Central Texas Floods (July 2025)</t>
         </is>
       </c>
-      <c r="D366" t="n">
+      <c r="D367" t="n">
         <v>63</v>
       </c>
-      <c r="E366" s="2" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="F366" t="n">
-        <v>162.4</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr"/>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>Uvalde, Tex, Shooting (May 24, 2022)</t>
-        </is>
-      </c>
-      <c r="D367" t="n">
-        <v>114</v>
-      </c>
       <c r="E367" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0074</v>
       </c>
       <c r="F367" t="n">
-        <v>114.5</v>
+        <v>164</v>
       </c>
     </row>
     <row r="368">
@@ -8708,17 +8708,17 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Hurricane Harvey (2017)</t>
+          <t>Uvalde, Tex, Shooting (May 24, 2022)</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E368" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.0133</v>
       </c>
       <c r="F368" t="n">
-        <v>111.4</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="369">
@@ -8730,39 +8730,39 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>El Paso, Tex, Shooting (2019)</t>
+          <t>Hurricane Harvey (2017)</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="E369" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0167</v>
       </c>
       <c r="F369" t="n">
-        <v>81.09999999999999</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Hurricane Ike</t>
+          <t>El Paso, Tex, Shooting (2019)</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E370" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F370" t="n">
-        <v>146.1</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="371">
@@ -8774,17 +8774,17 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Border Barriers</t>
+          <t>Hurricane Ike</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E371" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0053</v>
       </c>
       <c r="F371" t="n">
-        <v>27.1</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="372">
@@ -8796,17 +8796,17 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Immigration Detention</t>
+          <t>Border Barriers</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="E372" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0105</v>
       </c>
       <c r="F372" t="n">
-        <v>23.7</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="373">
@@ -8818,17 +8818,17 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Tornadoes</t>
+          <t>Immigration Detention</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="E373" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0189</v>
       </c>
       <c r="F373" t="n">
-        <v>23.1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="374">
@@ -8840,17 +8840,17 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mass Shootings</t>
+          <t>Tornadoes</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E374" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F374" t="n">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="375">
@@ -8862,65 +8862,65 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
+          <t>Mass Shootings</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>94</v>
+      </c>
+      <c r="E375" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F375" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
           <t>Power Failures and Blackouts</t>
         </is>
       </c>
-      <c r="D375" t="n">
+      <c r="D376" t="n">
         <v>74</v>
       </c>
-      <c r="E375" s="2" t="n">
+      <c r="E376" s="2" t="n">
         <v>0.0086</v>
       </c>
-      <c r="F375" t="n">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
+      <c r="F376" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>Utah</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
+      <c r="C377" t="inlineStr">
         <is>
           <t>Olympic Games (2002)</t>
         </is>
       </c>
-      <c r="D376" t="n">
-        <v>33</v>
-      </c>
-      <c r="E376" s="2" t="n">
-        <v>0.0318</v>
-      </c>
-      <c r="F376" t="n">
-        <v>135.6</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr"/>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>Polygamy</t>
-        </is>
-      </c>
       <c r="D377" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E377" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0302</v>
       </c>
       <c r="F377" t="n">
-        <v>434.1</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="378">
@@ -8932,17 +8932,17 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Fundamentalist Church of Jesus Christ of Latter-day Saints</t>
+          <t>Polygamy</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E378" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0292</v>
       </c>
       <c r="F378" t="n">
-        <v>388.5</v>
+        <v>438.3</v>
       </c>
     </row>
     <row r="379">
@@ -8954,17 +8954,17 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mormons (Church of Jesus Christ of Latter-Day Saints)</t>
+          <t>Fundamentalist Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="E379" s="2" t="n">
-        <v>0.0915</v>
+        <v>0.0107</v>
       </c>
       <c r="F379" t="n">
-        <v>365.9</v>
+        <v>392.3</v>
       </c>
     </row>
     <row r="380">
@@ -8976,17 +8976,17 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Residence Requirements</t>
+          <t>Mormons (Church of Jesus Christ of Latter-Day Saints)</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="E380" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0924</v>
       </c>
       <c r="F380" t="n">
-        <v>162.4</v>
+        <v>369.5</v>
       </c>
     </row>
     <row r="381">
@@ -8998,17 +8998,17 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Federal Lands</t>
+          <t>Residence Requirements</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E381" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0058</v>
       </c>
       <c r="F381" t="n">
-        <v>99.8</v>
+        <v>163.9</v>
       </c>
     </row>
     <row r="382">
@@ -9020,17 +9020,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Navajo Indians</t>
+          <t>Federal Lands</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E382" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.0156</v>
       </c>
       <c r="F382" t="n">
-        <v>97.5</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="383">
@@ -9042,65 +9042,65 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
+          <t>Navajo Indians</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>8</v>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F383" t="n">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
           <t>Public Property</t>
         </is>
       </c>
-      <c r="D383" t="n">
+      <c r="D384" t="n">
         <v>7</v>
       </c>
-      <c r="E383" s="2" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="F383" t="n">
-        <v>87.3</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
+      <c r="E384" s="2" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F384" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
         <is>
           <t>Vermont</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B385" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
+      <c r="C385" t="inlineStr">
         <is>
           <t>Hurricane Irene (2011)</t>
         </is>
       </c>
-      <c r="D384" t="n">
+      <c r="D385" t="n">
         <v>20</v>
       </c>
-      <c r="E384" s="2" t="n">
-        <v>0.0321</v>
-      </c>
-      <c r="F384" t="n">
-        <v>299.3</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr"/>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>Green Cards (US)</t>
-        </is>
-      </c>
-      <c r="D385" t="n">
-        <v>4</v>
-      </c>
       <c r="E385" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="F385" t="n">
-        <v>257.2</v>
+        <v>302.2</v>
       </c>
     </row>
     <row r="386">
@@ -9112,17 +9112,17 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Maple Syrup and Sugar</t>
+          <t>Green Cards (US)</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E386" s="2" t="n">
-        <v>0.0048</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F386" t="n">
-        <v>140.7</v>
+        <v>259.7</v>
       </c>
     </row>
     <row r="387">
@@ -9134,17 +9134,17 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Heroin</t>
+          <t>Maple Syrup and Sugar</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E387" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0049</v>
       </c>
       <c r="F387" t="n">
-        <v>61</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="388">
@@ -9156,17 +9156,17 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Euthanasia and Assisted Suicide</t>
+          <t>Heroin</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E388" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0146</v>
       </c>
       <c r="F388" t="n">
-        <v>53.2</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="389">
@@ -9178,17 +9178,17 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Foreign Students (in US)</t>
+          <t>Euthanasia and Assisted Suicide</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E389" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F389" t="n">
-        <v>49.1</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="390">
@@ -9200,17 +9200,17 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Executive Privilege, Doctrine of</t>
+          <t>Foreign Students (in US)</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E390" s="2" t="n">
-        <v>0.0048</v>
+        <v>0.0097</v>
       </c>
       <c r="F390" t="n">
-        <v>43.6</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="391">
@@ -9222,87 +9222,87 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
+          <t>Executive Privilege, Doctrine of</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>3</v>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F391" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
           <t>Pro-Palestinian Campus Protests (2023- )</t>
         </is>
       </c>
-      <c r="D391" t="n">
+      <c r="D392" t="n">
         <v>4</v>
       </c>
-      <c r="E391" s="2" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="F391" t="n">
-        <v>29.7</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
+      <c r="E392" s="2" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F392" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr">
+      <c r="C393" t="inlineStr">
         <is>
           <t>Virginia Beach, VA, Shooting (2019)</t>
         </is>
       </c>
-      <c r="D392" t="n">
+      <c r="D393" t="n">
         <v>12</v>
       </c>
-      <c r="E392" s="2" t="n">
+      <c r="E393" s="2" t="n">
         <v>0.0049</v>
       </c>
-      <c r="F392" t="n">
-        <v>660.5</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr"/>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>Charlottesville, VA, Violence (August, 2017)</t>
-        </is>
-      </c>
-      <c r="D393" t="n">
-        <v>92</v>
-      </c>
-      <c r="E393" s="2" t="n">
-        <v>0.0375</v>
-      </c>
       <c r="F393" t="n">
-        <v>226.3</v>
+        <v>667.6</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Serial Murders</t>
+          <t>Charlottesville, VA, Violence (August, 2017)</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>248</v>
+        <v>92</v>
       </c>
       <c r="E394" s="2" t="n">
-        <v>0.101</v>
+        <v>0.0379</v>
       </c>
       <c r="F394" t="n">
-        <v>230.4</v>
+        <v>228.7</v>
       </c>
     </row>
     <row r="395">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Gifts to Public Officials</t>
+          <t>Serial Murders</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="E395" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F395" t="n">
-        <v>93.09999999999999</v>
+        <v>220.6</v>
       </c>
     </row>
     <row r="396">
@@ -9336,17 +9336,17 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Neo Nazi Groups</t>
+          <t>Gifts to Public Officials</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E396" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0107</v>
       </c>
       <c r="F396" t="n">
-        <v>38.7</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="397">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Whites</t>
+          <t>Neo Nazi Groups</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E397" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F397" t="n">
-        <v>36.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="398">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Confessions</t>
+          <t>Whites</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E398" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="F398" t="n">
-        <v>25.8</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="399">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Fringe Groups and Movements</t>
+          <t>Confessions</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E399" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0049</v>
       </c>
       <c r="F399" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="400">
@@ -9424,65 +9424,65 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
+          <t>Fringe Groups and Movements</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>56</v>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F400" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
           <t>Civil War (US) (1861-65)</t>
         </is>
       </c>
-      <c r="D400" t="n">
-        <v>42</v>
-      </c>
-      <c r="E400" s="2" t="n">
-        <v>0.0171</v>
-      </c>
-      <c r="F400" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
+      <c r="D401" t="n">
+        <v>41</v>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F401" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
         <is>
           <t>Washington</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
         <is>
           <t>Hanford Nuclear Reservation (Wash)</t>
         </is>
       </c>
-      <c r="D401" t="n">
+      <c r="D402" t="n">
         <v>8</v>
       </c>
-      <c r="E401" s="2" t="n">
+      <c r="E402" s="2" t="n">
         <v>0.004500000000000001</v>
       </c>
-      <c r="F401" t="n">
-        <v>507.1</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr"/>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>Hornets (Insects)</t>
-        </is>
-      </c>
-      <c r="D402" t="n">
-        <v>10</v>
-      </c>
-      <c r="E402" s="2" t="n">
-        <v>0.005600000000000001</v>
-      </c>
       <c r="F402" t="n">
-        <v>446</v>
+        <v>514.5</v>
       </c>
     </row>
     <row r="403">
@@ -9494,17 +9494,17 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Landslides and Mudslides</t>
+          <t>Hornets (Insects)</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E403" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F403" t="n">
-        <v>87.7</v>
+        <v>452.6</v>
       </c>
     </row>
     <row r="404">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mad Cow Disease (Bovine Spongiform Encephalopathy)</t>
+          <t>Landslides and Mudslides</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E404" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0254</v>
       </c>
       <c r="F404" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="405">
@@ -9538,17 +9538,17 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Livestock Diseases</t>
+          <t>Mad Cow Disease (Bovine Spongiform Encephalopathy)</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E405" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0136</v>
       </c>
       <c r="F405" t="n">
-        <v>60</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="406">
@@ -9560,17 +9560,17 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Livestock Diseases</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F406" t="n">
-        <v>56</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="407">
@@ -9582,87 +9582,87 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Serial Murders</t>
+          <t>Salmon</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E407" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0119</v>
       </c>
       <c r="F407" t="n">
-        <v>47</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Nuclear Wastes</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>17</v>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F408" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
         <is>
           <t>West Virginia</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C409" t="inlineStr">
         <is>
           <t>Washington DC National Guard Shooting (Nov 2025)</t>
         </is>
       </c>
-      <c r="D408" t="n">
+      <c r="D409" t="n">
         <v>4</v>
       </c>
-      <c r="E408" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="F408" t="n">
-        <v>308.8</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr"/>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>American Families Plan (2021)</t>
-        </is>
-      </c>
-      <c r="D409" t="n">
-        <v>5</v>
-      </c>
       <c r="E409" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0061</v>
       </c>
       <c r="F409" t="n">
-        <v>73</v>
+        <v>315</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Strip Mining</t>
+          <t>American Families Plan (2021)</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E410" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="F410" t="n">
-        <v>694.9</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="411">
@@ -9674,17 +9674,17 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Mountaintop Removal Mining</t>
+          <t>Strip Mining</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E411" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="F411" t="n">
-        <v>294.8</v>
+        <v>708.7</v>
       </c>
     </row>
     <row r="412">
@@ -9696,17 +9696,17 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Mines and Mining</t>
+          <t>Mountaintop Removal Mining</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="E412" s="2" t="n">
-        <v>0.1619</v>
+        <v>0.0061</v>
       </c>
       <c r="F412" t="n">
-        <v>145.7</v>
+        <v>300.6</v>
       </c>
     </row>
     <row r="413">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Mines and Mining</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="E413" s="2" t="n">
-        <v>0.1274</v>
+        <v>0.1636</v>
       </c>
       <c r="F413" t="n">
-        <v>143.8</v>
+        <v>147.3</v>
       </c>
     </row>
     <row r="414">
@@ -9740,17 +9740,17 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Missing in Action</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="E414" s="2" t="n">
-        <v>0.006</v>
+        <v>0.1284</v>
       </c>
       <c r="F414" t="n">
-        <v>109</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="415">
@@ -9769,10 +9769,10 @@
         <v>11</v>
       </c>
       <c r="E415" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.0168</v>
       </c>
       <c r="F415" t="n">
-        <v>88.7</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="416">
@@ -9791,102 +9791,102 @@
         <v>17</v>
       </c>
       <c r="E416" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.026</v>
       </c>
       <c r="F416" t="n">
-        <v>68.90000000000001</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Carbon Monoxide</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>3</v>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F417" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>Waukesha, Wis, Holiday Parade Attack (2021)</t>
-        </is>
-      </c>
-      <c r="D417" t="n">
-        <v>11</v>
-      </c>
-      <c r="E417" s="2" t="n">
-        <v>0.005500000000000001</v>
-      </c>
-      <c r="F417" t="n">
-        <v>788.3</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr"/>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Oak Creek, Wis, Shooting (2012)</t>
+          <t>Abundant Life Christian School, Madison, Wis, Shooting (2024)</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E418" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F418" t="n">
-        <v>436.7</v>
+        <v>886.1</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Collective Bargaining</t>
+          <t>Waukesha, Wis, Holiday Parade Attack (2021)</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="E419" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F419" t="n">
-        <v>97.3</v>
+        <v>794.2</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Self-Defense</t>
+          <t>Oak Creek, Wis, Shooting (2012)</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E420" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F420" t="n">
-        <v>74.59999999999999</v>
+        <v>440</v>
       </c>
     </row>
     <row r="421">
@@ -9898,17 +9898,17 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Sikhs and Sikhism</t>
+          <t>Collective Bargaining</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E421" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="F421" t="n">
-        <v>73.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="422">
@@ -9920,17 +9920,17 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Project Democracy</t>
+          <t>Self-Defense</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E422" s="2" t="n">
-        <v>0.005</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F422" t="n">
-        <v>66.40000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="423">
@@ -9942,17 +9942,17 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Republican National Convention</t>
+          <t>Sikhs and Sikhism</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E423" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F423" t="n">
-        <v>36.1</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="424">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Deer</t>
+          <t>Project Democracy</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -9974,7 +9974,7 @@
         <v>0.005</v>
       </c>
       <c r="F424" t="n">
-        <v>32.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="425">
@@ -9986,25 +9986,21 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Voter Fraud (Election Fraud)</t>
+          <t>Republican National Convention</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E425" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0185</v>
       </c>
       <c r="F425" t="n">
-        <v>27.8</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
+      <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -10012,17 +10008,17 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Treasure Troves</t>
+          <t>Deer</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E426" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="F426" t="n">
-        <v>345.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="427">
@@ -10034,21 +10030,25 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Elk</t>
+          <t>Voter Fraud (Election Fraud)</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E427" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.019</v>
       </c>
       <c r="F427" t="n">
-        <v>327.4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr"/>
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Recurring</t>
@@ -10056,17 +10056,17 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Treasure Troves</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E428" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F428" t="n">
-        <v>247.3</v>
+        <v>345.7</v>
       </c>
     </row>
     <row r="429">
@@ -10078,17 +10078,17 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Snowmobiles</t>
+          <t>Elk</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E429" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0104</v>
       </c>
       <c r="F429" t="n">
-        <v>207.6</v>
+        <v>327.4</v>
       </c>
     </row>
     <row r="430">
@@ -10100,17 +10100,17 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Bison</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E430" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0313</v>
       </c>
       <c r="F430" t="n">
-        <v>164.5</v>
+        <v>247.3</v>
       </c>
     </row>
     <row r="431">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Ranches</t>
+          <t>Snowmobiles</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E431" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.0131</v>
       </c>
       <c r="F431" t="n">
-        <v>153.2</v>
+        <v>207.6</v>
       </c>
     </row>
     <row r="432">
@@ -10144,21 +10144,65 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
+          <t>Bison</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>3</v>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F432" t="n">
+        <v>164.5</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr"/>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Ranches</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>7</v>
+      </c>
+      <c r="E433" s="2" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F433" t="n">
+        <v>153.2</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr"/>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
           <t>National Parks, Monuments and Seashores</t>
         </is>
       </c>
-      <c r="D432" t="n">
+      <c r="D434" t="n">
         <v>25</v>
       </c>
-      <c r="E432" s="2" t="n">
+      <c r="E434" s="2" t="n">
         <v>0.0653</v>
       </c>
-      <c r="F432" t="n">
+      <c r="F434" t="n">
         <v>84.5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E432">
+  <conditionalFormatting sqref="E2:E434">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10168,7 +10212,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F432">
+  <conditionalFormatting sqref="F2:F434">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10271,31 +10315,31 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1709.4</v>
+        <v>1738.3</v>
       </c>
       <c r="D2" t="n">
-        <v>160</v>
+        <v>162.7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0281</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>531.8</v>
+        <v>473.2</v>
       </c>
       <c r="I2" t="n">
-        <v>305.3</v>
+        <v>310.4</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0098</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -10308,31 +10352,31 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>1331.8</v>
+        <v>601.3</v>
       </c>
       <c r="D3" t="n">
-        <v>233.7</v>
+        <v>206.5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.0433</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.013</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1065.5</v>
+        <v>1070.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1065.5</v>
+        <v>1070.1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0173</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="4">
@@ -10345,31 +10389,31 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>310.3</v>
+        <v>311.7</v>
       </c>
       <c r="D4" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.0467</v>
+        <v>0.0469</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>403.9</v>
+        <v>405.7</v>
       </c>
       <c r="I4" t="n">
-        <v>403.9</v>
+        <v>405.7</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0489</v>
+        <v>0.0491</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0489</v>
+        <v>0.0491</v>
       </c>
     </row>
     <row r="5">
@@ -10411,13 +10455,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>83.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0496</v>
+        <v>0.0503</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.0052</v>
@@ -10426,16 +10470,16 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>82.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>82.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="7">
@@ -10448,31 +10492,31 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>88.8</v>
+        <v>89.8</v>
       </c>
       <c r="D7" t="n">
-        <v>28.1</v>
+        <v>28.4</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0287</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>610.8</v>
+        <v>617.9</v>
       </c>
       <c r="I7" t="n">
-        <v>371.1</v>
+        <v>375.5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0283</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="8">
@@ -10485,31 +10529,31 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>117.5</v>
+        <v>36.6</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1916</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0073</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>38.1</v>
+        <v>45.1</v>
       </c>
       <c r="I8" t="n">
-        <v>38.1</v>
+        <v>45.1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0127</v>
+        <v>0.015</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.0127</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="9">
@@ -10522,16 +10566,16 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>186.1</v>
+        <v>193.3</v>
       </c>
       <c r="D9" t="n">
-        <v>79.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.5797</v>
+        <v>0.5692</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.005</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -10551,31 +10595,31 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>38.7</v>
+        <v>39.1</v>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1205</v>
+        <v>0.1215</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="I10" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.0959</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.0959</v>
+        <v>0.09669999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -10588,31 +10632,31 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>122.2</v>
+        <v>119.7</v>
       </c>
       <c r="D11" t="n">
-        <v>58.2</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.0291</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.0052</v>
       </c>
       <c r="G11" t="n">
         <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>229.3</v>
+        <v>228.4</v>
       </c>
       <c r="I11" t="n">
-        <v>79.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.019</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0054</v>
       </c>
     </row>
     <row r="12">
@@ -10625,31 +10669,31 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>90.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.0611</v>
+        <v>0.0619</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>501.8</v>
+        <v>507.7</v>
       </c>
       <c r="I12" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.1319</v>
+        <v>0.1334</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="13">
@@ -10662,13 +10706,13 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>3085.4</v>
+        <v>3125.5</v>
       </c>
       <c r="D13" t="n">
-        <v>393.1</v>
+        <v>374.1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.0471</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.0043</v>
@@ -10691,16 +10735,16 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>2510.1</v>
+        <v>2534.6</v>
       </c>
       <c r="D14" t="n">
-        <v>79.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0254</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -10720,13 +10764,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>111.4</v>
+        <v>112.6</v>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.0491</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.005500000000000001</v>
@@ -10735,16 +10779,16 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>373.5</v>
+        <v>377.5</v>
       </c>
       <c r="I15" t="n">
-        <v>373.5</v>
+        <v>377.5</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="16">
@@ -10757,13 +10801,13 @@
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>496.2</v>
+        <v>502.1</v>
       </c>
       <c r="D16" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0217</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0.0043</v>
@@ -10772,16 +10816,16 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1389.4</v>
+        <v>1406</v>
       </c>
       <c r="I16" t="n">
-        <v>1389.4</v>
+        <v>1406</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0098</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="17">
@@ -10794,13 +10838,13 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>135.5</v>
+        <v>136.1</v>
       </c>
       <c r="D17" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.2983</v>
+        <v>0.2995</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0.005</v>
@@ -10809,16 +10853,16 @@
         <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="I17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.1914</v>
+        <v>0.1922</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0756</v>
       </c>
     </row>
     <row r="18">
@@ -10831,13 +10875,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>338.8</v>
+        <v>341.1</v>
       </c>
       <c r="D18" t="n">
-        <v>103.1</v>
+        <v>103.8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0389</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0.004</v>
@@ -10860,13 +10904,13 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>286.3</v>
+        <v>288.6</v>
       </c>
       <c r="D19" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.0478</v>
+        <v>0.0482</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0.004500000000000001</v>
@@ -10875,13 +10919,13 @@
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>1626.7</v>
+        <v>1640</v>
       </c>
       <c r="I19" t="n">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0237</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0.004500000000000001</v>
@@ -10897,28 +10941,28 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>886.8</v>
+        <v>895.2</v>
       </c>
       <c r="D20" t="n">
-        <v>106.1</v>
+        <v>103.2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.1894</v>
+        <v>0.1842</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="G20" t="n">
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>566</v>
+        <v>571.4</v>
       </c>
       <c r="I20" t="n">
-        <v>230.6</v>
+        <v>232.8</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2927</v>
+        <v>0.2889</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0.006999999999999999</v>
@@ -10934,31 +10978,31 @@
         <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>191.3</v>
+        <v>182.7</v>
       </c>
       <c r="D21" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0344</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2133.8</v>
+        <v>2158.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2133.8</v>
+        <v>2158.2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.0503</v>
+        <v>0.0509</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.0503</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="22">
@@ -10971,16 +11015,16 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>290.9</v>
+        <v>279.3</v>
       </c>
       <c r="D22" t="n">
-        <v>27.2</v>
+        <v>27.7</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.1275</v>
+        <v>0.1224</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -11000,31 +11044,31 @@
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>264.4</v>
+        <v>251.9</v>
       </c>
       <c r="D23" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.0717</v>
+        <v>0.0707</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0048</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>228.5</v>
+        <v>232.3</v>
       </c>
       <c r="I23" t="n">
-        <v>228.5</v>
+        <v>232.3</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0452</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0452</v>
       </c>
     </row>
     <row r="24">
@@ -11037,31 +11081,31 @@
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>146.9</v>
+        <v>146.2</v>
       </c>
       <c r="D24" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>506.2</v>
+        <v>511.9</v>
       </c>
       <c r="I24" t="n">
-        <v>506.2</v>
+        <v>511.9</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0121</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0121</v>
       </c>
     </row>
     <row r="25">
@@ -11074,31 +11118,31 @@
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>565.3</v>
+        <v>571.1</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>47.4</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.1953</v>
+        <v>0.1973</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="G25" t="n">
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>969.8</v>
+        <v>979.6</v>
       </c>
       <c r="I25" t="n">
-        <v>122.3</v>
+        <v>123.5</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="26">
@@ -11111,28 +11155,28 @@
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>175.2</v>
+        <v>177.2</v>
       </c>
       <c r="D26" t="n">
-        <v>51.8</v>
+        <v>52.3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0451</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="G26" t="n">
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>423.4</v>
+        <v>392.4</v>
       </c>
       <c r="I26" t="n">
-        <v>75.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.0799</v>
+        <v>0.0776</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0.0063</v>
@@ -11148,13 +11192,13 @@
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>108.8</v>
+        <v>109.5</v>
       </c>
       <c r="D27" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.2043</v>
+        <v>0.2057</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.005</v>
@@ -11163,10 +11207,10 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>910.8</v>
+        <v>916.8</v>
       </c>
       <c r="I27" t="n">
-        <v>910.8</v>
+        <v>916.8</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.0072</v>
@@ -11185,16 +11229,16 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>1398.1</v>
+        <v>1408.7</v>
       </c>
       <c r="D28" t="n">
-        <v>96.2</v>
+        <v>97</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.0241</v>
+        <v>0.0243</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0046</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -11214,16 +11258,16 @@
         <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>212.3</v>
+        <v>214.2</v>
       </c>
       <c r="D29" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0281</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -11243,31 +11287,31 @@
         <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>197.1</v>
+        <v>199.1</v>
       </c>
       <c r="D30" t="n">
-        <v>27.1</v>
+        <v>26.3</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.046</v>
+        <v>0.0453</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>343.2</v>
+        <v>346.8</v>
       </c>
       <c r="I30" t="n">
-        <v>343.2</v>
+        <v>346.8</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.033</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="31">
@@ -11280,31 +11324,31 @@
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="D31" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.3174</v>
+        <v>0.3182</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0119</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>41</v>
+        <v>41.3</v>
       </c>
       <c r="I31" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.1951</v>
+        <v>0.1961</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.0565</v>
+        <v>0.0558</v>
       </c>
     </row>
     <row r="32">
@@ -11317,31 +11361,31 @@
         <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>59.5</v>
+        <v>27.7</v>
       </c>
       <c r="D32" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.0372</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
       <c r="I32" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0106</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="33">
@@ -11354,16 +11398,16 @@
         <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>320.8</v>
+        <v>325.5</v>
       </c>
       <c r="D33" t="n">
-        <v>87.5</v>
+        <v>86.8</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0281</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -11383,24 +11427,32 @@
         <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="D34" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.0556</v>
+        <v>0.0544</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0064</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.0058</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11412,31 +11464,31 @@
         <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="D35" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.0492</v>
+        <v>0.0491</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>457.6</v>
+        <v>460.6</v>
       </c>
       <c r="I35" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.027</v>
+        <v>0.0272</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="36">
@@ -11449,13 +11501,13 @@
         <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>4159.4</v>
+        <v>4179.5</v>
       </c>
       <c r="D36" t="n">
-        <v>73.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.1298</v>
+        <v>0.1304</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0.0072</v>
@@ -11478,13 +11530,13 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>132.9</v>
+        <v>134.1</v>
       </c>
       <c r="D37" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0218</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0.0064</v>
@@ -11493,16 +11545,16 @@
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>439.2</v>
+        <v>443.1</v>
       </c>
       <c r="I37" t="n">
-        <v>252.5</v>
+        <v>254.7</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.012</v>
+        <v>0.0121</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="38">
@@ -11515,13 +11567,13 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>1409.3</v>
+        <v>1421.7</v>
       </c>
       <c r="D38" t="n">
-        <v>37.8</v>
+        <v>38.1</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.1182</v>
+        <v>0.1174</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0.0061</v>
@@ -11530,16 +11582,16 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>909.3</v>
+        <v>917.2</v>
       </c>
       <c r="I38" t="n">
-        <v>909.3</v>
+        <v>917.2</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0263</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0263</v>
       </c>
     </row>
     <row r="39">
@@ -11552,31 +11604,31 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>873.2</v>
+        <v>883.7</v>
       </c>
       <c r="D39" t="n">
-        <v>78.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0262</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>62.1</v>
+        <v>62.9</v>
       </c>
       <c r="I39" t="n">
-        <v>62.1</v>
+        <v>62.9</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.0489</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.0489</v>
+        <v>0.04940000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -11589,13 +11641,13 @@
         <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="D40" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0164</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0.005</v>
@@ -11604,13 +11656,13 @@
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>240.7</v>
+        <v>243.1</v>
       </c>
       <c r="I40" t="n">
-        <v>185.3</v>
+        <v>187.2</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0103</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0.0058</v>
@@ -11626,13 +11678,13 @@
         <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>3586.9</v>
+        <v>3622.9</v>
       </c>
       <c r="D41" t="n">
-        <v>56.4</v>
+        <v>55.9</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.0929</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0.005</v>
@@ -11641,16 +11693,16 @@
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>2359.8</v>
+        <v>2383.5</v>
       </c>
       <c r="I41" t="n">
-        <v>717.4</v>
+        <v>724.6</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="42">
@@ -11663,13 +11715,13 @@
         <v>7</v>
       </c>
       <c r="C42" t="n">
-        <v>117.8</v>
+        <v>117.1</v>
       </c>
       <c r="D42" t="n">
         <v>19</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.2226</v>
+        <v>0.222</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>0.0059</v>
@@ -11678,16 +11730,16 @@
         <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>521.9</v>
+        <v>524</v>
       </c>
       <c r="I42" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.0919</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0153</v>
       </c>
     </row>
     <row r="43">
@@ -11700,16 +11752,16 @@
         <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>2746.5</v>
+        <v>2783.6</v>
       </c>
       <c r="D43" t="n">
-        <v>186.7</v>
+        <v>141.9</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.0248</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0068</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -11729,13 +11781,13 @@
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>165.2</v>
+        <v>166.5</v>
       </c>
       <c r="D44" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0326</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0.0053</v>
@@ -11744,16 +11796,16 @@
         <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>1628.7</v>
+        <v>1641</v>
       </c>
       <c r="I44" t="n">
-        <v>83.5</v>
+        <v>84.2</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.0188</v>
+        <v>0.019</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="45">
@@ -11766,31 +11818,31 @@
         <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>146.1</v>
+        <v>147.6</v>
       </c>
       <c r="D45" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0189</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="G45" t="n">
         <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>162.4</v>
+        <v>164</v>
       </c>
       <c r="I45" t="n">
-        <v>81.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.0167</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.005600000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -11803,13 +11855,13 @@
         <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>434.1</v>
+        <v>438.3</v>
       </c>
       <c r="D46" t="n">
-        <v>87.3</v>
+        <v>88.2</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.0915</v>
+        <v>0.0924</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>0.0058</v>
@@ -11818,16 +11870,16 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>135.6</v>
+        <v>128.6</v>
       </c>
       <c r="I46" t="n">
-        <v>135.6</v>
+        <v>128.6</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0302</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0302</v>
       </c>
     </row>
     <row r="47">
@@ -11840,31 +11892,31 @@
         <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>257.2</v>
+        <v>259.7</v>
       </c>
       <c r="D47" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0146</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.0048</v>
+        <v>0.0049</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>299.3</v>
+        <v>302.2</v>
       </c>
       <c r="I47" t="n">
-        <v>299.3</v>
+        <v>302.2</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.03240000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -11877,13 +11929,13 @@
         <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>230.4</v>
+        <v>220.6</v>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.101</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>0.0049</v>
@@ -11892,13 +11944,13 @@
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>660.5</v>
+        <v>667.6</v>
       </c>
       <c r="I48" t="n">
-        <v>226.3</v>
+        <v>228.7</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0379</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0.0049</v>
@@ -11914,13 +11966,13 @@
         <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>507.1</v>
+        <v>514.5</v>
       </c>
       <c r="D49" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0254</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>0.004500000000000001</v>
@@ -11943,31 +11995,31 @@
         <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>694.9</v>
+        <v>708.7</v>
       </c>
       <c r="D50" t="n">
-        <v>68.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.1619</v>
+        <v>0.1636</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0046</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>308.8</v>
+        <v>315</v>
       </c>
       <c r="I50" t="n">
-        <v>73</v>
+        <v>74.5</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0076</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="51">
@@ -11980,31 +12032,31 @@
         <v>7</v>
       </c>
       <c r="C51" t="n">
-        <v>97.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.0225</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>0.005</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>788.3</v>
+        <v>886.1</v>
       </c>
       <c r="I51" t="n">
-        <v>436.7</v>
+        <v>440</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.006500000000000001</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.004500000000000001</v>
       </c>
     </row>
     <row r="52">

--- a/state_keywords_analysis.xlsx
+++ b/state_keywords_analysis.xlsx
@@ -1214,7 +1214,7 @@
         <v>0.016</v>
       </c>
       <c r="F34" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>0.0135</v>
       </c>
       <c r="F35" t="n">
-        <v>78.59999999999999</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="36">
@@ -1255,7 +1255,7 @@
         <v>683</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.0503</v>
+        <v>0.0504</v>
       </c>
       <c r="F36" t="n">
         <v>41.8</v>
@@ -1299,10 +1299,10 @@
         <v>226</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0167</v>
       </c>
       <c r="F38" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="39">
@@ -1324,7 +1324,7 @@
         <v>0.0052</v>
       </c>
       <c r="F39" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="40">
@@ -1343,7 +1343,7 @@
         <v>599</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0442</v>
       </c>
       <c r="F40" t="n">
         <v>17.6</v>
@@ -1394,7 +1394,7 @@
         <v>0.0091</v>
       </c>
       <c r="F42" t="n">
-        <v>617.9</v>
+        <v>618.2</v>
       </c>
     </row>
     <row r="43">
@@ -1416,7 +1416,7 @@
         <v>0.009599999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>517.9</v>
+        <v>518.1</v>
       </c>
     </row>
     <row r="44">
@@ -1438,7 +1438,7 @@
         <v>0.0283</v>
       </c>
       <c r="F44" t="n">
-        <v>375.5</v>
+        <v>375.7</v>
       </c>
     </row>
     <row r="45">
@@ -1460,7 +1460,7 @@
         <v>0.0135</v>
       </c>
       <c r="F45" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1482,7 +1482,7 @@
         <v>0.0218</v>
       </c>
       <c r="F46" t="n">
-        <v>69.59999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="47">
@@ -1615,10 +1615,10 @@
         <v>139</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0169</v>
       </c>
       <c r="F52" t="n">
-        <v>45.1</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="53">
@@ -1630,17 +1630,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lotteries</t>
+          <t>Bribery</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>552</v>
+        <v>136</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.0166</v>
       </c>
       <c r="F53" t="n">
-        <v>36.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="54">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bribery</t>
+          <t>Impeachment</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.016</v>
       </c>
       <c r="F54" t="n">
-        <v>18.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -1674,17 +1674,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Culture (Arts)</t>
+          <t>Casinos</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>304</v>
+        <v>68</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.0329</v>
+        <v>0.0083</v>
       </c>
       <c r="F55" t="n">
-        <v>16.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="56">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Impeachment</t>
+          <t>Commuting</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.0142</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>12.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="57">
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Special Sections</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="58">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Casinos</t>
+          <t>Restaurants</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>68</v>
+        <v>735</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -1762,17 +1762,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Commuting</t>
+          <t>Railroads</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.0144</v>
       </c>
       <c r="F59" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -1795,10 +1795,10 @@
         <v>73</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.0109</v>
       </c>
       <c r="F60" t="n">
-        <v>193.3</v>
+        <v>194.1</v>
       </c>
     </row>
     <row r="61">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1802</v>
+        <v>1788</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="F61" t="n">
-        <v>122.2</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="62">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>0.0204</v>
       </c>
       <c r="F62" t="n">
-        <v>97.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3842</v>
+        <v>3818</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.5692</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>91.3</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -1883,10 +1883,10 @@
         <v>34</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="F64" t="n">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="65">
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1106</v>
+        <v>1095</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.1639</v>
+        <v>0.1629</v>
       </c>
       <c r="F65" t="n">
-        <v>82.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3814</v>
+        <v>3791</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2136,7 +2136,7 @@
         <v>0.0064</v>
       </c>
       <c r="F75" t="n">
-        <v>228.4</v>
+        <v>228.5</v>
       </c>
     </row>
     <row r="76">
@@ -2158,7 +2158,7 @@
         <v>0.0113</v>
       </c>
       <c r="F76" t="n">
-        <v>218.3</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="77">
@@ -2180,7 +2180,7 @@
         <v>0.0102</v>
       </c>
       <c r="F77" t="n">
-        <v>180.2</v>
+        <v>180.3</v>
       </c>
     </row>
     <row r="78">
@@ -2202,7 +2202,7 @@
         <v>0.0054</v>
       </c>
       <c r="F78" t="n">
-        <v>159</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="79">
@@ -2224,7 +2224,7 @@
         <v>0.009300000000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>105.3</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="80">
@@ -2246,7 +2246,7 @@
         <v>0.019</v>
       </c>
       <c r="F80" t="n">
-        <v>91.90000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81">
@@ -2265,7 +2265,7 @@
         <v>73</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0105</v>
       </c>
       <c r="F81" t="n">
         <v>81.3</v>
@@ -2290,7 +2290,7 @@
         <v>0.0291</v>
       </c>
       <c r="F82" t="n">
-        <v>119.7</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="83">
@@ -2356,7 +2356,7 @@
         <v>0.0052</v>
       </c>
       <c r="F85" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="86">
@@ -2404,7 +2404,7 @@
         <v>0.0073</v>
       </c>
       <c r="F87" t="n">
-        <v>507.7</v>
+        <v>507.9</v>
       </c>
     </row>
     <row r="88">
@@ -2426,7 +2426,7 @@
         <v>0.0461</v>
       </c>
       <c r="F88" t="n">
-        <v>340.2</v>
+        <v>340.3</v>
       </c>
     </row>
     <row r="89">
@@ -2489,10 +2489,10 @@
         <v>440</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.1334</v>
+        <v>0.1335</v>
       </c>
       <c r="F91" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="92">
@@ -2514,7 +2514,7 @@
         <v>0.0619</v>
       </c>
       <c r="F92" t="n">
-        <v>91.09999999999999</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="93">
@@ -2577,7 +2577,7 @@
         <v>77</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0234</v>
       </c>
       <c r="F95" t="n">
         <v>25.7</v>
@@ -2944,7 +2944,7 @@
         <v>0.0051</v>
       </c>
       <c r="F111" t="n">
-        <v>377.5</v>
+        <v>377.6</v>
       </c>
     </row>
     <row r="112">
@@ -3073,7 +3073,7 @@
         <v>28</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0068</v>
       </c>
       <c r="F117" t="n">
         <v>12.6</v>
@@ -3888,7 +3888,7 @@
         <v>0.0124</v>
       </c>
       <c r="F153" t="n">
-        <v>571.4</v>
+        <v>571.7</v>
       </c>
     </row>
     <row r="154">
@@ -3910,7 +3910,7 @@
         <v>0.012</v>
       </c>
       <c r="F154" t="n">
-        <v>529.8</v>
+        <v>530</v>
       </c>
     </row>
     <row r="155">
@@ -3932,7 +3932,7 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="F155" t="n">
-        <v>427.3</v>
+        <v>427.4</v>
       </c>
     </row>
     <row r="156">
@@ -3954,7 +3954,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F156" t="n">
-        <v>298.4</v>
+        <v>298.5</v>
       </c>
     </row>
     <row r="157">
@@ -3973,10 +3973,10 @@
         <v>698</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.2889</v>
+        <v>0.289</v>
       </c>
       <c r="F157" t="n">
-        <v>272.2</v>
+        <v>272.3</v>
       </c>
     </row>
     <row r="158">
@@ -3998,7 +3998,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F158" t="n">
-        <v>267</v>
+        <v>267.1</v>
       </c>
     </row>
     <row r="159">
@@ -4020,7 +4020,7 @@
         <v>0.0161</v>
       </c>
       <c r="F159" t="n">
-        <v>232.8</v>
+        <v>232.9</v>
       </c>
     </row>
     <row r="160">
@@ -4042,7 +4042,7 @@
         <v>0.005</v>
       </c>
       <c r="F160" t="n">
-        <v>895.2</v>
+        <v>895.6</v>
       </c>
     </row>
     <row r="161">
@@ -4064,7 +4064,7 @@
         <v>0.0116</v>
       </c>
       <c r="F161" t="n">
-        <v>642.7</v>
+        <v>643</v>
       </c>
     </row>
     <row r="162">
@@ -4086,7 +4086,7 @@
         <v>0.0166</v>
       </c>
       <c r="F162" t="n">
-        <v>314.1</v>
+        <v>314.2</v>
       </c>
     </row>
     <row r="163">
@@ -4108,7 +4108,7 @@
         <v>0.0137</v>
       </c>
       <c r="F163" t="n">
-        <v>107</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="164">
@@ -4127,7 +4127,7 @@
         <v>445</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.1842</v>
+        <v>0.1843</v>
       </c>
       <c r="F164" t="n">
         <v>103.2</v>
@@ -4333,10 +4333,10 @@
         <v>233</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.1224</v>
+        <v>0.1226</v>
       </c>
       <c r="F173" t="n">
-        <v>279.3</v>
+        <v>279.6</v>
       </c>
     </row>
     <row r="174">
@@ -4358,7 +4358,7 @@
         <v>0.011</v>
       </c>
       <c r="F174" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="175">
@@ -4380,7 +4380,7 @@
         <v>0.021</v>
       </c>
       <c r="F175" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="176">
@@ -4424,7 +4424,7 @@
         <v>0.0074</v>
       </c>
       <c r="F177" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="178">
@@ -4443,7 +4443,7 @@
         <v>49</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.0258</v>
       </c>
       <c r="F178" t="n">
         <v>30.3</v>
@@ -4468,7 +4468,7 @@
         <v>0.0053</v>
       </c>
       <c r="F179" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="180">
@@ -4491,10 +4491,10 @@
         <v>142</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.0452</v>
+        <v>0.0453</v>
       </c>
       <c r="F180" t="n">
-        <v>232.3</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="181">
@@ -4516,7 +4516,7 @@
         <v>0.0048</v>
       </c>
       <c r="F181" t="n">
-        <v>251.9</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="182">
@@ -4538,7 +4538,7 @@
         <v>0.0707</v>
       </c>
       <c r="F182" t="n">
-        <v>58.1</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="183">
@@ -4560,7 +4560,7 @@
         <v>0.0076</v>
       </c>
       <c r="F183" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="184">
@@ -4579,7 +4579,7 @@
         <v>19</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="F184" t="n">
         <v>35.4</v>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.022</v>
+        <v>0.0217</v>
       </c>
       <c r="F185" t="n">
-        <v>32.3</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="186">
@@ -4623,7 +4623,7 @@
         <v>68</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0217</v>
       </c>
       <c r="F186" t="n">
         <v>24.4</v>
@@ -4851,10 +4851,10 @@
         <v>38</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0227</v>
       </c>
       <c r="F196" t="n">
-        <v>979.6</v>
+        <v>981.4</v>
       </c>
     </row>
     <row r="197">
@@ -4876,7 +4876,7 @@
         <v>0.0048</v>
       </c>
       <c r="F197" t="n">
-        <v>687.4</v>
+        <v>688.7</v>
       </c>
     </row>
     <row r="198">
@@ -4895,10 +4895,10 @@
         <v>163</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0973</v>
       </c>
       <c r="F198" t="n">
-        <v>123.5</v>
+        <v>123.7</v>
       </c>
     </row>
     <row r="199">
@@ -4920,7 +4920,7 @@
         <v>0.0209</v>
       </c>
       <c r="F199" t="n">
-        <v>571.1</v>
+        <v>572.1</v>
       </c>
     </row>
     <row r="200">
@@ -4942,7 +4942,7 @@
         <v>0.0334</v>
       </c>
       <c r="F200" t="n">
-        <v>251.5</v>
+        <v>252</v>
       </c>
     </row>
     <row r="201">
@@ -4964,7 +4964,7 @@
         <v>0.006</v>
       </c>
       <c r="F201" t="n">
-        <v>117.2</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="202">
@@ -4986,7 +4986,7 @@
         <v>0.0185</v>
       </c>
       <c r="F202" t="n">
-        <v>101.4</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="203">
@@ -5005,10 +5005,10 @@
         <v>89</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.053</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="F203" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="204">
@@ -5030,7 +5030,7 @@
         <v>0.006</v>
       </c>
       <c r="F204" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -5049,10 +5049,10 @@
         <v>331</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>0.1973</v>
+        <v>0.1976</v>
       </c>
       <c r="F205" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="206">
@@ -5798,7 +5798,7 @@
         <v>0.033</v>
       </c>
       <c r="F238" t="n">
-        <v>346.8</v>
+        <v>347</v>
       </c>
     </row>
     <row r="239">
@@ -5820,7 +5820,7 @@
         <v>0.0086</v>
       </c>
       <c r="F239" t="n">
-        <v>199.1</v>
+        <v>199.3</v>
       </c>
     </row>
     <row r="240">
@@ -5842,7 +5842,7 @@
         <v>0.033</v>
       </c>
       <c r="F240" t="n">
-        <v>163.5</v>
+        <v>163.6</v>
       </c>
     </row>
     <row r="241">
@@ -5886,7 +5886,7 @@
         <v>0.0453</v>
       </c>
       <c r="F242" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="243">
@@ -6199,10 +6199,10 @@
         <v>213</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0112</v>
       </c>
       <c r="F256" t="n">
-        <v>14</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="257">
@@ -6221,10 +6221,10 @@
         <v>165</v>
       </c>
       <c r="E257" s="2" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F257" t="n">
-        <v>27.7</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="258">
@@ -6236,17 +6236,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Lotteries</t>
+          <t>Casinos</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>580</v>
+        <v>234</v>
       </c>
       <c r="E258" s="2" t="n">
-        <v>0.029</v>
+        <v>0.0123</v>
       </c>
       <c r="F258" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="259">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Casinos</t>
+          <t>Property Taxes</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F259" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="260">
@@ -6280,17 +6280,17 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Property Taxes</t>
+          <t>Bridges and Tunnels</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0114</v>
       </c>
       <c r="F260" t="n">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="261">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bridges and Tunnels</t>
+          <t>Commuting</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.01</v>
       </c>
       <c r="F261" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="262">
@@ -6324,17 +6324,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Commuting</t>
+          <t>Roads and Traffic</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>190</v>
+        <v>745</v>
       </c>
       <c r="E262" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0393</v>
       </c>
       <c r="F262" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="263">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Roads and Traffic</t>
+          <t>Minorities (US)</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>745</v>
+        <v>118</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0062</v>
       </c>
       <c r="F263" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="264">
@@ -6379,10 +6379,10 @@
         <v>22</v>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.0258</v>
       </c>
       <c r="F264" t="n">
-        <v>325.5</v>
+        <v>325.8</v>
       </c>
     </row>
     <row r="265">
@@ -6404,7 +6404,7 @@
         <v>0.004699999999999999</v>
       </c>
       <c r="F265" t="n">
-        <v>206.5</v>
+        <v>206.7</v>
       </c>
     </row>
     <row r="266">
@@ -6423,10 +6423,10 @@
         <v>5</v>
       </c>
       <c r="E266" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
       <c r="F266" t="n">
-        <v>147.1</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="267">
@@ -6448,7 +6448,7 @@
         <v>0.004699999999999999</v>
       </c>
       <c r="F267" t="n">
-        <v>108.8</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="268">
@@ -6470,7 +6470,7 @@
         <v>0.0281</v>
       </c>
       <c r="F268" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="269">
@@ -6489,10 +6489,10 @@
         <v>5</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
       <c r="F269" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="270">
@@ -6511,10 +6511,10 @@
         <v>15</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.0175</v>
+        <v>0.0176</v>
       </c>
       <c r="F270" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -6537,10 +6537,10 @@
         <v>677</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
       <c r="F271" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="272">
@@ -6556,13 +6556,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.025</v>
       </c>
       <c r="F272" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="273">
@@ -6581,10 +6581,10 @@
         <v>740</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F273" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="274">
@@ -6600,13 +6600,13 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0255</v>
       </c>
       <c r="F274" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="275">
@@ -6618,14 +6618,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Fires and Firemen</t>
+          <t>Buses</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>757</v>
+        <v>966</v>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F275" t="n">
         <v>8.800000000000001</v>
@@ -6640,17 +6640,17 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Buses</t>
+          <t>Fires and Firemen</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>966</v>
+        <v>749</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F276" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -6662,17 +6662,17 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>World Trade Center (NYC)</t>
+          <t>Zoning</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>6336</v>
+        <v>574</v>
       </c>
       <c r="E277" s="2" t="n">
-        <v>0.0544</v>
+        <v>0.005</v>
       </c>
       <c r="F277" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="278">
@@ -6684,17 +6684,17 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Hijacking</t>
+          <t>World Trade Center (NYC)</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>5564</v>
+        <v>6300</v>
       </c>
       <c r="E278" s="2" t="n">
-        <v>0.0478</v>
+        <v>0.055</v>
       </c>
       <c r="F278" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="279">
@@ -6720,7 +6720,7 @@
         <v>0.02</v>
       </c>
       <c r="F279" t="n">
-        <v>460.6</v>
+        <v>460.8</v>
       </c>
     </row>
     <row r="280">
@@ -6742,7 +6742,7 @@
         <v>0.0272</v>
       </c>
       <c r="F280" t="n">
-        <v>301.3</v>
+        <v>301.5</v>
       </c>
     </row>
     <row r="281">
@@ -6764,7 +6764,7 @@
         <v>0.0052</v>
       </c>
       <c r="F281" t="n">
-        <v>283.5</v>
+        <v>283.6</v>
       </c>
     </row>
     <row r="282">
@@ -6786,7 +6786,7 @@
         <v>0.0048</v>
       </c>
       <c r="F282" t="n">
-        <v>96.3</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="283">
@@ -6830,7 +6830,7 @@
         <v>0.0086</v>
       </c>
       <c r="F284" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="285">
@@ -7124,7 +7124,7 @@
         <v>0.0121</v>
       </c>
       <c r="F297" t="n">
-        <v>443.1</v>
+        <v>443.3</v>
       </c>
     </row>
     <row r="298">
@@ -7146,7 +7146,7 @@
         <v>0.0077</v>
       </c>
       <c r="F298" t="n">
-        <v>254.7</v>
+        <v>254.8</v>
       </c>
     </row>
     <row r="299">
@@ -7503,7 +7503,7 @@
         <v>66</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.0495</v>
       </c>
       <c r="F314" t="n">
         <v>62.9</v>
@@ -7528,7 +7528,7 @@
         <v>0.004500000000000001</v>
       </c>
       <c r="F315" t="n">
-        <v>883.7</v>
+        <v>884.4</v>
       </c>
     </row>
     <row r="316">
@@ -7550,7 +7550,7 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>281.8</v>
+        <v>282</v>
       </c>
     </row>
     <row r="317">
@@ -7572,7 +7572,7 @@
         <v>0.0262</v>
       </c>
       <c r="F317" t="n">
-        <v>169.8</v>
+        <v>169.9</v>
       </c>
     </row>
     <row r="318">
@@ -7594,7 +7594,7 @@
         <v>0.021</v>
       </c>
       <c r="F318" t="n">
-        <v>158.1</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="319">
@@ -7616,7 +7616,7 @@
         <v>0.0097</v>
       </c>
       <c r="F319" t="n">
-        <v>130</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="320">
@@ -7638,7 +7638,7 @@
         <v>0.024</v>
       </c>
       <c r="F320" t="n">
-        <v>114.7</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="321">
@@ -7660,7 +7660,7 @@
         <v>0.0105</v>
       </c>
       <c r="F321" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="322">
@@ -7686,7 +7686,7 @@
         <v>0.0058</v>
       </c>
       <c r="F322" t="n">
-        <v>243.1</v>
+        <v>243.2</v>
       </c>
     </row>
     <row r="323">
@@ -7815,7 +7815,7 @@
         <v>30</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F328" t="n">
         <v>33.3</v>
@@ -8090,7 +8090,7 @@
         <v>0.05429999999999999</v>
       </c>
       <c r="F340" t="n">
-        <v>524</v>
+        <v>524.2</v>
       </c>
     </row>
     <row r="341">
@@ -8112,7 +8112,7 @@
         <v>0.0153</v>
       </c>
       <c r="F341" t="n">
-        <v>351.9</v>
+        <v>352.1</v>
       </c>
     </row>
     <row r="342">
@@ -8178,7 +8178,7 @@
         <v>0.0059</v>
       </c>
       <c r="F344" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="345">
@@ -8219,7 +8219,7 @@
         <v>450</v>
       </c>
       <c r="E346" s="2" t="n">
-        <v>0.222</v>
+        <v>0.2221</v>
       </c>
       <c r="F346" t="n">
         <v>41.8</v>
@@ -9097,10 +9097,10 @@
         <v>20</v>
       </c>
       <c r="E385" s="2" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0325</v>
       </c>
       <c r="F385" t="n">
-        <v>302.2</v>
+        <v>303.2</v>
       </c>
     </row>
     <row r="386">
@@ -9122,7 +9122,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F386" t="n">
-        <v>259.7</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="387">
@@ -9144,7 +9144,7 @@
         <v>0.0049</v>
       </c>
       <c r="F387" t="n">
-        <v>142.1</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="388">
@@ -9166,7 +9166,7 @@
         <v>0.0146</v>
       </c>
       <c r="F388" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="389">
@@ -9188,7 +9188,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F389" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="390">
@@ -9207,10 +9207,10 @@
         <v>6</v>
       </c>
       <c r="E390" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
       <c r="F390" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="391">
@@ -9232,7 +9232,7 @@
         <v>0.0049</v>
       </c>
       <c r="F391" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="392">
@@ -9254,7 +9254,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F392" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="393">
@@ -9280,7 +9280,7 @@
         <v>0.0049</v>
       </c>
       <c r="F393" t="n">
-        <v>667.6</v>
+        <v>667.8</v>
       </c>
     </row>
     <row r="394">
@@ -9302,7 +9302,7 @@
         <v>0.0379</v>
       </c>
       <c r="F394" t="n">
-        <v>228.7</v>
+        <v>228.8</v>
       </c>
     </row>
     <row r="395">
@@ -9324,7 +9324,7 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="F395" t="n">
-        <v>220.6</v>
+        <v>220.7</v>
       </c>
     </row>
     <row r="396">
@@ -9431,7 +9431,7 @@
         <v>56</v>
       </c>
       <c r="E400" s="2" t="n">
-        <v>0.023</v>
+        <v>0.0231</v>
       </c>
       <c r="F400" t="n">
         <v>25.8</v>
@@ -9842,7 +9842,7 @@
         <v>0.004500000000000001</v>
       </c>
       <c r="F418" t="n">
-        <v>886.1</v>
+        <v>886.6</v>
       </c>
     </row>
     <row r="419">
@@ -9864,7 +9864,7 @@
         <v>0.005500000000000001</v>
       </c>
       <c r="F419" t="n">
-        <v>794.2</v>
+        <v>794.6</v>
       </c>
     </row>
     <row r="420">
@@ -9886,7 +9886,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F420" t="n">
-        <v>440</v>
+        <v>440.2</v>
       </c>
     </row>
     <row r="421">
@@ -10063,10 +10063,10 @@
         <v>3</v>
       </c>
       <c r="E428" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F428" t="n">
-        <v>345.7</v>
+        <v>346.7</v>
       </c>
     </row>
     <row r="429">
@@ -10085,10 +10085,10 @@
         <v>4</v>
       </c>
       <c r="E429" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0105</v>
       </c>
       <c r="F429" t="n">
-        <v>327.4</v>
+        <v>328.2</v>
       </c>
     </row>
     <row r="430">
@@ -10107,10 +10107,10 @@
         <v>12</v>
       </c>
       <c r="E430" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0314</v>
       </c>
       <c r="F430" t="n">
-        <v>247.3</v>
+        <v>248</v>
       </c>
     </row>
     <row r="431">
@@ -10132,7 +10132,7 @@
         <v>0.0131</v>
       </c>
       <c r="F431" t="n">
-        <v>207.6</v>
+        <v>208.2</v>
       </c>
     </row>
     <row r="432">
@@ -10151,10 +10151,10 @@
         <v>3</v>
       </c>
       <c r="E432" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F432" t="n">
-        <v>164.5</v>
+        <v>164.9</v>
       </c>
     </row>
     <row r="433">
@@ -10176,7 +10176,7 @@
         <v>0.0183</v>
       </c>
       <c r="F433" t="n">
-        <v>153.2</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="434">
@@ -10195,10 +10195,10 @@
         <v>25</v>
       </c>
       <c r="E434" s="2" t="n">
-        <v>0.0653</v>
+        <v>0.0654</v>
       </c>
       <c r="F434" t="n">
-        <v>84.5</v>
+        <v>84.7</v>
       </c>
     </row>
   </sheetData>
@@ -10455,13 +10455,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="D6" t="n">
         <v>17.3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0503</v>
+        <v>0.0504</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.0052</v>
@@ -10470,10 +10470,10 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="I6" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.016</v>
@@ -10492,7 +10492,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D7" t="n">
         <v>28.4</v>
@@ -10507,10 +10507,10 @@
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>617.9</v>
+        <v>618.2</v>
       </c>
       <c r="I7" t="n">
-        <v>375.5</v>
+        <v>375.7</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.0283</v>
@@ -10529,31 +10529,31 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.6</v>
+        <v>20.5</v>
       </c>
       <c r="D8" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>45.1</v>
+        <v>50.8</v>
       </c>
       <c r="I8" t="n">
-        <v>45.1</v>
+        <v>50.8</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0169</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="9">
@@ -10566,16 +10566,16 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>193.3</v>
+        <v>194.1</v>
       </c>
       <c r="D9" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.5692</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -10632,7 +10632,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>119.7</v>
+        <v>119.8</v>
       </c>
       <c r="D11" t="n">
         <v>51</v>
@@ -10647,7 +10647,7 @@
         <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>228.4</v>
+        <v>228.5</v>
       </c>
       <c r="I11" t="n">
         <v>81.3</v>
@@ -10669,7 +10669,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>91.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="D12" t="n">
         <v>20.5</v>
@@ -10684,13 +10684,13 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>507.7</v>
+        <v>507.9</v>
       </c>
       <c r="I12" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.1334</v>
+        <v>0.1335</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0.0067</v>
@@ -10779,10 +10779,10 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>377.5</v>
+        <v>377.6</v>
       </c>
       <c r="I15" t="n">
-        <v>377.5</v>
+        <v>377.6</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.0051</v>
@@ -10941,13 +10941,13 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>895.2</v>
+        <v>895.6</v>
       </c>
       <c r="D20" t="n">
         <v>103.2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.1842</v>
+        <v>0.1843</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0.005</v>
@@ -10956,13 +10956,13 @@
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>571.4</v>
+        <v>571.7</v>
       </c>
       <c r="I20" t="n">
-        <v>232.8</v>
+        <v>232.9</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2889</v>
+        <v>0.289</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0.006999999999999999</v>
@@ -11015,13 +11015,13 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>279.3</v>
+        <v>279.6</v>
       </c>
       <c r="D22" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.1224</v>
+        <v>0.1226</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0.0053</v>
@@ -11044,7 +11044,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>251.9</v>
+        <v>252.2</v>
       </c>
       <c r="D23" t="n">
         <v>24</v>
@@ -11059,16 +11059,16 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>232.3</v>
+        <v>232.5</v>
       </c>
       <c r="I23" t="n">
-        <v>232.3</v>
+        <v>232.5</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.0452</v>
+        <v>0.0453</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.0452</v>
+        <v>0.0453</v>
       </c>
     </row>
     <row r="24">
@@ -11118,13 +11118,13 @@
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>571.1</v>
+        <v>572.1</v>
       </c>
       <c r="D25" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.1973</v>
+        <v>0.1976</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0.006</v>
@@ -11133,13 +11133,13 @@
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>979.6</v>
+        <v>981.4</v>
       </c>
       <c r="I25" t="n">
-        <v>123.5</v>
+        <v>123.7</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0973</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0.0048</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>199.1</v>
+        <v>199.3</v>
       </c>
       <c r="D30" t="n">
         <v>26.3</v>
@@ -11302,10 +11302,10 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>346.8</v>
+        <v>347</v>
       </c>
       <c r="I30" t="n">
-        <v>346.8</v>
+        <v>347</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.033</v>
@@ -11361,31 +11361,31 @@
         <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>27.7</v>
+        <v>29.2</v>
       </c>
       <c r="D32" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0393</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0062</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0112</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="33">
@@ -11398,10 +11398,10 @@
         <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>325.5</v>
+        <v>325.8</v>
       </c>
       <c r="D33" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0.0281</v>
@@ -11427,31 +11427,31 @@
         <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="D34" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.0544</v>
+        <v>0.055</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.005</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="35">
@@ -11479,10 +11479,10 @@
         <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>460.6</v>
+        <v>460.8</v>
       </c>
       <c r="I35" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.0272</v>
@@ -11545,10 +11545,10 @@
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>443.1</v>
+        <v>443.3</v>
       </c>
       <c r="I37" t="n">
-        <v>254.7</v>
+        <v>254.8</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.0121</v>
@@ -11604,10 +11604,10 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>883.7</v>
+        <v>884.4</v>
       </c>
       <c r="D39" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>0.0262</v>
@@ -11625,10 +11625,10 @@
         <v>62.9</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.0495</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.0495</v>
       </c>
     </row>
     <row r="40">
@@ -11656,7 +11656,7 @@
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>243.1</v>
+        <v>243.2</v>
       </c>
       <c r="I40" t="n">
         <v>187.2</v>
@@ -11721,7 +11721,7 @@
         <v>19</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.222</v>
+        <v>0.2221</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>0.0059</v>
@@ -11730,7 +11730,7 @@
         <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>524</v>
+        <v>524.2</v>
       </c>
       <c r="I42" t="n">
         <v>25.9</v>
@@ -11892,10 +11892,10 @@
         <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>259.7</v>
+        <v>260.5</v>
       </c>
       <c r="D47" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0.0146</v>
@@ -11907,16 +11907,16 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>302.2</v>
+        <v>303.2</v>
       </c>
       <c r="I47" t="n">
-        <v>302.2</v>
+        <v>303.2</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0325</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0325</v>
       </c>
     </row>
     <row r="48">
@@ -11929,7 +11929,7 @@
         <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>220.6</v>
+        <v>220.7</v>
       </c>
       <c r="D48" t="n">
         <v>19.8</v>
@@ -11944,10 +11944,10 @@
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>667.6</v>
+        <v>667.8</v>
       </c>
       <c r="I48" t="n">
-        <v>228.7</v>
+        <v>228.8</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.0379</v>
@@ -12047,10 +12047,10 @@
         <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>886.1</v>
+        <v>886.6</v>
       </c>
       <c r="I51" t="n">
-        <v>440</v>
+        <v>440.2</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.006500000000000001</v>
@@ -12069,16 +12069,16 @@
         <v>7</v>
       </c>
       <c r="C52" t="n">
-        <v>345.7</v>
+        <v>346.7</v>
       </c>
       <c r="D52" t="n">
-        <v>84.5</v>
+        <v>84.7</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.0653</v>
+        <v>0.0654</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>

--- a/state_keywords_analysis.xlsx
+++ b/state_keywords_analysis.xlsx
@@ -491,10 +491,10 @@
         <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>473.2</v>
+        <v>473.9</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>310.4</v>
+        <v>310.8</v>
       </c>
     </row>
     <row r="4">
@@ -538,7 +538,7 @@
         <v>0.005600000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1738.3</v>
+        <v>1740.7</v>
       </c>
     </row>
     <row r="5">
@@ -560,7 +560,7 @@
         <v>0.0141</v>
       </c>
       <c r="F5" t="n">
-        <v>585</v>
+        <v>585.8</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         <v>0.0155</v>
       </c>
       <c r="F6" t="n">
-        <v>531.1</v>
+        <v>531.9</v>
       </c>
     </row>
     <row r="7">
@@ -604,7 +604,7 @@
         <v>0.0042</v>
       </c>
       <c r="F7" t="n">
-        <v>351</v>
+        <v>351.5</v>
       </c>
     </row>
     <row r="8">
@@ -623,10 +623,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>244.8</v>
+        <v>245.1</v>
       </c>
     </row>
     <row r="9">
@@ -648,7 +648,7 @@
         <v>0.0042</v>
       </c>
       <c r="F9" t="n">
-        <v>228.2</v>
+        <v>228.5</v>
       </c>
     </row>
     <row r="10">
@@ -667,10 +667,10 @@
         <v>20</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0282</v>
       </c>
       <c r="F10" t="n">
-        <v>162.7</v>
+        <v>162.9</v>
       </c>
     </row>
     <row r="11">
@@ -693,10 +693,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0174</v>
       </c>
       <c r="F11" t="n">
-        <v>1070.1</v>
+        <v>1074.7</v>
       </c>
     </row>
     <row r="12">
@@ -715,10 +715,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.0304</v>
       </c>
       <c r="F12" t="n">
-        <v>601.3</v>
+        <v>603.9</v>
       </c>
     </row>
     <row r="13">
@@ -740,7 +740,7 @@
         <v>0.013</v>
       </c>
       <c r="F13" t="n">
-        <v>460.5</v>
+        <v>462.5</v>
       </c>
     </row>
     <row r="14">
@@ -759,10 +759,10 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.0435</v>
       </c>
       <c r="F14" t="n">
-        <v>390.1</v>
+        <v>391.8</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +784,7 @@
         <v>0.013</v>
       </c>
       <c r="F15" t="n">
-        <v>292.6</v>
+        <v>293.9</v>
       </c>
     </row>
     <row r="16">
@@ -803,10 +803,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.0435</v>
       </c>
       <c r="F16" t="n">
-        <v>234.7</v>
+        <v>235.7</v>
       </c>
     </row>
     <row r="17">
@@ -825,10 +825,10 @@
         <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0348</v>
       </c>
       <c r="F17" t="n">
-        <v>215.2</v>
+        <v>216.2</v>
       </c>
     </row>
     <row r="18">
@@ -847,10 +847,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0391</v>
       </c>
       <c r="F18" t="n">
-        <v>206.5</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="19">
@@ -1236,7 +1236,7 @@
         <v>0.0135</v>
       </c>
       <c r="F35" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="36">
@@ -1615,10 +1615,10 @@
         <v>139</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.017</v>
       </c>
       <c r="F52" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="53">
@@ -1747,7 +1747,7 @@
         <v>735</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.08960000000000001</v>
+        <v>0.0897</v>
       </c>
       <c r="F58" t="n">
         <v>9</v>
@@ -1861,7 +1861,7 @@
         <v>3818</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5681</v>
       </c>
       <c r="F63" t="n">
         <v>91.09999999999999</v>
@@ -1927,7 +1927,7 @@
         <v>3791</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5640999999999999</v>
       </c>
       <c r="F66" t="n">
         <v>79.90000000000001</v>
@@ -2136,7 +2136,7 @@
         <v>0.0064</v>
       </c>
       <c r="F75" t="n">
-        <v>228.5</v>
+        <v>228.7</v>
       </c>
     </row>
     <row r="76">
@@ -2158,7 +2158,7 @@
         <v>0.0113</v>
       </c>
       <c r="F76" t="n">
-        <v>218.5</v>
+        <v>218.6</v>
       </c>
     </row>
     <row r="77">
@@ -2180,7 +2180,7 @@
         <v>0.0102</v>
       </c>
       <c r="F77" t="n">
-        <v>180.3</v>
+        <v>180.4</v>
       </c>
     </row>
     <row r="78">
@@ -2202,7 +2202,7 @@
         <v>0.0054</v>
       </c>
       <c r="F78" t="n">
-        <v>159.1</v>
+        <v>159.2</v>
       </c>
     </row>
     <row r="79">
@@ -2224,7 +2224,7 @@
         <v>0.009300000000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>105.4</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="80">
@@ -2243,7 +2243,7 @@
         <v>133</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.019</v>
+        <v>0.0191</v>
       </c>
       <c r="F80" t="n">
         <v>92</v>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0103</v>
       </c>
       <c r="F81" t="n">
-        <v>81.3</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="82">
@@ -2312,7 +2312,7 @@
         <v>0.0109</v>
       </c>
       <c r="F83" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="84">
@@ -2334,7 +2334,7 @@
         <v>0.0067</v>
       </c>
       <c r="F84" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="85">
@@ -2404,7 +2404,7 @@
         <v>0.0073</v>
       </c>
       <c r="F87" t="n">
-        <v>507.9</v>
+        <v>508.2</v>
       </c>
     </row>
     <row r="88">
@@ -2426,7 +2426,7 @@
         <v>0.0461</v>
       </c>
       <c r="F88" t="n">
-        <v>340.3</v>
+        <v>340.5</v>
       </c>
     </row>
     <row r="89">
@@ -2448,7 +2448,7 @@
         <v>0.0097</v>
       </c>
       <c r="F89" t="n">
-        <v>269.1</v>
+        <v>269.3</v>
       </c>
     </row>
     <row r="90">
@@ -2536,7 +2536,7 @@
         <v>0.0155</v>
       </c>
       <c r="F93" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94">
@@ -2602,7 +2602,7 @@
         <v>0.008500000000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="97">
@@ -2628,7 +2628,7 @@
         <v>0.0043</v>
       </c>
       <c r="F97" t="n">
-        <v>3125.5</v>
+        <v>3130.1</v>
       </c>
     </row>
     <row r="98">
@@ -2650,7 +2650,7 @@
         <v>0.03759999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>1451.1</v>
+        <v>1453.2</v>
       </c>
     </row>
     <row r="99">
@@ -2672,7 +2672,7 @@
         <v>0.0434</v>
       </c>
       <c r="F99" t="n">
-        <v>1339.5</v>
+        <v>1341.5</v>
       </c>
     </row>
     <row r="100">
@@ -2691,10 +2691,10 @@
         <v>14</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0203</v>
       </c>
       <c r="F100" t="n">
-        <v>994.5</v>
+        <v>995.9</v>
       </c>
     </row>
     <row r="101">
@@ -2716,7 +2716,7 @@
         <v>0.0116</v>
       </c>
       <c r="F101" t="n">
-        <v>609.9</v>
+        <v>610.7</v>
       </c>
     </row>
     <row r="102">
@@ -2738,7 +2738,7 @@
         <v>0.0058</v>
       </c>
       <c r="F102" t="n">
-        <v>463</v>
+        <v>463.7</v>
       </c>
     </row>
     <row r="103">
@@ -2757,10 +2757,10 @@
         <v>31</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0449</v>
       </c>
       <c r="F103" t="n">
-        <v>374.1</v>
+        <v>374.6</v>
       </c>
     </row>
     <row r="104">
@@ -3882,13 +3882,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.0124</v>
+        <v>0.012</v>
       </c>
       <c r="F153" t="n">
-        <v>571.7</v>
+        <v>552.8</v>
       </c>
     </row>
     <row r="154">
@@ -3910,7 +3910,7 @@
         <v>0.012</v>
       </c>
       <c r="F154" t="n">
-        <v>530</v>
+        <v>530.3</v>
       </c>
     </row>
     <row r="155">
@@ -3932,7 +3932,7 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="F155" t="n">
-        <v>427.4</v>
+        <v>427.6</v>
       </c>
     </row>
     <row r="156">
@@ -3954,7 +3954,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F156" t="n">
-        <v>298.5</v>
+        <v>298.7</v>
       </c>
     </row>
     <row r="157">
@@ -3973,10 +3973,10 @@
         <v>698</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.289</v>
+        <v>0.2891</v>
       </c>
       <c r="F157" t="n">
-        <v>272.3</v>
+        <v>272.4</v>
       </c>
     </row>
     <row r="158">
@@ -3998,7 +3998,7 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="F158" t="n">
-        <v>267.1</v>
+        <v>267.2</v>
       </c>
     </row>
     <row r="159">
@@ -4017,10 +4017,10 @@
         <v>39</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0162</v>
       </c>
       <c r="F159" t="n">
-        <v>232.9</v>
+        <v>233</v>
       </c>
     </row>
     <row r="160">
@@ -4042,7 +4042,7 @@
         <v>0.005</v>
       </c>
       <c r="F160" t="n">
-        <v>895.6</v>
+        <v>896</v>
       </c>
     </row>
     <row r="161">
@@ -4064,7 +4064,7 @@
         <v>0.0116</v>
       </c>
       <c r="F161" t="n">
-        <v>643</v>
+        <v>643.3</v>
       </c>
     </row>
     <row r="162">
@@ -4086,7 +4086,7 @@
         <v>0.0166</v>
       </c>
       <c r="F162" t="n">
-        <v>314.2</v>
+        <v>314.4</v>
       </c>
     </row>
     <row r="163">
@@ -4130,7 +4130,7 @@
         <v>0.1843</v>
       </c>
       <c r="F164" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="165">
@@ -4494,7 +4494,7 @@
         <v>0.0453</v>
       </c>
       <c r="F180" t="n">
-        <v>232.5</v>
+        <v>232.6</v>
       </c>
     </row>
     <row r="181">
@@ -4535,7 +4535,7 @@
         <v>222</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.0707</v>
+        <v>0.0708</v>
       </c>
       <c r="F182" t="n">
         <v>58.2</v>
@@ -4557,7 +4557,7 @@
         <v>24</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
       <c r="F183" t="n">
         <v>41.4</v>
@@ -4645,7 +4645,7 @@
         <v>222</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.0707</v>
+        <v>0.0708</v>
       </c>
       <c r="F187" t="n">
         <v>24</v>
@@ -5078,7 +5078,7 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="F206" t="n">
-        <v>392.4</v>
+        <v>392.8</v>
       </c>
     </row>
     <row r="207">
@@ -5100,7 +5100,7 @@
         <v>0.0063</v>
       </c>
       <c r="F207" t="n">
-        <v>311.4</v>
+        <v>311.6</v>
       </c>
     </row>
     <row r="208">
@@ -5119,10 +5119,10 @@
         <v>98</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.0776</v>
+        <v>0.07769999999999999</v>
       </c>
       <c r="F208" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="209">
@@ -5144,7 +5144,7 @@
         <v>0.0143</v>
       </c>
       <c r="F209" t="n">
-        <v>177.2</v>
+        <v>177.3</v>
       </c>
     </row>
     <row r="210">
@@ -5163,10 +5163,10 @@
         <v>57</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.0451</v>
+        <v>0.0452</v>
       </c>
       <c r="F210" t="n">
-        <v>120.5</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="211">
@@ -5188,7 +5188,7 @@
         <v>0.0071</v>
       </c>
       <c r="F211" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="212">
@@ -5276,7 +5276,7 @@
         <v>0.005500000000000001</v>
       </c>
       <c r="F215" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="216">
@@ -5637,10 +5637,10 @@
         <v>16</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0282</v>
       </c>
       <c r="F231" t="n">
-        <v>214.2</v>
+        <v>214.9</v>
       </c>
     </row>
     <row r="232">
@@ -5662,7 +5662,7 @@
         <v>0.0141</v>
       </c>
       <c r="F232" t="n">
-        <v>167.1</v>
+        <v>167.7</v>
       </c>
     </row>
     <row r="233">
@@ -5681,10 +5681,10 @@
         <v>4</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0071</v>
       </c>
       <c r="F233" t="n">
-        <v>84.5</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="234">
@@ -5706,7 +5706,7 @@
         <v>0.0053</v>
       </c>
       <c r="F234" t="n">
-        <v>71.7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="235">
@@ -5728,7 +5728,7 @@
         <v>0.0176</v>
       </c>
       <c r="F235" t="n">
-        <v>69.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="236">
@@ -5747,10 +5747,10 @@
         <v>4</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0071</v>
       </c>
       <c r="F236" t="n">
-        <v>54.7</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="237">
@@ -5772,7 +5772,7 @@
         <v>0.0053</v>
       </c>
       <c r="F237" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="238">
@@ -6537,7 +6537,7 @@
         <v>677</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="F271" t="n">
         <v>7.8</v>
@@ -6556,13 +6556,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2863</v>
+        <v>2773</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0244</v>
       </c>
       <c r="F272" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273">
@@ -6578,13 +6578,13 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>740</v>
+        <v>706</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0062</v>
       </c>
       <c r="F273" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="274">
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2927</v>
+        <v>2910</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0256</v>
       </c>
       <c r="F274" t="n">
         <v>9.5</v>
@@ -6618,17 +6618,17 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Buses</t>
+          <t>Fires and Firemen</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>966</v>
+        <v>749</v>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="F275" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="276">
@@ -6640,17 +6640,17 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Fires and Firemen</t>
+          <t>Buses</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>749</v>
+        <v>937</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F276" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="277">
@@ -6688,13 +6688,13 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>6300</v>
+        <v>6299</v>
       </c>
       <c r="E278" s="2" t="n">
-        <v>0.055</v>
+        <v>0.0554</v>
       </c>
       <c r="F278" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="279">
@@ -6720,7 +6720,7 @@
         <v>0.02</v>
       </c>
       <c r="F279" t="n">
-        <v>460.8</v>
+        <v>461.1</v>
       </c>
     </row>
     <row r="280">
@@ -6742,7 +6742,7 @@
         <v>0.0272</v>
       </c>
       <c r="F280" t="n">
-        <v>301.5</v>
+        <v>301.6</v>
       </c>
     </row>
     <row r="281">
@@ -6764,7 +6764,7 @@
         <v>0.0052</v>
       </c>
       <c r="F281" t="n">
-        <v>283.6</v>
+        <v>283.8</v>
       </c>
     </row>
     <row r="282">
@@ -6808,7 +6808,7 @@
         <v>0.005699999999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="284">
@@ -6918,7 +6918,7 @@
         <v>0.005699999999999999</v>
       </c>
       <c r="F288" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="289">
@@ -7124,7 +7124,7 @@
         <v>0.0121</v>
       </c>
       <c r="F297" t="n">
-        <v>443.3</v>
+        <v>443.8</v>
       </c>
     </row>
     <row r="298">
@@ -7146,7 +7146,7 @@
         <v>0.0077</v>
       </c>
       <c r="F298" t="n">
-        <v>254.8</v>
+        <v>255.1</v>
       </c>
     </row>
     <row r="299">
@@ -7168,7 +7168,7 @@
         <v>0.0073</v>
       </c>
       <c r="F299" t="n">
-        <v>134.1</v>
+        <v>134.3</v>
       </c>
     </row>
     <row r="300">
@@ -7190,7 +7190,7 @@
         <v>0.0129</v>
       </c>
       <c r="F300" t="n">
-        <v>118.2</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="301">
@@ -7209,10 +7209,10 @@
         <v>16</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F301" t="n">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="302">
@@ -7256,7 +7256,7 @@
         <v>0.0109</v>
       </c>
       <c r="F303" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="304">
@@ -7278,7 +7278,7 @@
         <v>0.0073</v>
       </c>
       <c r="F304" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="305">
@@ -7300,7 +7300,7 @@
         <v>0.008100000000000001</v>
       </c>
       <c r="F305" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="306">
@@ -8472,7 +8472,7 @@
         <v>0.0061</v>
       </c>
       <c r="F357" t="n">
-        <v>1641</v>
+        <v>1642.3</v>
       </c>
     </row>
     <row r="358">
@@ -8494,7 +8494,7 @@
         <v>0.0091</v>
       </c>
       <c r="F358" t="n">
-        <v>1406.6</v>
+        <v>1407.7</v>
       </c>
     </row>
     <row r="359">
@@ -8516,7 +8516,7 @@
         <v>0.019</v>
       </c>
       <c r="F359" t="n">
-        <v>872.9</v>
+        <v>873.5</v>
       </c>
     </row>
     <row r="360">
@@ -8560,7 +8560,7 @@
         <v>0.0053</v>
       </c>
       <c r="F361" t="n">
-        <v>166.5</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="362">
@@ -8582,7 +8582,7 @@
         <v>0.0326</v>
       </c>
       <c r="F362" t="n">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="363">
@@ -8604,7 +8604,7 @@
         <v>0.0053</v>
       </c>
       <c r="F363" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="364">
@@ -8626,7 +8626,7 @@
         <v>0.0061</v>
       </c>
       <c r="F364" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="365">
@@ -8670,7 +8670,7 @@
         <v>0.0068</v>
       </c>
       <c r="F366" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="367">
@@ -8696,7 +8696,7 @@
         <v>0.0074</v>
       </c>
       <c r="F367" t="n">
-        <v>164</v>
+        <v>164.1</v>
       </c>
     </row>
     <row r="368">
@@ -8718,7 +8718,7 @@
         <v>0.0133</v>
       </c>
       <c r="F368" t="n">
-        <v>115.6</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="369">
@@ -8740,7 +8740,7 @@
         <v>0.0167</v>
       </c>
       <c r="F369" t="n">
-        <v>112.5</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="370">
@@ -8762,7 +8762,7 @@
         <v>0.005600000000000001</v>
       </c>
       <c r="F370" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="371">
@@ -8784,7 +8784,7 @@
         <v>0.0053</v>
       </c>
       <c r="F371" t="n">
-        <v>147.6</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="372">
@@ -10066,7 +10066,7 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="F428" t="n">
-        <v>346.7</v>
+        <v>347.6</v>
       </c>
     </row>
     <row r="429">
@@ -10088,7 +10088,7 @@
         <v>0.0105</v>
       </c>
       <c r="F429" t="n">
-        <v>328.2</v>
+        <v>329.1</v>
       </c>
     </row>
     <row r="430">
@@ -10107,10 +10107,10 @@
         <v>12</v>
       </c>
       <c r="E430" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0315</v>
       </c>
       <c r="F430" t="n">
-        <v>248</v>
+        <v>248.6</v>
       </c>
     </row>
     <row r="431">
@@ -10132,7 +10132,7 @@
         <v>0.0131</v>
       </c>
       <c r="F431" t="n">
-        <v>208.2</v>
+        <v>208.7</v>
       </c>
     </row>
     <row r="432">
@@ -10154,7 +10154,7 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="F432" t="n">
-        <v>164.9</v>
+        <v>165.3</v>
       </c>
     </row>
     <row r="433">
@@ -10173,10 +10173,10 @@
         <v>7</v>
       </c>
       <c r="E433" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.0184</v>
       </c>
       <c r="F433" t="n">
-        <v>153.6</v>
+        <v>154</v>
       </c>
     </row>
     <row r="434">
@@ -10195,10 +10195,10 @@
         <v>25</v>
       </c>
       <c r="E434" s="2" t="n">
-        <v>0.0654</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="F434" t="n">
-        <v>84.7</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10315,13 +10315,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1738.3</v>
+        <v>1740.7</v>
       </c>
       <c r="D2" t="n">
-        <v>162.7</v>
+        <v>162.9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0282</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.0042</v>
@@ -10330,13 +10330,13 @@
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>473.2</v>
+        <v>473.9</v>
       </c>
       <c r="I2" t="n">
-        <v>310.4</v>
+        <v>310.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.006999999999999999</v>
@@ -10352,13 +10352,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>601.3</v>
+        <v>603.9</v>
       </c>
       <c r="D3" t="n">
-        <v>206.5</v>
+        <v>207.4</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.0435</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.013</v>
@@ -10367,16 +10367,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1070.1</v>
+        <v>1074.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1070.1</v>
+        <v>1074.7</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0174</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="4">
@@ -10455,7 +10455,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="D6" t="n">
         <v>17.3</v>
@@ -10535,7 +10535,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.08960000000000001</v>
+        <v>0.0897</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.005699999999999999</v>
@@ -10544,16 +10544,16 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="I8" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.017</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="9">
@@ -10572,7 +10572,7 @@
         <v>79.90000000000001</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5681</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.0051</v>
@@ -10647,13 +10647,13 @@
         <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>228.5</v>
+        <v>228.7</v>
       </c>
       <c r="I11" t="n">
-        <v>81.3</v>
+        <v>80.3</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.019</v>
+        <v>0.0191</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0.0054</v>
@@ -10672,7 +10672,7 @@
         <v>91.2</v>
       </c>
       <c r="D12" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0.0619</v>
@@ -10684,7 +10684,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>507.9</v>
+        <v>508.2</v>
       </c>
       <c r="I12" t="n">
         <v>23.3</v>
@@ -10706,13 +10706,13 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>3125.5</v>
+        <v>3130.1</v>
       </c>
       <c r="D13" t="n">
-        <v>374.1</v>
+        <v>374.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0449</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.0043</v>
@@ -10941,10 +10941,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>895.6</v>
+        <v>896</v>
       </c>
       <c r="D20" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0.1843</v>
@@ -10956,13 +10956,13 @@
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>571.7</v>
+        <v>552.8</v>
       </c>
       <c r="I20" t="n">
-        <v>232.9</v>
+        <v>233</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.289</v>
+        <v>0.2891</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0.006999999999999999</v>
@@ -11050,7 +11050,7 @@
         <v>24</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.0707</v>
+        <v>0.0708</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.0048</v>
@@ -11059,10 +11059,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>232.5</v>
+        <v>232.6</v>
       </c>
       <c r="I23" t="n">
-        <v>232.5</v>
+        <v>232.6</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.0453</v>
@@ -11155,13 +11155,13 @@
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>177.2</v>
+        <v>177.3</v>
       </c>
       <c r="D26" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.0451</v>
+        <v>0.0452</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0.0048</v>
@@ -11170,13 +11170,13 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>392.4</v>
+        <v>392.8</v>
       </c>
       <c r="I26" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.0776</v>
+        <v>0.07769999999999999</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0.0063</v>
@@ -11258,13 +11258,13 @@
         <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>214.2</v>
+        <v>214.9</v>
       </c>
       <c r="D29" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0282</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0.0053</v>
@@ -11427,13 +11427,13 @@
         <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.055</v>
+        <v>0.0554</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0.005</v>
@@ -11448,10 +11448,10 @@
         <v>7.8</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="35">
@@ -11479,7 +11479,7 @@
         <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>460.8</v>
+        <v>461.1</v>
       </c>
       <c r="I35" t="n">
         <v>35.4</v>
@@ -11530,25 +11530,25 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>134.1</v>
+        <v>134.3</v>
       </c>
       <c r="D37" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>0.0218</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>443.3</v>
+        <v>443.8</v>
       </c>
       <c r="I37" t="n">
-        <v>254.8</v>
+        <v>255.1</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.0121</v>
@@ -11781,10 +11781,10 @@
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>166.5</v>
+        <v>166.6</v>
       </c>
       <c r="D44" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>0.0326</v>
@@ -11796,7 +11796,7 @@
         <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>1641</v>
+        <v>1642.3</v>
       </c>
       <c r="I44" t="n">
         <v>84.2</v>
@@ -11818,7 +11818,7 @@
         <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>147.6</v>
+        <v>147.7</v>
       </c>
       <c r="D45" t="n">
         <v>21.1</v>
@@ -11833,10 +11833,10 @@
         <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>164</v>
+        <v>164.1</v>
       </c>
       <c r="I45" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.0167</v>
@@ -12069,13 +12069,13 @@
         <v>7</v>
       </c>
       <c r="C52" t="n">
-        <v>346.7</v>
+        <v>347.6</v>
       </c>
       <c r="D52" t="n">
-        <v>84.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.0654</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>0.007900000000000001</v>

--- a/state_keywords_analysis.xlsx
+++ b/state_keywords_analysis.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F434"/>
+  <dimension ref="A1:F435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9107,12 +9107,12 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Green Cards (US)</t>
+          <t>Pro-Palestinian Campus Protests (2023- )</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -9122,7 +9122,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F386" t="n">
-        <v>260.5</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="387">
@@ -9134,17 +9134,17 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Maple Syrup and Sugar</t>
+          <t>Green Cards (US)</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E387" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F387" t="n">
-        <v>142.6</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="388">
@@ -9156,17 +9156,17 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Heroin</t>
+          <t>Maple Syrup and Sugar</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E388" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0049</v>
       </c>
       <c r="F388" t="n">
-        <v>61.8</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="389">
@@ -9178,17 +9178,17 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Euthanasia and Assisted Suicide</t>
+          <t>Heroin</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E389" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0146</v>
       </c>
       <c r="F389" t="n">
-        <v>53.9</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="390">
@@ -9200,17 +9200,17 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Foreign Students (in US)</t>
+          <t>Euthanasia and Assisted Suicide</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E390" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F390" t="n">
-        <v>49.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="391">
@@ -9222,17 +9222,17 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Executive Privilege, Doctrine of</t>
+          <t>Foreign Students (in US)</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E391" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.0098</v>
       </c>
       <c r="F391" t="n">
-        <v>44.1</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="392">
@@ -9244,87 +9244,87 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Pro-Palestinian Campus Protests (2023- )</t>
+          <t>Executive Privilege, Doctrine of</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E392" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0049</v>
       </c>
       <c r="F392" t="n">
-        <v>30.1</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
+      <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Headline event</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, Shooting (2019)</t>
+          <t>Mad Cow Disease (Bovine Spongiform Encephalopathy)</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0.0049</v>
       </c>
       <c r="F393" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Headline event</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, Shooting (2019)</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>12</v>
+      </c>
+      <c r="E394" s="2" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F394" t="n">
         <v>667.8</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr"/>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>Charlottesville, VA, Violence (August, 2017)</t>
-        </is>
-      </c>
-      <c r="D394" t="n">
-        <v>92</v>
-      </c>
-      <c r="E394" s="2" t="n">
-        <v>0.0379</v>
-      </c>
-      <c r="F394" t="n">
-        <v>228.8</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Serial Murders</t>
+          <t>Charlottesville, VA, Violence (August, 2017)</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>235</v>
+        <v>92</v>
       </c>
       <c r="E395" s="2" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0379</v>
       </c>
       <c r="F395" t="n">
-        <v>220.7</v>
+        <v>228.8</v>
       </c>
     </row>
     <row r="396">
@@ -9336,17 +9336,17 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Gifts to Public Officials</t>
+          <t>Serial Murders</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="E396" s="2" t="n">
-        <v>0.0107</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F396" t="n">
-        <v>94.09999999999999</v>
+        <v>220.7</v>
       </c>
     </row>
     <row r="397">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Neo Nazi Groups</t>
+          <t>Gifts to Public Officials</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E397" s="2" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0107</v>
       </c>
       <c r="F397" t="n">
-        <v>39.1</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="398">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Whites</t>
+          <t>Neo Nazi Groups</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E398" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F398" t="n">
-        <v>36.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="399">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Confessions</t>
+          <t>Whites</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E399" s="2" t="n">
-        <v>0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="F399" t="n">
-        <v>26.1</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="400">
@@ -9424,17 +9424,17 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Fringe Groups and Movements</t>
+          <t>Confessions</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E400" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0049</v>
       </c>
       <c r="F400" t="n">
-        <v>25.8</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="401">
@@ -9446,65 +9446,65 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
+          <t>Fringe Groups and Movements</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>56</v>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="F401" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
           <t>Civil War (US) (1861-65)</t>
         </is>
       </c>
-      <c r="D401" t="n">
+      <c r="D402" t="n">
         <v>41</v>
       </c>
-      <c r="E401" s="2" t="n">
+      <c r="E402" s="2" t="n">
         <v>0.0169</v>
       </c>
-      <c r="F401" t="n">
+      <c r="F402" t="n">
         <v>19.8</v>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>Washington</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
         <is>
           <t>Hanford Nuclear Reservation (Wash)</t>
         </is>
       </c>
-      <c r="D402" t="n">
+      <c r="D403" t="n">
         <v>8</v>
       </c>
-      <c r="E402" s="2" t="n">
+      <c r="E403" s="2" t="n">
         <v>0.004500000000000001</v>
       </c>
-      <c r="F402" t="n">
+      <c r="F403" t="n">
         <v>514.5</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr"/>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>Hornets (Insects)</t>
-        </is>
-      </c>
-      <c r="D403" t="n">
-        <v>10</v>
-      </c>
-      <c r="E403" s="2" t="n">
-        <v>0.005600000000000001</v>
-      </c>
-      <c r="F403" t="n">
-        <v>452.6</v>
       </c>
     </row>
     <row r="404">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Landslides and Mudslides</t>
+          <t>Hornets (Insects)</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E404" s="2" t="n">
-        <v>0.0254</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F404" t="n">
-        <v>89</v>
+        <v>452.6</v>
       </c>
     </row>
     <row r="405">
@@ -9538,17 +9538,17 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Mad Cow Disease (Bovine Spongiform Encephalopathy)</t>
+          <t>Landslides and Mudslides</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E405" s="2" t="n">
-        <v>0.0136</v>
+        <v>0.0254</v>
       </c>
       <c r="F405" t="n">
-        <v>81.5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="406">
@@ -9560,17 +9560,17 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Livestock Diseases</t>
+          <t>Mad Cow Disease (Bovine Spongiform Encephalopathy)</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0136</v>
       </c>
       <c r="F406" t="n">
-        <v>57.1</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="407">
@@ -9582,17 +9582,17 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Livestock Diseases</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E407" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F407" t="n">
-        <v>56.8</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="408">
@@ -9604,87 +9604,87 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
+          <t>Salmon</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>21</v>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="F408" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
           <t>Nuclear Wastes</t>
         </is>
       </c>
-      <c r="D408" t="n">
+      <c r="D409" t="n">
         <v>17</v>
       </c>
-      <c r="E408" s="2" t="n">
+      <c r="E409" s="2" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="F408" t="n">
+      <c r="F409" t="n">
         <v>47.5</v>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
+    <row r="410">
+      <c r="A410" t="inlineStr">
         <is>
           <t>West Virginia</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C410" t="inlineStr">
         <is>
           <t>Washington DC National Guard Shooting (Nov 2025)</t>
         </is>
       </c>
-      <c r="D409" t="n">
+      <c r="D410" t="n">
         <v>4</v>
       </c>
-      <c r="E409" s="2" t="n">
+      <c r="E410" s="2" t="n">
         <v>0.0061</v>
       </c>
-      <c r="F409" t="n">
+      <c r="F410" t="n">
         <v>315</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr"/>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>American Families Plan (2021)</t>
-        </is>
-      </c>
-      <c r="D410" t="n">
-        <v>5</v>
-      </c>
-      <c r="E410" s="2" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="F410" t="n">
-        <v>74.5</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Strip Mining</t>
+          <t>American Families Plan (2021)</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E411" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.0076</v>
       </c>
       <c r="F411" t="n">
-        <v>708.7</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="412">
@@ -9696,17 +9696,17 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Mountaintop Removal Mining</t>
+          <t>Strip Mining</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E412" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0046</v>
       </c>
       <c r="F412" t="n">
-        <v>300.6</v>
+        <v>708.7</v>
       </c>
     </row>
     <row r="413">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Mines and Mining</t>
+          <t>Mountaintop Removal Mining</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="E413" s="2" t="n">
-        <v>0.1636</v>
+        <v>0.0061</v>
       </c>
       <c r="F413" t="n">
-        <v>147.3</v>
+        <v>300.6</v>
       </c>
     </row>
     <row r="414">
@@ -9740,17 +9740,17 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Mines and Mining</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E414" s="2" t="n">
-        <v>0.1284</v>
+        <v>0.1636</v>
       </c>
       <c r="F414" t="n">
-        <v>144.9</v>
+        <v>147.3</v>
       </c>
     </row>
     <row r="415">
@@ -9762,17 +9762,17 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Explosions (Accidental)</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="E415" s="2" t="n">
-        <v>0.0168</v>
+        <v>0.1284</v>
       </c>
       <c r="F415" t="n">
-        <v>90.5</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="416">
@@ -9784,17 +9784,17 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Explosions</t>
+          <t>Explosions (Accidental)</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E416" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0168</v>
       </c>
       <c r="F416" t="n">
-        <v>70.3</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="417">
@@ -9806,65 +9806,65 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
+          <t>Explosions</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>17</v>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F417" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
           <t>Carbon Monoxide</t>
         </is>
       </c>
-      <c r="D417" t="n">
+      <c r="D418" t="n">
         <v>3</v>
       </c>
-      <c r="E417" s="2" t="n">
+      <c r="E418" s="2" t="n">
         <v>0.0046</v>
       </c>
-      <c r="F417" t="n">
+      <c r="F418" t="n">
         <v>62.8</v>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
+    <row r="419">
+      <c r="A419" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>Headline event</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C419" t="inlineStr">
         <is>
           <t>Abundant Life Christian School, Madison, Wis, Shooting (2024)</t>
         </is>
       </c>
-      <c r="D418" t="n">
+      <c r="D419" t="n">
         <v>9</v>
       </c>
-      <c r="E418" s="2" t="n">
+      <c r="E419" s="2" t="n">
         <v>0.004500000000000001</v>
       </c>
-      <c r="F418" t="n">
+      <c r="F419" t="n">
         <v>886.6</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr"/>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Headline event</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>Waukesha, Wis, Holiday Parade Attack (2021)</t>
-        </is>
-      </c>
-      <c r="D419" t="n">
-        <v>11</v>
-      </c>
-      <c r="E419" s="2" t="n">
-        <v>0.005500000000000001</v>
-      </c>
-      <c r="F419" t="n">
-        <v>794.6</v>
       </c>
     </row>
     <row r="420">
@@ -9876,39 +9876,39 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Oak Creek, Wis, Shooting (2012)</t>
+          <t>Waukesha, Wis, Holiday Parade Attack (2021)</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E420" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F420" t="n">
-        <v>440.2</v>
+        <v>794.6</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Headline event</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Collective Bargaining</t>
+          <t>Oak Creek, Wis, Shooting (2012)</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E421" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F421" t="n">
-        <v>98.09999999999999</v>
+        <v>440.2</v>
       </c>
     </row>
     <row r="422">
@@ -9920,17 +9920,17 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Self-Defense</t>
+          <t>Collective Bargaining</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="E422" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="F422" t="n">
-        <v>75.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="423">
@@ -9942,17 +9942,17 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Sikhs and Sikhism</t>
+          <t>Self-Defense</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E423" s="2" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F423" t="n">
-        <v>74.5</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="424">
@@ -9964,17 +9964,17 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Project Democracy</t>
+          <t>Sikhs and Sikhism</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E424" s="2" t="n">
-        <v>0.005</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F424" t="n">
-        <v>66.90000000000001</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="425">
@@ -9986,17 +9986,17 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Republican National Convention</t>
+          <t>Project Democracy</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E425" s="2" t="n">
-        <v>0.0185</v>
+        <v>0.005</v>
       </c>
       <c r="F425" t="n">
-        <v>36.3</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="426">
@@ -10008,17 +10008,17 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Deer</t>
+          <t>Republican National Convention</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E426" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0185</v>
       </c>
       <c r="F426" t="n">
-        <v>32.8</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="427">
@@ -10030,65 +10030,65 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>10</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F427" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr"/>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
           <t>Voter Fraud (Election Fraud)</t>
         </is>
       </c>
-      <c r="D427" t="n">
+      <c r="D428" t="n">
         <v>38</v>
       </c>
-      <c r="E427" s="2" t="n">
+      <c r="E428" s="2" t="n">
         <v>0.019</v>
       </c>
-      <c r="F427" t="n">
+      <c r="F428" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
+    <row r="429">
+      <c r="A429" t="inlineStr">
         <is>
           <t>Wyoming</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
         <is>
           <t>Treasure Troves</t>
         </is>
       </c>
-      <c r="D428" t="n">
+      <c r="D429" t="n">
         <v>3</v>
       </c>
-      <c r="E428" s="2" t="n">
+      <c r="E429" s="2" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="F428" t="n">
+      <c r="F429" t="n">
         <v>347.6</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr"/>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Recurring</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>Elk</t>
-        </is>
-      </c>
-      <c r="D429" t="n">
-        <v>4</v>
-      </c>
-      <c r="E429" s="2" t="n">
-        <v>0.0105</v>
-      </c>
-      <c r="F429" t="n">
-        <v>329.1</v>
       </c>
     </row>
     <row r="430">
@@ -10100,17 +10100,17 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Elk</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E430" s="2" t="n">
-        <v>0.0315</v>
+        <v>0.0105</v>
       </c>
       <c r="F430" t="n">
-        <v>248.6</v>
+        <v>329.1</v>
       </c>
     </row>
     <row r="431">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Snowmobiles</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E431" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0315</v>
       </c>
       <c r="F431" t="n">
-        <v>208.7</v>
+        <v>248.6</v>
       </c>
     </row>
     <row r="432">
@@ -10144,17 +10144,17 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Bison</t>
+          <t>Snowmobiles</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E432" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0131</v>
       </c>
       <c r="F432" t="n">
-        <v>165.3</v>
+        <v>208.7</v>
       </c>
     </row>
     <row r="433">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Ranches</t>
+          <t>Bison</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E433" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F433" t="n">
-        <v>154</v>
+        <v>165.3</v>
       </c>
     </row>
     <row r="434">
@@ -10188,21 +10188,43 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
+          <t>Ranches</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>7</v>
+      </c>
+      <c r="E434" s="2" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="F434" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr"/>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
           <t>National Parks, Monuments and Seashores</t>
         </is>
       </c>
-      <c r="D434" t="n">
+      <c r="D435" t="n">
         <v>25</v>
       </c>
-      <c r="E434" s="2" t="n">
+      <c r="E435" s="2" t="n">
         <v>0.06559999999999999</v>
       </c>
-      <c r="F434" t="n">
+      <c r="F435" t="n">
         <v>84.90000000000001</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E434">
+  <conditionalFormatting sqref="E2:E435">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10212,7 +10234,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F434">
+  <conditionalFormatting sqref="F2:F435">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11895,7 +11917,7 @@
         <v>260.5</v>
       </c>
       <c r="D47" t="n">
-        <v>30.1</v>
+        <v>29.3</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0.0146</v>
@@ -11904,19 +11926,19 @@
         <v>0.0049</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>303.2</v>
       </c>
       <c r="I47" t="n">
-        <v>303.2</v>
+        <v>30.1</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.0325</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.006500000000000001</v>
       </c>
     </row>
     <row r="48">

--- a/state_keywords_analysis.xlsx
+++ b/state_keywords_analysis.xlsx
@@ -8348,17 +8348,17 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>budgets_and_budgeting</t>
+          <t>Oglala Sioux Indians</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E352" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0248</v>
       </c>
       <c r="F352" t="n">
-        <v>1826.7</v>
+        <v>1786.2</v>
       </c>
     </row>
     <row r="353">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Oglala Sioux Indians</t>
+          <t>Neutrinos</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E353" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.0068</v>
       </c>
       <c r="F353" t="n">
-        <v>1786.2</v>
+        <v>317.7</v>
       </c>
     </row>
     <row r="354">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>health_insurance</t>
+          <t>Bison</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -8402,7 +8402,7 @@
         <v>0.0068</v>
       </c>
       <c r="F354" t="n">
-        <v>1328.5</v>
+        <v>141.9</v>
       </c>
     </row>
     <row r="355">
@@ -8414,17 +8414,17 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Neutrinos</t>
+          <t>Native Americans</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="E355" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.1329</v>
       </c>
       <c r="F355" t="n">
-        <v>317.7</v>
+        <v>99</v>
       </c>
     </row>
     <row r="356">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Bison</t>
+          <t>Medal of Honor (US)</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8446,7 +8446,7 @@
         <v>0.0068</v>
       </c>
       <c r="F356" t="n">
-        <v>141.9</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="357">
@@ -11777,10 +11777,10 @@
         <v>2783.6</v>
       </c>
       <c r="D43" t="n">
-        <v>141.9</v>
+        <v>94.3</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.1329</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>0.0068</v>
